--- a/data/rateBuildUp/File1/RPT_RPT4414865920010NC_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT4414865920010NC_rateBuildUp.xlsx
@@ -3105,49 +3105,49 @@
         </is>
       </c>
       <c r="BB11" s="383" t="n">
-        <v>28535.49427273367</v>
+        <v>27784.07371349034</v>
       </c>
       <c r="BC11" s="384" t="n">
-        <v>28218.52276767156</v>
+        <v>26791.38312506493</v>
       </c>
       <c r="BD11" s="384" t="n">
-        <v>28320.32774088531</v>
+        <v>26298.97718566558</v>
       </c>
       <c r="BE11" s="384" t="n">
-        <v>26280.61468023898</v>
+        <v>23936.89680193758</v>
       </c>
       <c r="BF11" s="385" t="n">
-        <v>26274.64259933642</v>
+        <v>23500.69273359952</v>
       </c>
       <c r="BG11" s="386" t="n">
-        <v>405.1659959509614</v>
+        <v>394.4968252558961</v>
       </c>
       <c r="BH11" s="372" t="n">
-        <v>489.8307372219012</v>
+        <v>465.0577585294278</v>
       </c>
       <c r="BI11" s="372" t="n">
-        <v>541.8775257478356</v>
+        <v>503.2012629745701</v>
       </c>
       <c r="BJ11" s="372" t="n">
-        <v>582.7679089778392</v>
+        <v>530.7963860971854</v>
       </c>
       <c r="BK11" s="387" t="n">
-        <v>577.2373044476068</v>
+        <v>516.295377754712</v>
       </c>
       <c r="BL11" s="388" t="n">
-        <v>405.1659959509614</v>
+        <v>394.4968252558961</v>
       </c>
       <c r="BM11" s="389" t="n">
-        <v>489.8307372219012</v>
+        <v>465.0577585294278</v>
       </c>
       <c r="BN11" s="389" t="n">
-        <v>541.8775257478356</v>
+        <v>503.2012629745701</v>
       </c>
       <c r="BO11" s="389" t="n">
-        <v>582.7679089778392</v>
+        <v>530.7963860971854</v>
       </c>
       <c r="BP11" s="390" t="n">
-        <v>577.2373044476068</v>
+        <v>516.295377754712</v>
       </c>
       <c r="BR11" s="83" t="inlineStr">
         <is>
@@ -3155,64 +3155,64 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>28322.20805009452</v>
+        <v>27576.4039224841</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>28002.07171383925</v>
+        <v>26585.87899011109</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>28094.86551429901</v>
+        <v>26089.60722330238</v>
       </c>
       <c r="BV11" s="375" t="n">
-        <v>26054.0704913905</v>
+        <v>23730.55593299199</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26045.21236363478</v>
+        <v>23295.48463409304</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>405.8570401836623</v>
+        <v>395.1696723324924</v>
       </c>
       <c r="BY11" s="372" t="n">
-        <v>490.9636863282959</v>
+        <v>466.1334092224325</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>543.4302890512533</v>
+        <v>504.6431985010564</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>584.8282025319799</v>
+        <v>532.6729416795874</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>578.9790234911328</v>
+        <v>517.8532145136863</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>405.8570401836623</v>
+        <v>395.1696723324924</v>
       </c>
       <c r="CD11" s="389" t="n">
-        <v>490.9636863282959</v>
+        <v>466.1334092224325</v>
       </c>
       <c r="CE11" s="389" t="n">
-        <v>543.4302890512533</v>
+        <v>504.6431985010564</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>584.8282025319799</v>
+        <v>532.6729416795874</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>578.9790234911328</v>
+        <v>517.8532145136863</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>-0.6910442327008468</v>
+        <v>-0.6728470765962697</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>-1.132949106394676</v>
+        <v>-1.075650693004661</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>-1.552763303417692</v>
+        <v>-1.441935526486247</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>-2.060293554140685</v>
+        <v>-1.876555582402034</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>-1.741719043526018</v>
+        <v>-1.557836758974304</v>
       </c>
       <c r="DC11" s="393" t="n">
         <v>0.006882681329727</v>
@@ -3221,7 +3221,7 @@
         <v>0.00707891088497888</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.007369697822890921</v>
+        <v>0.007369697822890922</v>
       </c>
       <c r="DF11" s="394" t="n">
         <v>0.008029147366660704</v>
@@ -3387,49 +3387,49 @@
         </is>
       </c>
       <c r="BB12" s="383" t="n">
-        <v>26415.84627540727</v>
+        <v>25724.68915433884</v>
       </c>
       <c r="BC12" s="384" t="n">
-        <v>27986.99490390122</v>
+        <v>26623.44544715671</v>
       </c>
       <c r="BD12" s="384" t="n">
-        <v>30304.56250072378</v>
+        <v>28213.13054823015</v>
       </c>
       <c r="BE12" s="384" t="n">
-        <v>32921.43236967759</v>
+        <v>30066.982829936</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>35412.91240490867</v>
+        <v>31762.82686408767</v>
       </c>
       <c r="BG12" s="386" t="n">
-        <v>1087.317919203497</v>
+        <v>1058.868801394144</v>
       </c>
       <c r="BH12" s="372" t="n">
-        <v>1288.207101130799</v>
+        <v>1225.444589508786</v>
       </c>
       <c r="BI12" s="372" t="n">
-        <v>1387.655666521349</v>
+        <v>1291.888324559152</v>
       </c>
       <c r="BJ12" s="372" t="n">
-        <v>1565.504867365974</v>
+        <v>1429.767922571558</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>1656.811177512632</v>
+        <v>1486.040062904413</v>
       </c>
       <c r="BL12" s="386" t="n">
-        <v>1087.317919203497</v>
+        <v>1058.868801394144</v>
       </c>
       <c r="BM12" s="372" t="n">
-        <v>1288.207101130799</v>
+        <v>1225.444589508786</v>
       </c>
       <c r="BN12" s="372" t="n">
-        <v>1387.655666521349</v>
+        <v>1291.888324559152</v>
       </c>
       <c r="BO12" s="372" t="n">
-        <v>1565.504867365974</v>
+        <v>1429.767922571558</v>
       </c>
       <c r="BP12" s="387" t="n">
-        <v>1656.811177512632</v>
+        <v>1486.040062904413</v>
       </c>
       <c r="BR12" s="101" t="inlineStr">
         <is>
@@ -3437,67 +3437,67 @@
         </is>
       </c>
       <c r="BS12" s="391" t="n">
-        <v>26329.80067622504</v>
+        <v>25640.89489429568</v>
       </c>
       <c r="BT12" s="375" t="n">
-        <v>27900.96826196152</v>
+        <v>26541.61009410976</v>
       </c>
       <c r="BU12" s="375" t="n">
-        <v>30211.6015632763</v>
+        <v>28126.58519506662</v>
       </c>
       <c r="BV12" s="375" t="n">
-        <v>32821.07093582704</v>
+        <v>29975.32322428799</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>35324.77891113863</v>
+        <v>31683.77748030535</v>
       </c>
       <c r="BX12" s="386" t="n">
-        <v>1088.422091931164</v>
+        <v>1059.944084006551</v>
       </c>
       <c r="BY12" s="372" t="n">
-        <v>1289.442759230059</v>
+        <v>1226.620045327102</v>
       </c>
       <c r="BZ12" s="372" t="n">
-        <v>1388.989011114385</v>
+        <v>1293.129650021884</v>
       </c>
       <c r="CA12" s="372" t="n">
-        <v>1567.225421588523</v>
+        <v>1431.339296310296</v>
       </c>
       <c r="CB12" s="387" t="n">
-        <v>1658.548376232081</v>
+        <v>1487.598204791289</v>
       </c>
       <c r="CC12" s="386" t="n">
-        <v>1088.422091931164</v>
+        <v>1059.944084006551</v>
       </c>
       <c r="CD12" s="372" t="n">
-        <v>1289.442759230059</v>
+        <v>1226.620045327102</v>
       </c>
       <c r="CE12" s="372" t="n">
-        <v>1388.989011114385</v>
+        <v>1293.129650021884</v>
       </c>
       <c r="CF12" s="372" t="n">
-        <v>1567.225421588523</v>
+        <v>1431.339296310296</v>
       </c>
       <c r="CG12" s="387" t="n">
-        <v>1658.548376232081</v>
+        <v>1487.598204791289</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>-1.104172727667901</v>
+        <v>-1.075282612406681</v>
       </c>
       <c r="CX12" s="103" t="n">
-        <v>-1.235658099259808</v>
+        <v>-1.175455818316323</v>
       </c>
       <c r="CY12" s="103" t="n">
-        <v>-1.333344593036372</v>
+        <v>-1.24132546273222</v>
       </c>
       <c r="CZ12" s="103" t="n">
-        <v>-1.720554222548571</v>
+        <v>-1.571373738737748</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>-1.737198719449225</v>
+        <v>-1.558141886876456</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.001959277825132627</v>
+        <v>0.001959277825132628</v>
       </c>
       <c r="DD12" s="397" t="n">
         <v>0.001775498736090939</v>
@@ -3669,49 +3669,49 @@
         </is>
       </c>
       <c r="BB13" s="383" t="n">
-        <v>56418.80044405717</v>
+        <v>55082.99891742843</v>
       </c>
       <c r="BC13" s="384" t="n">
-        <v>68061.90318124631</v>
+        <v>64948.66164323039</v>
       </c>
       <c r="BD13" s="384" t="n">
-        <v>80312.38502111268</v>
+        <v>74864.23957735994</v>
       </c>
       <c r="BE13" s="384" t="n">
-        <v>95718.50622591648</v>
+        <v>87437.11829818884</v>
       </c>
       <c r="BF13" s="385" t="n">
-        <v>102321.5533311226</v>
+        <v>91795.15736865136</v>
       </c>
       <c r="BG13" s="386" t="n">
-        <v>945.448734626155</v>
+        <v>923.0637875318773</v>
       </c>
       <c r="BH13" s="372" t="n">
-        <v>1031.972578942236</v>
+        <v>984.7687872659901</v>
       </c>
       <c r="BI13" s="372" t="n">
-        <v>1111.671683105557</v>
+        <v>1036.259291683383</v>
       </c>
       <c r="BJ13" s="372" t="n">
-        <v>1205.24108025732</v>
+        <v>1100.965853599615</v>
       </c>
       <c r="BK13" s="387" t="n">
-        <v>1269.824711142503</v>
+        <v>1139.190672885082</v>
       </c>
       <c r="BL13" s="386" t="n">
-        <v>945.448734626155</v>
+        <v>923.0637875318773</v>
       </c>
       <c r="BM13" s="372" t="n">
-        <v>1031.972578942236</v>
+        <v>984.7687872659901</v>
       </c>
       <c r="BN13" s="372" t="n">
-        <v>1111.671683105557</v>
+        <v>1036.259291683383</v>
       </c>
       <c r="BO13" s="372" t="n">
-        <v>1205.24108025732</v>
+        <v>1100.965853599615</v>
       </c>
       <c r="BP13" s="387" t="n">
-        <v>1269.824711142503</v>
+        <v>1139.190672885082</v>
       </c>
       <c r="BR13" s="111" t="inlineStr">
         <is>
@@ -3719,70 +3719,70 @@
         </is>
       </c>
       <c r="BS13" s="391" t="n">
-        <v>56389.2075636782</v>
+        <v>55054.1066938248</v>
       </c>
       <c r="BT13" s="375" t="n">
-        <v>68028.40616848743</v>
+        <v>64916.69682817164</v>
       </c>
       <c r="BU13" s="375" t="n">
-        <v>80275.37117388066</v>
+        <v>74829.73663580077</v>
       </c>
       <c r="BV13" s="375" t="n">
-        <v>95676.90735934766</v>
+        <v>87399.11848853173</v>
       </c>
       <c r="BW13" s="392" t="n">
-        <v>102277.2793220108</v>
+        <v>91755.43807685556</v>
       </c>
       <c r="BX13" s="386" t="n">
-        <v>946.2000887448385</v>
+        <v>923.7973521908262</v>
       </c>
       <c r="BY13" s="372" t="n">
-        <v>1032.705485420063</v>
+        <v>985.4681696314484</v>
       </c>
       <c r="BZ13" s="372" t="n">
-        <v>1112.37738860219</v>
+        <v>1036.917124287372</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>1205.922877818226</v>
+        <v>1101.588663297958</v>
       </c>
       <c r="CB13" s="387" t="n">
-        <v>1270.521214318287</v>
+        <v>1139.815522846281</v>
       </c>
       <c r="CC13" s="386" t="n">
-        <v>946.2000887448385</v>
+        <v>923.7973521908262</v>
       </c>
       <c r="CD13" s="372" t="n">
-        <v>1032.705485420063</v>
+        <v>985.4681696314484</v>
       </c>
       <c r="CE13" s="372" t="n">
-        <v>1112.37738860219</v>
+        <v>1036.917124287372</v>
       </c>
       <c r="CF13" s="372" t="n">
-        <v>1205.922877818226</v>
+        <v>1101.588663297958</v>
       </c>
       <c r="CG13" s="387" t="n">
-        <v>1270.521214318287</v>
+        <v>1139.815522846281</v>
       </c>
       <c r="CW13" s="102" t="n">
-        <v>-0.75135411868348</v>
+        <v>-0.7335646589489215</v>
       </c>
       <c r="CX13" s="103" t="n">
-        <v>-0.7329064778266456</v>
+        <v>-0.6993823654582911</v>
       </c>
       <c r="CY13" s="103" t="n">
-        <v>-0.7057054966328451</v>
+        <v>-0.6578326039884814</v>
       </c>
       <c r="CZ13" s="103" t="n">
-        <v>-0.6817975609060341</v>
+        <v>-0.6228096983427349</v>
       </c>
       <c r="DA13" s="104" t="n">
-        <v>-0.696503175783846</v>
+        <v>-0.6248499611997431</v>
       </c>
       <c r="DC13" s="396" t="n">
         <v>0.0002838850552595797</v>
       </c>
       <c r="DD13" s="397" t="n">
-        <v>0.0002515107465432486</v>
+        <v>0.0002515107465432487</v>
       </c>
       <c r="DE13" s="397" t="n">
         <v>0.0002202215810066617</v>
@@ -3951,49 +3951,49 @@
         </is>
       </c>
       <c r="BB14" s="413" t="n">
-        <v>1396.713675262076</v>
+        <v>1356.32443166663</v>
       </c>
       <c r="BC14" s="414" t="n">
-        <v>1574.304239361768</v>
+        <v>1484.18872850535</v>
       </c>
       <c r="BD14" s="414" t="n">
-        <v>1783.009384712696</v>
+        <v>1631.170089156166</v>
       </c>
       <c r="BE14" s="414" t="n">
-        <v>1972.040097159817</v>
+        <v>1768.194195092247</v>
       </c>
       <c r="BF14" s="415" t="n">
-        <v>2175.911643434732</v>
+        <v>1915.790957739362</v>
       </c>
       <c r="BG14" s="416" t="n">
-        <v>321.7129035306248</v>
+        <v>312.4098222630497</v>
       </c>
       <c r="BH14" s="417" t="n">
-        <v>353.4360612834363</v>
+        <v>333.2048566526532</v>
       </c>
       <c r="BI14" s="417" t="n">
-        <v>388.4849113107987</v>
+        <v>355.4019248871028</v>
       </c>
       <c r="BJ14" s="417" t="n">
-        <v>421.1306995175711</v>
+        <v>377.5992482782462</v>
       </c>
       <c r="BK14" s="418" t="n">
-        <v>455.4315438154514</v>
+        <v>400.9867018927469</v>
       </c>
       <c r="BL14" s="417" t="n">
-        <v>321.7129035306248</v>
+        <v>312.4098222630497</v>
       </c>
       <c r="BM14" s="417" t="n">
-        <v>353.4360612834363</v>
+        <v>333.2048566526532</v>
       </c>
       <c r="BN14" s="417" t="n">
-        <v>388.4849113107987</v>
+        <v>355.4019248871028</v>
       </c>
       <c r="BO14" s="417" t="n">
-        <v>421.1306995175711</v>
+        <v>377.5992482782462</v>
       </c>
       <c r="BP14" s="418" t="n">
-        <v>455.4315438154514</v>
+        <v>400.9867018927469</v>
       </c>
       <c r="BR14" s="111" t="inlineStr">
         <is>
@@ -4001,64 +4001,64 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>1388.182490247327</v>
+        <v>1348.039945825678</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>1564.688323821328</v>
+        <v>1475.123242240022</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>1772.118689494749</v>
+        <v>1621.206834648398</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>1959.99479451594</v>
+        <v>1757.393991666511</v>
       </c>
       <c r="BW14" s="421" t="n">
-        <v>2162.621084936832</v>
+        <v>1904.089227170288</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>320.6687990267247</v>
+        <v>311.3959104836098</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>352.2890007084519</v>
+        <v>332.1234555271661</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>387.2241012132336</v>
+        <v>354.2484841161863</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>419.7639390213697</v>
+        <v>376.3737671235042</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>453.9534616845575</v>
+        <v>399.6853179924828</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>320.6687990267247</v>
+        <v>311.3959104836098</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>352.2890007084519</v>
+        <v>332.1234555271661</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>387.2241012132336</v>
+        <v>354.2484841161863</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>419.7639390213697</v>
+        <v>376.3737671235042</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>453.9534616845575</v>
+        <v>399.6853179924828</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>1.044104503900144</v>
+        <v>1.013911779439923</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>1.14706057498438</v>
+        <v>1.081401125487048</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>1.260810097565127</v>
+        <v>1.153440770916518</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>1.366760496201437</v>
+        <v>1.225481154741999</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>1.478082130893938</v>
+        <v>1.301383900264057</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4233,49 +4233,49 @@
         </is>
       </c>
       <c r="BB15" s="439" t="n">
-        <v>112766.8546674602</v>
+        <v>109948.0862169242</v>
       </c>
       <c r="BC15" s="440" t="n">
-        <v>125841.7250921808</v>
+        <v>119847.6789439574</v>
       </c>
       <c r="BD15" s="440" t="n">
-        <v>140720.2846474345</v>
+        <v>131007.5174004118</v>
       </c>
       <c r="BE15" s="440" t="n">
-        <v>156892.5933729929</v>
+        <v>143209.1921251547</v>
       </c>
       <c r="BF15" s="441" t="n">
-        <v>166185.0199788024</v>
+        <v>148974.4679240779</v>
       </c>
       <c r="BG15" s="442" t="n">
-        <v>710.3905683925639</v>
+        <v>692.6333424093773</v>
       </c>
       <c r="BH15" s="443" t="n">
-        <v>840.391685889968</v>
+        <v>800.3624623226825</v>
       </c>
       <c r="BI15" s="443" t="n">
-        <v>932.3153456690918</v>
+        <v>867.9652629784621</v>
       </c>
       <c r="BJ15" s="443" t="n">
-        <v>1044.371866423584</v>
+        <v>953.2868827860611</v>
       </c>
       <c r="BK15" s="444" t="n">
-        <v>1091.534200601508</v>
+        <v>978.4920853653659</v>
       </c>
       <c r="BL15" s="443" t="n">
-        <v>710.3905683925639</v>
+        <v>692.6333424093773</v>
       </c>
       <c r="BM15" s="443" t="n">
-        <v>840.391685889968</v>
+        <v>800.3624623226825</v>
       </c>
       <c r="BN15" s="443" t="n">
-        <v>932.3153456690918</v>
+        <v>867.9652629784621</v>
       </c>
       <c r="BO15" s="443" t="n">
-        <v>1044.371866423584</v>
+        <v>953.2868827860611</v>
       </c>
       <c r="BP15" s="444" t="n">
-        <v>1091.534200601508</v>
+        <v>978.4920853653659</v>
       </c>
       <c r="BR15" s="155" t="inlineStr">
         <is>
@@ -4283,49 +4283,49 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>112429.3987802451</v>
+        <v>109619.4454564302</v>
       </c>
       <c r="BT15" s="440" t="n">
-        <v>125496.1344681095</v>
+        <v>119519.3091546325</v>
       </c>
       <c r="BU15" s="440" t="n">
-        <v>140353.9569409507</v>
+        <v>130667.1358888182</v>
       </c>
       <c r="BV15" s="440" t="n">
-        <v>156512.0435810811</v>
+        <v>142862.3916374782</v>
       </c>
       <c r="BW15" s="441" t="n">
-        <v>165809.8916817211</v>
+        <v>148638.7894184242</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>712.0337954935408</v>
+        <v>694.2379008963784</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>842.3216510005188</v>
+        <v>802.2055997203179</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>934.4971416336789</v>
+        <v>870.0008724722524</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>1046.899489790889</v>
+        <v>955.5978025301367</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>1094.111246718037</v>
+        <v>980.8062085549263</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>712.0337954935408</v>
+        <v>694.2379008963784</v>
       </c>
       <c r="CD15" s="443" t="n">
-        <v>842.3216510005188</v>
+        <v>802.2055997203179</v>
       </c>
       <c r="CE15" s="443" t="n">
-        <v>934.4971416336789</v>
+        <v>870.0008724722524</v>
       </c>
       <c r="CF15" s="443" t="n">
-        <v>1046.899489790889</v>
+        <v>955.5978025301367</v>
       </c>
       <c r="CG15" s="444" t="n">
-        <v>1094.111246718037</v>
+        <v>980.8062085549263</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="BB29" s="391" t="n">
-        <v>21.09561146293518</v>
+        <v>21.65292007098677</v>
       </c>
       <c r="BC29" s="375" t="n">
-        <v>2.57706793923193</v>
+        <v>2.723505556116789</v>
       </c>
       <c r="BD29" s="375" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="BG29" s="386" t="n">
-        <v>0.2995295734807621</v>
+        <v>0.3074426131174727</v>
       </c>
       <c r="BH29" s="372" t="n">
-        <v>0.04473398905172605</v>
+        <v>0.04727592388035945</v>
       </c>
       <c r="BI29" s="372" t="n">
         <v>0</v>
@@ -7316,10 +7316,10 @@
         <v>0</v>
       </c>
       <c r="BL29" s="388" t="n">
-        <v>0.2995295734807621</v>
+        <v>0.3074426131174727</v>
       </c>
       <c r="BM29" s="389" t="n">
-        <v>0.04473398905172605</v>
+        <v>0.04727592388035945</v>
       </c>
       <c r="BN29" s="389" t="n">
         <v>0</v>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>21.08304189588392</v>
+        <v>21.64001843828623</v>
       </c>
       <c r="BT29" s="375" t="n">
-        <v>2.57553242421191</v>
+        <v>2.721882787999247</v>
       </c>
       <c r="BU29" s="375" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3101013105104077</v>
       </c>
       <c r="BY29" s="372" t="n">
-        <v>0.04515711930786146</v>
+        <v>0.04772309781240928</v>
       </c>
       <c r="BZ29" s="372" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3101013105104077</v>
       </c>
       <c r="CD29" s="389" t="n">
-        <v>0.04515711930786146</v>
+        <v>0.04772309781240928</v>
       </c>
       <c r="CE29" s="389" t="n">
         <v>0</v>
@@ -7381,10 +7381,10 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-0.002590267133255164</v>
+        <v>-0.002658697392935006</v>
       </c>
       <c r="CX29" s="92" t="n">
-        <v>-0.0004231302561354122</v>
+        <v>-0.0004471739320498352</v>
       </c>
       <c r="CY29" s="92" t="n">
         <v>0</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="BB30" s="391" t="n">
-        <v>158.9298921825861</v>
+        <v>163.7061332432859</v>
       </c>
       <c r="BC30" s="375" t="n">
-        <v>22.90282108124559</v>
+        <v>24.43885241209066</v>
       </c>
       <c r="BD30" s="375" t="n">
         <v>0</v>
@@ -7583,10 +7583,10 @@
         <v>0</v>
       </c>
       <c r="BG30" s="386" t="n">
-        <v>6.541805167456871</v>
+        <v>6.738402786839948</v>
       </c>
       <c r="BH30" s="372" t="n">
-        <v>1.054188806411513</v>
+        <v>1.12489044746831</v>
       </c>
       <c r="BI30" s="372" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>0</v>
       </c>
       <c r="BL30" s="386" t="n">
-        <v>6.541805167456871</v>
+        <v>6.738402786839948</v>
       </c>
       <c r="BM30" s="372" t="n">
-        <v>1.054188806411513</v>
+        <v>1.12489044746831</v>
       </c>
       <c r="BN30" s="372" t="n">
         <v>0</v>
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="BS30" s="391" t="n">
-        <v>158.7231850621592</v>
+        <v>163.4932140565034</v>
       </c>
       <c r="BT30" s="375" t="n">
-        <v>22.87303325385615</v>
+        <v>24.40706679429865</v>
       </c>
       <c r="BU30" s="375" t="n">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>0</v>
       </c>
       <c r="BX30" s="386" t="n">
-        <v>6.561303795942799</v>
+        <v>6.758487397916835</v>
       </c>
       <c r="BY30" s="372" t="n">
-        <v>1.057076830950801</v>
+        <v>1.127972164136653</v>
       </c>
       <c r="BZ30" s="372" t="n">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="CC30" s="386" t="n">
-        <v>6.561303795942799</v>
+        <v>6.758487397916835</v>
       </c>
       <c r="CD30" s="372" t="n">
-        <v>1.057076830950801</v>
+        <v>1.127972164136653</v>
       </c>
       <c r="CE30" s="372" t="n">
         <v>0</v>
@@ -7663,10 +7663,10 @@
         <v>0</v>
       </c>
       <c r="CW30" s="102" t="n">
-        <v>-0.01949862848592865</v>
+        <v>-0.02008461107688753</v>
       </c>
       <c r="CX30" s="103" t="n">
-        <v>-0.002888024539288159</v>
+        <v>-0.003081716668343226</v>
       </c>
       <c r="CY30" s="103" t="n">
         <v>0</v>
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="BB33" s="439" t="n">
-        <v>180.0255036455213</v>
+        <v>185.3590533142727</v>
       </c>
       <c r="BC33" s="440" t="n">
-        <v>25.47988902047752</v>
+        <v>27.16235796820744</v>
       </c>
       <c r="BD33" s="440" t="n">
         <v>0</v>
@@ -8429,10 +8429,10 @@
         <v>0</v>
       </c>
       <c r="BG33" s="442" t="n">
-        <v>1.13409583194487</v>
+        <v>1.167695273836793</v>
       </c>
       <c r="BH33" s="443" t="n">
-        <v>0.1701588791358589</v>
+        <v>0.1813946827964059</v>
       </c>
       <c r="BI33" s="443" t="n">
         <v>0</v>
@@ -8444,10 +8444,10 @@
         <v>0</v>
       </c>
       <c r="BL33" s="443" t="n">
-        <v>1.13409583194487</v>
+        <v>1.167695273836793</v>
       </c>
       <c r="BM33" s="443" t="n">
-        <v>0.1701588791358589</v>
+        <v>0.1813946827964059</v>
       </c>
       <c r="BN33" s="443" t="n">
         <v>0</v>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="BT33" s="440" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="BU33" s="440" t="n">
         <v>0</v>
@@ -8479,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>1.138742282919725</v>
+        <v>1.172479081409225</v>
       </c>
       <c r="BY33" s="443" t="n">
-        <v>0.1708090687286676</v>
+        <v>0.1820876929709564</v>
       </c>
       <c r="BZ33" s="443" t="n">
         <v>0</v>
@@ -8494,10 +8494,10 @@
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>1.138742282919725</v>
+        <v>1.172479081409225</v>
       </c>
       <c r="CD33" s="443" t="n">
-        <v>0.1708090687286676</v>
+        <v>0.1820876929709564</v>
       </c>
       <c r="CE33" s="443" t="n">
         <v>0</v>
@@ -9376,49 +9376,49 @@
         </is>
       </c>
       <c r="BB38" s="391" t="n">
-        <v>128.9348234157811</v>
+        <v>132.3410525783478</v>
       </c>
       <c r="BC38" s="375" t="n">
-        <v>71.00908550703852</v>
+        <v>75.04405916858781</v>
       </c>
       <c r="BD38" s="375" t="n">
-        <v>32.88217324194801</v>
+        <v>35.42778513914132</v>
       </c>
       <c r="BE38" s="375" t="n">
-        <v>14.73269668860666</v>
+        <v>16.19195831570391</v>
       </c>
       <c r="BF38" s="392" t="n">
-        <v>16.02712779187732</v>
+        <v>18.12360006971424</v>
       </c>
       <c r="BG38" s="386" t="n">
-        <v>1.830702690576236</v>
+        <v>1.879066605982714</v>
       </c>
       <c r="BH38" s="372" t="n">
-        <v>1.232609977132257</v>
+        <v>1.302650997336615</v>
       </c>
       <c r="BI38" s="372" t="n">
-        <v>0.6291632936095912</v>
+        <v>0.6778707057902047</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.3266949022040898</v>
+        <v>0.3590537666150697</v>
       </c>
       <c r="BK38" s="387" t="n">
-        <v>0.3521058758323221</v>
+        <v>0.3981640477725287</v>
       </c>
       <c r="BL38" s="388" t="n">
-        <v>1.830702690576236</v>
+        <v>1.879066605982714</v>
       </c>
       <c r="BM38" s="389" t="n">
-        <v>1.232609977132257</v>
+        <v>1.302650997336615</v>
       </c>
       <c r="BN38" s="389" t="n">
-        <v>0.6291632936095912</v>
+        <v>0.6778707057902047</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.3266949022040898</v>
+        <v>0.3590537666150697</v>
       </c>
       <c r="BP38" s="390" t="n">
-        <v>0.3521058758323221</v>
+        <v>0.3981640477725287</v>
       </c>
       <c r="BR38" s="83" t="inlineStr">
         <is>
@@ -9426,64 +9426,64 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>128.4033868530686</v>
+        <v>131.7955764050009</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.71498798436707</v>
+        <v>74.73325004134584</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>32.62212940287412</v>
+        <v>35.14760970214451</v>
       </c>
       <c r="BV38" s="375" t="n">
-        <v>14.47832342928954</v>
+        <v>15.91238959189533</v>
       </c>
       <c r="BW38" s="392" t="n">
-        <v>15.75040501531567</v>
+        <v>17.81067981365151</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>1.840019621548196</v>
+        <v>1.888629673732478</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>1.239854376999804</v>
+        <v>1.310307048226713</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6798493372454784</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3571808177187467</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3959272768541202</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>1.840019621548196</v>
+        <v>1.888629673732478</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>1.239854376999804</v>
+        <v>1.310307048226713</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6798493372454784</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3571808177187467</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3959272768541202</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-0.009316930971960291</v>
+        <v>-0.009563067749764009</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>-0.00724439986754799</v>
+        <v>-0.007656050890097355</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>-0.001836459774122279</v>
+        <v>-0.001978631455273661</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>0.00170415384382655</v>
+        <v>0.001872948896323001</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>0.001978029376756785</v>
+        <v>0.002236770918408515</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0.003528009884850775</v>
@@ -9658,49 +9658,49 @@
         </is>
       </c>
       <c r="BB39" s="391" t="n">
-        <v>126.1809430239881</v>
+        <v>129.9729961920392</v>
       </c>
       <c r="BC39" s="375" t="n">
-        <v>68.63775949785337</v>
+        <v>73.24111157809315</v>
       </c>
       <c r="BD39" s="375" t="n">
-        <v>77.47123527199035</v>
+        <v>85.2077707547443</v>
       </c>
       <c r="BE39" s="375" t="n">
-        <v>84.15760347840747</v>
+        <v>96.09210573091531</v>
       </c>
       <c r="BF39" s="392" t="n">
-        <v>92.18559925034108</v>
+        <v>107.7473085430547</v>
       </c>
       <c r="BG39" s="386" t="n">
-        <v>5.193806739392923</v>
+        <v>5.349893631980306</v>
       </c>
       <c r="BH39" s="372" t="n">
-        <v>3.159312012398926</v>
+        <v>3.371198671153544</v>
       </c>
       <c r="BI39" s="372" t="n">
-        <v>3.547432787225304</v>
+        <v>3.901691235986298</v>
       </c>
       <c r="BJ39" s="372" t="n">
-        <v>4.001926052058736</v>
+        <v>4.569444535340154</v>
       </c>
       <c r="BK39" s="387" t="n">
-        <v>4.31295030178016</v>
+        <v>5.041012811933838</v>
       </c>
       <c r="BL39" s="386" t="n">
-        <v>5.193806739392923</v>
+        <v>5.349893631980306</v>
       </c>
       <c r="BM39" s="372" t="n">
-        <v>3.159312012398926</v>
+        <v>3.371198671153544</v>
       </c>
       <c r="BN39" s="372" t="n">
-        <v>3.547432787225304</v>
+        <v>3.901691235986298</v>
       </c>
       <c r="BO39" s="372" t="n">
-        <v>4.001926052058736</v>
+        <v>4.569444535340154</v>
       </c>
       <c r="BP39" s="387" t="n">
-        <v>4.31295030178016</v>
+        <v>5.041012811933838</v>
       </c>
       <c r="BR39" s="101" t="inlineStr">
         <is>
@@ -9708,64 +9708,64 @@
         </is>
       </c>
       <c r="BS39" s="391" t="n">
-        <v>124.4753800840562</v>
+        <v>128.216176816748</v>
       </c>
       <c r="BT39" s="375" t="n">
-        <v>66.92868720343631</v>
+        <v>71.41741634785559</v>
       </c>
       <c r="BU39" s="375" t="n">
-        <v>75.5422104497019</v>
+        <v>83.08610709131239</v>
       </c>
       <c r="BV39" s="375" t="n">
-        <v>82.06208885902393</v>
+        <v>93.69942338203943</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>89.89018846223225</v>
+        <v>105.0644129885356</v>
       </c>
       <c r="BX39" s="386" t="n">
-        <v>5.14556700413425</v>
+        <v>5.300204171933326</v>
       </c>
       <c r="BY39" s="372" t="n">
-        <v>3.093108106104748</v>
+        <v>3.300554644843954</v>
       </c>
       <c r="BZ39" s="372" t="n">
-        <v>3.473079703178348</v>
+        <v>3.819913005419322</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>3.918512959555194</v>
+        <v>4.474202520680724</v>
       </c>
       <c r="CB39" s="387" t="n">
-        <v>4.220471598372009</v>
+        <v>4.932922920770681</v>
       </c>
       <c r="CC39" s="386" t="n">
-        <v>5.14556700413425</v>
+        <v>5.300204171933326</v>
       </c>
       <c r="CD39" s="372" t="n">
-        <v>3.093108106104748</v>
+        <v>3.300554644843954</v>
       </c>
       <c r="CE39" s="372" t="n">
-        <v>3.473079703178348</v>
+        <v>3.819913005419322</v>
       </c>
       <c r="CF39" s="372" t="n">
-        <v>3.918512959555194</v>
+        <v>4.474202520680724</v>
       </c>
       <c r="CG39" s="387" t="n">
-        <v>4.220471598372009</v>
+        <v>4.932922920770681</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.0482397352586732</v>
+        <v>0.04968946004697994</v>
       </c>
       <c r="CX39" s="103" t="n">
-        <v>0.0662039062941786</v>
+        <v>0.07064402630958933</v>
       </c>
       <c r="CY39" s="103" t="n">
-        <v>0.07435308404695595</v>
+        <v>0.08177823056697608</v>
       </c>
       <c r="CZ39" s="103" t="n">
-        <v>0.0834130925035419</v>
+        <v>0.09524201465942994</v>
       </c>
       <c r="DA39" s="104" t="n">
-        <v>0.09247870340815112</v>
+        <v>0.1080898911631571</v>
       </c>
       <c r="DC39" s="396" t="n">
         <v>0.01223209394752628</v>
@@ -9940,49 +9940,49 @@
         </is>
       </c>
       <c r="BB40" s="391" t="n">
-        <v>51.96539694362117</v>
+        <v>53.27807584018875</v>
       </c>
       <c r="BC40" s="375" t="n">
-        <v>76.16858652246991</v>
+        <v>80.08240875628728</v>
       </c>
       <c r="BD40" s="375" t="n">
-        <v>111.1588074867999</v>
+        <v>119.950827239901</v>
       </c>
       <c r="BE40" s="375" t="n">
-        <v>190.9170385954531</v>
+        <v>211.0597523381235</v>
       </c>
       <c r="BF40" s="392" t="n">
-        <v>343.9608887271743</v>
+        <v>384.6542147030659</v>
       </c>
       <c r="BG40" s="386" t="n">
-        <v>0.870819981956345</v>
+        <v>0.8928174471977565</v>
       </c>
       <c r="BH40" s="372" t="n">
-        <v>1.15488825604331</v>
+        <v>1.214230663989182</v>
       </c>
       <c r="BI40" s="372" t="n">
-        <v>1.538643119344203</v>
+        <v>1.660340904738794</v>
       </c>
       <c r="BJ40" s="372" t="n">
-        <v>2.40393490150404</v>
+        <v>2.657562199168209</v>
       </c>
       <c r="BK40" s="387" t="n">
-        <v>4.268602478686694</v>
+        <v>4.773612315036071</v>
       </c>
       <c r="BL40" s="386" t="n">
-        <v>0.870819981956345</v>
+        <v>0.8928174471977565</v>
       </c>
       <c r="BM40" s="372" t="n">
-        <v>1.15488825604331</v>
+        <v>1.214230663989182</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>1.538643119344203</v>
+        <v>1.660340904738794</v>
       </c>
       <c r="BO40" s="372" t="n">
-        <v>2.40393490150404</v>
+        <v>2.657562199168209</v>
       </c>
       <c r="BP40" s="387" t="n">
-        <v>4.268602478686694</v>
+        <v>4.773612315036071</v>
       </c>
       <c r="BR40" s="111" t="inlineStr">
         <is>
@@ -9990,64 +9990,64 @@
         </is>
       </c>
       <c r="BS40" s="391" t="n">
-        <v>51.28127016427074</v>
+        <v>52.57666758434341</v>
       </c>
       <c r="BT40" s="375" t="n">
-        <v>75.3469277074357</v>
+        <v>79.21853008808637</v>
       </c>
       <c r="BU40" s="375" t="n">
-        <v>110.2409153392682</v>
+        <v>118.9603351241367</v>
       </c>
       <c r="BV40" s="375" t="n">
-        <v>189.8957709512762</v>
+        <v>209.9307357891729</v>
       </c>
       <c r="BW40" s="392" t="n">
-        <v>342.7936332465233</v>
+        <v>383.3488635570995</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.8604898787695601</v>
+        <v>0.8822263990504747</v>
       </c>
       <c r="BY40" s="372" t="n">
-        <v>1.143804330213192</v>
+        <v>1.202577205267193</v>
       </c>
       <c r="BZ40" s="372" t="n">
-        <v>1.527610520250207</v>
+        <v>1.648435690767439</v>
       </c>
       <c r="CA40" s="372" t="n">
-        <v>2.393468402265413</v>
+        <v>2.645991431292258</v>
       </c>
       <c r="CB40" s="387" t="n">
-        <v>4.258292614547694</v>
+        <v>4.762082711455975</v>
       </c>
       <c r="CC40" s="386" t="n">
-        <v>0.8604898787695601</v>
+        <v>0.8822263990504747</v>
       </c>
       <c r="CD40" s="372" t="n">
-        <v>1.143804330213192</v>
+        <v>1.202577205267193</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>1.527610520250207</v>
+        <v>1.648435690767439</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>2.393468402265413</v>
+        <v>2.645991431292258</v>
       </c>
       <c r="CG40" s="387" t="n">
-        <v>4.258292614547694</v>
+        <v>4.762082711455975</v>
       </c>
       <c r="CW40" s="102" t="n">
-        <v>0.01033010318678496</v>
+        <v>0.01059104814728173</v>
       </c>
       <c r="CX40" s="103" t="n">
-        <v>0.01108392583011741</v>
+        <v>0.01165345872198897</v>
       </c>
       <c r="CY40" s="103" t="n">
-        <v>0.01103259909399612</v>
+        <v>0.01190521397135513</v>
       </c>
       <c r="CZ40" s="103" t="n">
-        <v>0.01046649923862697</v>
+        <v>0.01157076787595024</v>
       </c>
       <c r="DA40" s="104" t="n">
-        <v>0.01030986413899981</v>
+        <v>0.01152960358009647</v>
       </c>
       <c r="DC40" s="396" t="n">
         <v>0.01292745161799779</v>
@@ -10222,49 +10222,49 @@
         </is>
       </c>
       <c r="BB41" s="419" t="n">
-        <v>205.9361072516242</v>
+        <v>207.0369461870185</v>
       </c>
       <c r="BC41" s="420" t="n">
-        <v>262.1317542878902</v>
+        <v>265.0408734935592</v>
       </c>
       <c r="BD41" s="420" t="n">
-        <v>321.7147627279968</v>
+        <v>327.2949243971454</v>
       </c>
       <c r="BE41" s="420" t="n">
-        <v>381.2459079147778</v>
+        <v>389.5462384134134</v>
       </c>
       <c r="BF41" s="421" t="n">
-        <v>447.9607220782643</v>
+        <v>459.5921912655211</v>
       </c>
       <c r="BG41" s="416" t="n">
-        <v>47.43441993813283</v>
+        <v>47.6879823514591</v>
       </c>
       <c r="BH41" s="417" t="n">
-        <v>58.8493713326904</v>
+        <v>59.50247738941581</v>
       </c>
       <c r="BI41" s="417" t="n">
-        <v>70.09572251124145</v>
+        <v>71.31153698183574</v>
       </c>
       <c r="BJ41" s="417" t="n">
-        <v>81.41536073206443</v>
+        <v>83.18790277831987</v>
       </c>
       <c r="BK41" s="418" t="n">
-        <v>93.76090423540577</v>
+        <v>96.19544149466334</v>
       </c>
       <c r="BL41" s="417" t="n">
-        <v>47.43441993813283</v>
+        <v>47.6879823514591</v>
       </c>
       <c r="BM41" s="417" t="n">
-        <v>58.8493713326904</v>
+        <v>59.50247738941581</v>
       </c>
       <c r="BN41" s="417" t="n">
-        <v>70.09572251124145</v>
+        <v>71.31153698183574</v>
       </c>
       <c r="BO41" s="417" t="n">
-        <v>81.41536073206443</v>
+        <v>83.18790277831987</v>
       </c>
       <c r="BP41" s="418" t="n">
-        <v>93.76090423540577</v>
+        <v>96.19544149466334</v>
       </c>
       <c r="BR41" s="111" t="inlineStr">
         <is>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>204.6782409735905</v>
+        <v>205.7723559391435</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>260.5306426687525</v>
+        <v>263.4219928537459</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>319.7497156239126</v>
+        <v>325.2957934343184</v>
       </c>
       <c r="BV41" s="420" t="n">
-        <v>378.9172421086479</v>
+        <v>387.1668738445939</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>445.2245594222547</v>
+        <v>456.7849831136539</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>47.2804736992541</v>
+        <v>47.53321318737323</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>58.658378389092</v>
+        <v>59.30936481997549</v>
       </c>
       <c r="BZ41" s="417" t="n">
-        <v>69.86823003427472</v>
+        <v>71.08009863434312</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>81.15113088855017</v>
+        <v>82.91792023036146</v>
       </c>
       <c r="CB41" s="418" t="n">
-        <v>93.4566075326219</v>
+        <v>95.88324361316492</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>47.2804736992541</v>
+        <v>47.53321318737323</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>58.658378389092</v>
+        <v>59.30936481997549</v>
       </c>
       <c r="CE41" s="417" t="n">
-        <v>69.86823003427472</v>
+        <v>71.08009863434312</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>81.15113088855017</v>
+        <v>82.91792023036146</v>
       </c>
       <c r="CG41" s="418" t="n">
-        <v>93.4566075326219</v>
+        <v>95.88324361316492</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.1539462388787314</v>
+        <v>0.1547691640858702</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.1909929435984026</v>
+        <v>0.1931125694403235</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.2274924769667308</v>
+        <v>0.2314383474926274</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.2642298435142578</v>
+        <v>0.2699825479584064</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.3042967027838728</v>
+        <v>0.3121978814984203</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10504,49 +10504,49 @@
         </is>
       </c>
       <c r="BB42" s="439" t="n">
-        <v>513.0172706350146</v>
+        <v>522.6290707975943</v>
       </c>
       <c r="BC42" s="440" t="n">
-        <v>477.947185815252</v>
+        <v>493.4084529965274</v>
       </c>
       <c r="BD42" s="440" t="n">
-        <v>543.226978728735</v>
+        <v>567.881307530932</v>
       </c>
       <c r="BE42" s="440" t="n">
-        <v>671.0532466772451</v>
+        <v>712.8900547981561</v>
       </c>
       <c r="BF42" s="441" t="n">
-        <v>900.134337847657</v>
+        <v>970.1173145813559</v>
       </c>
       <c r="BG42" s="442" t="n">
-        <v>3.231824028047248</v>
+        <v>3.292374907123429</v>
       </c>
       <c r="BH42" s="443" t="n">
-        <v>3.191809719386966</v>
+        <v>3.295062598215108</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>3.599046503630636</v>
+        <v>3.762389046157811</v>
       </c>
       <c r="BJ42" s="443" t="n">
-        <v>4.466935733771606</v>
+        <v>4.745426798538228</v>
       </c>
       <c r="BK42" s="444" t="n">
-        <v>5.912250183691859</v>
+        <v>6.371911424966649</v>
       </c>
       <c r="BL42" s="443" t="n">
-        <v>3.231824028047248</v>
+        <v>3.292374907123429</v>
       </c>
       <c r="BM42" s="443" t="n">
-        <v>3.191809719386966</v>
+        <v>3.295062598215108</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>3.599046503630636</v>
+        <v>3.762389046157811</v>
       </c>
       <c r="BO42" s="443" t="n">
-        <v>4.466935733771606</v>
+        <v>4.745426798538228</v>
       </c>
       <c r="BP42" s="444" t="n">
-        <v>5.912250183691859</v>
+        <v>6.371911424966649</v>
       </c>
       <c r="BR42" s="155" t="inlineStr">
         <is>
@@ -10554,49 +10554,49 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>508.838278074986</v>
+        <v>518.3607767452357</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>473.5212455639916</v>
+        <v>488.7911893310337</v>
       </c>
       <c r="BU42" s="440" t="n">
-        <v>538.1549708157568</v>
+        <v>562.489845351912</v>
       </c>
       <c r="BV42" s="440" t="n">
-        <v>665.3534253482376</v>
+        <v>706.7094226077015</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>893.6587861463258</v>
+        <v>963.0089394729405</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>3.22255614955571</v>
+        <v>3.282863693172597</v>
       </c>
       <c r="BY42" s="443" t="n">
-        <v>3.178242892004288</v>
+        <v>3.280733732053298</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>3.583114384120006</v>
+        <v>3.745139532478443</v>
       </c>
       <c r="CA42" s="443" t="n">
-        <v>4.450508379994656</v>
+        <v>4.727136117005175</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>5.896886601481767</v>
+        <v>6.354499726649944</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>3.22255614955571</v>
+        <v>3.282863693172597</v>
       </c>
       <c r="CD42" s="443" t="n">
-        <v>3.178242892004288</v>
+        <v>3.280733732053298</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>3.583114384120006</v>
+        <v>3.745139532478443</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>4.450508379994656</v>
+        <v>4.727136117005175</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>5.896886601481767</v>
+        <v>6.354499726649944</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11384,49 +11384,49 @@
         </is>
       </c>
       <c r="BB47" s="391" t="n">
-        <v>28685.52470761239</v>
+        <v>27938.06768613968</v>
       </c>
       <c r="BC47" s="375" t="n">
-        <v>28292.10892111783</v>
+        <v>26869.15068978964</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>28353.20991412726</v>
+        <v>26334.40497080472</v>
       </c>
       <c r="BE47" s="375" t="n">
-        <v>26295.34737692758</v>
+        <v>23953.08876025328</v>
       </c>
       <c r="BF47" s="392" t="n">
-        <v>26290.66972712829</v>
+        <v>23518.81633366923</v>
       </c>
       <c r="BG47" s="386" t="n">
-        <v>407.2962282150184</v>
+        <v>396.6833344749963</v>
       </c>
       <c r="BH47" s="372" t="n">
-        <v>491.1080811880852</v>
+        <v>466.4076854506448</v>
       </c>
       <c r="BI47" s="372" t="n">
-        <v>542.5066890414453</v>
+        <v>503.8791336803603</v>
       </c>
       <c r="BJ47" s="372" t="n">
-        <v>583.0946038800432</v>
+        <v>531.1554398638004</v>
       </c>
       <c r="BK47" s="387" t="n">
-        <v>577.5894103234391</v>
+        <v>516.6935418024846</v>
       </c>
       <c r="BL47" s="388" t="n">
-        <v>407.2962282150184</v>
+        <v>396.6833344749963</v>
       </c>
       <c r="BM47" s="389" t="n">
-        <v>491.1080811880852</v>
+        <v>466.4076854506448</v>
       </c>
       <c r="BN47" s="389" t="n">
-        <v>542.5066890414453</v>
+        <v>503.8791336803603</v>
       </c>
       <c r="BO47" s="389" t="n">
-        <v>583.0946038800432</v>
+        <v>531.1554398638004</v>
       </c>
       <c r="BP47" s="390" t="n">
-        <v>577.5894103234391</v>
+        <v>516.6935418024846</v>
       </c>
       <c r="BR47" s="83" t="inlineStr">
         <is>
@@ -11434,49 +11434,49 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>28471.69447884347</v>
+        <v>27729.83951732739</v>
       </c>
       <c r="BT47" s="375" t="n">
-        <v>28075.36223424783</v>
+        <v>26663.33412294043</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>28127.48764370189</v>
+        <v>26124.75483300452</v>
       </c>
       <c r="BV47" s="375" t="n">
-        <v>26068.54881481979</v>
+        <v>23746.46832258388</v>
       </c>
       <c r="BW47" s="392" t="n">
-        <v>26060.96276865009</v>
+        <v>23313.29531390669</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>407.9991796458245</v>
+        <v>397.3684033167352</v>
       </c>
       <c r="BY47" s="372" t="n">
-        <v>492.2486978246035</v>
+        <v>467.4914393684716</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>544.061288804637</v>
+        <v>505.3230478383018</v>
       </c>
       <c r="CA47" s="372" t="n">
-        <v>585.1531932803401</v>
+        <v>533.0301224973061</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>579.3291513375884</v>
+        <v>518.2491417905404</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>407.9991796458245</v>
+        <v>397.3684033167353</v>
       </c>
       <c r="CD47" s="389" t="n">
-        <v>492.2486978246035</v>
+        <v>467.4914393684716</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>544.061288804637</v>
+        <v>505.3230478383018</v>
       </c>
       <c r="CF47" s="389" t="n">
-        <v>585.15319328034</v>
+        <v>533.0301224973061</v>
       </c>
       <c r="CG47" s="390" t="n">
-        <v>579.3291513375883</v>
+        <v>518.2491417905404</v>
       </c>
     </row>
     <row r="48">
@@ -11636,49 +11636,49 @@
         </is>
       </c>
       <c r="BB48" s="391" t="n">
-        <v>26700.95711061384</v>
+        <v>26018.36828377417</v>
       </c>
       <c r="BC48" s="375" t="n">
-        <v>28078.53548448032</v>
+        <v>26721.12541114689</v>
       </c>
       <c r="BD48" s="375" t="n">
-        <v>30382.03373599577</v>
+        <v>28298.3383189849</v>
       </c>
       <c r="BE48" s="375" t="n">
-        <v>33005.589973156</v>
+        <v>30163.07493566691</v>
       </c>
       <c r="BF48" s="392" t="n">
-        <v>35505.09800415902</v>
+        <v>31870.57417263072</v>
       </c>
       <c r="BG48" s="386" t="n">
-        <v>1099.053531110346</v>
+        <v>1070.957097812965</v>
       </c>
       <c r="BH48" s="372" t="n">
-        <v>1292.42060194961</v>
+        <v>1229.940678627408</v>
       </c>
       <c r="BI48" s="372" t="n">
-        <v>1391.203099308574</v>
+        <v>1295.790015795138</v>
       </c>
       <c r="BJ48" s="372" t="n">
-        <v>1569.506793418033</v>
+        <v>1434.337367106898</v>
       </c>
       <c r="BK48" s="387" t="n">
-        <v>1661.124127814412</v>
+        <v>1491.081075716347</v>
       </c>
       <c r="BL48" s="386" t="n">
-        <v>1099.053531110346</v>
+        <v>1070.957097812965</v>
       </c>
       <c r="BM48" s="372" t="n">
-        <v>1292.42060194961</v>
+        <v>1229.940678627408</v>
       </c>
       <c r="BN48" s="372" t="n">
-        <v>1391.203099308574</v>
+        <v>1295.790015795138</v>
       </c>
       <c r="BO48" s="372" t="n">
-        <v>1569.506793418033</v>
+        <v>1434.337367106898</v>
       </c>
       <c r="BP48" s="387" t="n">
-        <v>1661.124127814412</v>
+        <v>1491.081075716347</v>
       </c>
       <c r="BR48" s="101" t="inlineStr">
         <is>
@@ -11686,49 +11686,49 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>26612.99924137126</v>
+        <v>25932.60428516893</v>
       </c>
       <c r="BT48" s="375" t="n">
-        <v>27990.76998241881</v>
+        <v>26637.43457725192</v>
       </c>
       <c r="BU48" s="375" t="n">
-        <v>30287.14377372601</v>
+        <v>28209.67130215793</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>32903.13302468607</v>
+        <v>30069.02264767003</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>35414.66909960086</v>
+        <v>31788.84189329389</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>1100.128962731242</v>
+        <v>1072.002775576401</v>
       </c>
       <c r="BY48" s="372" t="n">
-        <v>1293.592944167114</v>
+        <v>1231.048572136083</v>
       </c>
       <c r="BZ48" s="372" t="n">
-        <v>1392.462090817563</v>
+        <v>1296.949563027303</v>
       </c>
       <c r="CA48" s="372" t="n">
-        <v>1571.143934548078</v>
+        <v>1435.813498830977</v>
       </c>
       <c r="CB48" s="387" t="n">
-        <v>1662.768847830454</v>
+        <v>1492.53112771206</v>
       </c>
       <c r="CC48" s="386" t="n">
-        <v>1100.128962731241</v>
+        <v>1072.002775576401</v>
       </c>
       <c r="CD48" s="372" t="n">
-        <v>1293.592944167114</v>
+        <v>1231.048572136083</v>
       </c>
       <c r="CE48" s="372" t="n">
-        <v>1392.462090817563</v>
+        <v>1296.949563027303</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>1571.143934548078</v>
+        <v>1435.813498830976</v>
       </c>
       <c r="CG48" s="387" t="n">
-        <v>1662.768847830453</v>
+        <v>1492.53112771206</v>
       </c>
     </row>
     <row r="49">
@@ -11888,49 +11888,49 @@
         </is>
       </c>
       <c r="BB49" s="391" t="n">
-        <v>56470.76584100079</v>
+        <v>55136.27699326861</v>
       </c>
       <c r="BC49" s="375" t="n">
-        <v>68138.07176776878</v>
+        <v>65028.74405198667</v>
       </c>
       <c r="BD49" s="375" t="n">
-        <v>80423.54382859949</v>
+        <v>74984.19040459984</v>
       </c>
       <c r="BE49" s="375" t="n">
-        <v>95909.42326451193</v>
+        <v>87648.17805052697</v>
       </c>
       <c r="BF49" s="392" t="n">
-        <v>102665.5142198498</v>
+        <v>92179.81158335443</v>
       </c>
       <c r="BG49" s="386" t="n">
-        <v>946.3195546081114</v>
+        <v>923.9566049790751</v>
       </c>
       <c r="BH49" s="372" t="n">
-        <v>1033.127467198279</v>
+        <v>985.9830179299793</v>
       </c>
       <c r="BI49" s="372" t="n">
-        <v>1113.210326224902</v>
+        <v>1037.919632588122</v>
       </c>
       <c r="BJ49" s="372" t="n">
-        <v>1207.645015158824</v>
+        <v>1103.623415798784</v>
       </c>
       <c r="BK49" s="387" t="n">
-        <v>1274.09331362119</v>
+        <v>1143.964285200118</v>
       </c>
       <c r="BL49" s="386" t="n">
-        <v>946.3195546081114</v>
+        <v>923.9566049790751</v>
       </c>
       <c r="BM49" s="372" t="n">
-        <v>1033.127467198279</v>
+        <v>985.9830179299793</v>
       </c>
       <c r="BN49" s="372" t="n">
-        <v>1113.210326224902</v>
+        <v>1037.919632588122</v>
       </c>
       <c r="BO49" s="372" t="n">
-        <v>1207.645015158824</v>
+        <v>1103.623415798784</v>
       </c>
       <c r="BP49" s="387" t="n">
-        <v>1274.09331362119</v>
+        <v>1143.964285200118</v>
       </c>
       <c r="BR49" s="111" t="inlineStr">
         <is>
@@ -11938,49 +11938,49 @@
         </is>
       </c>
       <c r="BS49" s="391" t="n">
-        <v>56440.48883384246</v>
+        <v>55106.68336140914</v>
       </c>
       <c r="BT49" s="375" t="n">
-        <v>68103.75309619487</v>
+        <v>64995.91535825973</v>
       </c>
       <c r="BU49" s="375" t="n">
-        <v>80385.61208921993</v>
+        <v>74948.69697092491</v>
       </c>
       <c r="BV49" s="375" t="n">
-        <v>95866.80313029894</v>
+        <v>87609.0492243209</v>
       </c>
       <c r="BW49" s="392" t="n">
-        <v>102620.0729552573</v>
+        <v>92138.78694041265</v>
       </c>
       <c r="BX49" s="386" t="n">
-        <v>947.0605786236081</v>
+        <v>924.6795785898768</v>
       </c>
       <c r="BY49" s="372" t="n">
-        <v>1033.849289750276</v>
+        <v>986.6707468367156</v>
       </c>
       <c r="BZ49" s="372" t="n">
-        <v>1113.90499912244</v>
+        <v>1038.565559978139</v>
       </c>
       <c r="CA49" s="372" t="n">
-        <v>1208.316346220492</v>
+        <v>1104.23465472925</v>
       </c>
       <c r="CB49" s="387" t="n">
-        <v>1274.779506932834</v>
+        <v>1144.577605557737</v>
       </c>
       <c r="CC49" s="386" t="n">
-        <v>947.060578623608</v>
+        <v>924.6795785898767</v>
       </c>
       <c r="CD49" s="372" t="n">
-        <v>1033.849289750276</v>
+        <v>986.6707468367156</v>
       </c>
       <c r="CE49" s="372" t="n">
-        <v>1113.90499912244</v>
+        <v>1038.565559978139</v>
       </c>
       <c r="CF49" s="372" t="n">
-        <v>1208.316346220492</v>
+        <v>1104.23465472925</v>
       </c>
       <c r="CG49" s="387" t="n">
-        <v>1274.779506932834</v>
+        <v>1144.577605557737</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" thickBot="1">
@@ -12140,49 +12140,49 @@
         </is>
       </c>
       <c r="BB50" s="419" t="n">
-        <v>1602.6497825137</v>
+        <v>1563.361377853649</v>
       </c>
       <c r="BC50" s="420" t="n">
-        <v>1836.435993649658</v>
+        <v>1749.229601998909</v>
       </c>
       <c r="BD50" s="420" t="n">
-        <v>2104.724147440693</v>
+        <v>1958.465013553312</v>
       </c>
       <c r="BE50" s="420" t="n">
-        <v>2353.286005074595</v>
+        <v>2157.74043350566</v>
       </c>
       <c r="BF50" s="421" t="n">
-        <v>2623.872365512996</v>
+        <v>2375.383149004883</v>
       </c>
       <c r="BG50" s="416" t="n">
-        <v>369.1473234687576</v>
+        <v>360.0978046145088</v>
       </c>
       <c r="BH50" s="417" t="n">
-        <v>412.2854326161267</v>
+        <v>392.707334042069</v>
       </c>
       <c r="BI50" s="417" t="n">
-        <v>458.5806338220402</v>
+        <v>426.7134618689385</v>
       </c>
       <c r="BJ50" s="417" t="n">
-        <v>502.5460602496356</v>
+        <v>460.7871510565661</v>
       </c>
       <c r="BK50" s="418" t="n">
-        <v>549.1924480508571</v>
+        <v>497.1821433874102</v>
       </c>
       <c r="BL50" s="417" t="n">
-        <v>369.1473234687576</v>
+        <v>360.0978046145088</v>
       </c>
       <c r="BM50" s="417" t="n">
-        <v>412.2854326161267</v>
+        <v>392.707334042069</v>
       </c>
       <c r="BN50" s="417" t="n">
-        <v>458.5806338220402</v>
+        <v>426.7134618689385</v>
       </c>
       <c r="BO50" s="417" t="n">
-        <v>502.5460602496356</v>
+        <v>460.7871510565661</v>
       </c>
       <c r="BP50" s="418" t="n">
-        <v>549.1924480508571</v>
+        <v>497.1821433874102</v>
       </c>
       <c r="BR50" s="111" t="inlineStr">
         <is>
@@ -12190,49 +12190,49 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>1592.860731220918</v>
+        <v>1553.812301764822</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>1825.218966490081</v>
+        <v>1738.545235093768</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>2091.868405118662</v>
+        <v>1946.502628082717</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>2338.912036624588</v>
+        <v>2144.560865511105</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>2607.845644359086</v>
+        <v>2360.874210283941</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>367.9492727259788</v>
+        <v>358.929123670983</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>410.9473790975439</v>
+        <v>391.4328203471416</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>457.0923312475084</v>
+        <v>425.3285827505294</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>500.9150699099199</v>
+        <v>459.2916873538657</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>547.4100692171794</v>
+        <v>495.5685616056477</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>367.9492727259787</v>
+        <v>358.9291236709831</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>410.9473790975439</v>
+        <v>391.4328203471416</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>457.0923312475084</v>
+        <v>425.3285827505294</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>500.9150699099199</v>
+        <v>459.2916873538656</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>547.4100692171793</v>
+        <v>495.5685616056477</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12392,49 +12392,49 @@
         </is>
       </c>
       <c r="BB51" s="439" t="n">
-        <v>113459.8974417407</v>
+        <v>110656.0743410361</v>
       </c>
       <c r="BC51" s="440" t="n">
-        <v>126345.1521670166</v>
+        <v>120368.2497549221</v>
       </c>
       <c r="BD51" s="440" t="n">
-        <v>141263.5116261632</v>
+        <v>131575.3987079428</v>
       </c>
       <c r="BE51" s="440" t="n">
-        <v>157563.6466196701</v>
+        <v>143922.0821799528</v>
       </c>
       <c r="BF51" s="441" t="n">
-        <v>167085.1543166501</v>
+        <v>149944.5852386593</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>714.756488252556</v>
+        <v>697.0934125903375</v>
       </c>
       <c r="BH51" s="443" t="n">
-        <v>843.753654488491</v>
+        <v>803.8389196036941</v>
       </c>
       <c r="BI51" s="443" t="n">
-        <v>935.9143921727223</v>
+        <v>871.7276520246199</v>
       </c>
       <c r="BJ51" s="443" t="n">
-        <v>1048.838802157356</v>
+        <v>958.0323095845995</v>
       </c>
       <c r="BK51" s="444" t="n">
-        <v>1097.4464507852</v>
+        <v>984.8639967903325</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>714.756488252556</v>
+        <v>697.0934125903375</v>
       </c>
       <c r="BM51" s="443" t="n">
-        <v>843.753654488491</v>
+        <v>803.8389196036941</v>
       </c>
       <c r="BN51" s="443" t="n">
-        <v>935.9143921727223</v>
+        <v>871.7276520246199</v>
       </c>
       <c r="BO51" s="443" t="n">
-        <v>1048.838802157356</v>
+        <v>958.0323095845995</v>
       </c>
       <c r="BP51" s="444" t="n">
-        <v>1097.4464507852</v>
+        <v>984.8639967903325</v>
       </c>
       <c r="BR51" s="155" t="inlineStr">
         <is>
@@ -12442,49 +12442,49 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>113118.0432852781</v>
+        <v>110322.9394656703</v>
       </c>
       <c r="BT51" s="440" t="n">
-        <v>125995.1042793516</v>
+        <v>120035.2292935459</v>
       </c>
       <c r="BU51" s="440" t="n">
-        <v>140892.1119117665</v>
+        <v>131229.6257341701</v>
       </c>
       <c r="BV51" s="440" t="n">
-        <v>157177.3970064294</v>
+        <v>143569.1010600859</v>
       </c>
       <c r="BW51" s="441" t="n">
-        <v>166703.5504678674</v>
+        <v>149601.7983578972</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>716.3950939260161</v>
+        <v>698.6932436709603</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>845.6707029612517</v>
+        <v>805.6684211453423</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>938.0802560177989</v>
+        <v>873.7460120047308</v>
       </c>
       <c r="CA51" s="417" t="n">
-        <v>1051.349998170884</v>
+        <v>960.3249386471419</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>1100.008133319518</v>
+        <v>987.1607082815765</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>716.3950939260161</v>
+        <v>698.6932436709603</v>
       </c>
       <c r="CD51" s="417" t="n">
-        <v>845.6707029612517</v>
+        <v>805.6684211453423</v>
       </c>
       <c r="CE51" s="417" t="n">
-        <v>938.0802560177989</v>
+        <v>873.7460120047308</v>
       </c>
       <c r="CF51" s="417" t="n">
-        <v>1051.349998170884</v>
+        <v>960.3249386471419</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>1100.008133319518</v>
+        <v>987.1607082815765</v>
       </c>
     </row>
     <row r="52">
@@ -13653,13 +13653,13 @@
         <v>4951</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>0.6454387887317973</v>
+        <v>0.6454387887317972</v>
       </c>
       <c r="CX58" s="92" t="n">
         <v>0.5738078228343186</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5642210685925357</v>
+        <v>0.5642210685925358</v>
       </c>
       <c r="CZ58" s="92" t="n">
         <v>0.5462383402166368</v>
@@ -13674,7 +13674,7 @@
         <v>0.009097557460024304</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.009932858034555738</v>
+        <v>0.009932858034555739</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.0112498614015952</v>
@@ -14271,7 +14271,7 @@
         <v>8129</v>
       </c>
       <c r="CW60" s="102" t="n">
-        <v>0.07866122670599515</v>
+        <v>0.07866122670599514</v>
       </c>
       <c r="CX60" s="103" t="n">
         <v>0.07924287032825833</v>
@@ -14535,7 +14535,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="CB61" s="213" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="CC61" s="212" t="n">
         <v>4.329022637876395</v>
@@ -14550,7 +14550,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="CG61" s="213" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="CI61" s="211" t="n">
         <v>0</v>
@@ -14580,19 +14580,19 @@
         <v>972</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.0124683621236049</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157616</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989036</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069173</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177136</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14889,19 +14889,19 @@
         <v>22134</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273312</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974732</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7444004017231202</v>
+        <v>0.7444004017231198</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908425</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675241</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -16585,7 +16585,7 @@
         <v>4.669278385810257</v>
       </c>
       <c r="CG70" s="213" t="n">
-        <v>4.763971351474489</v>
+        <v>4.76397135147449</v>
       </c>
       <c r="CW70" s="465" t="n"/>
       <c r="CX70" s="465" t="n"/>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>56692.45154007564</v>
+        <v>56692.45154007563</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>53152.45709114791</v>
+        <v>53152.45709114789</v>
       </c>
       <c r="DE96" s="375" t="n">
         <v>54365.6603069615</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>49985.42743288455</v>
+        <v>49985.42743288452</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47629.9399622732</v>
+        <v>47629.93996227319</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21317,16 +21317,16 @@
         <v>49357.38537421892</v>
       </c>
       <c r="DD97" s="375" t="n">
-        <v>48368.75020593862</v>
+        <v>48368.75020593861</v>
       </c>
       <c r="DE97" s="375" t="n">
-        <v>51410.76756020102</v>
+        <v>51410.76756020103</v>
       </c>
       <c r="DF97" s="375" t="n">
         <v>53321.8451024732</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>57463.98155283603</v>
+        <v>57463.98155283602</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21550,10 +21550,10 @@
         <v>149628.6636626866</v>
       </c>
       <c r="DF98" s="375" t="n">
-        <v>174895.0914295518</v>
+        <v>174895.0914295517</v>
       </c>
       <c r="DG98" s="392" t="n">
-        <v>192284.587741564</v>
+        <v>192284.5877415641</v>
       </c>
       <c r="DI98" s="368" t="n"/>
       <c r="DJ98" s="368" t="n"/>
@@ -21771,10 +21771,10 @@
         <v>8916.232863213503</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>9666.763954639384</v>
+        <v>9666.763954639382</v>
       </c>
       <c r="DE99" s="420" t="n">
-        <v>10532.06229950653</v>
+        <v>10532.06229950652</v>
       </c>
       <c r="DF99" s="420" t="n">
         <v>11358.94083284316</v>
@@ -21997,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>224374.2119641716</v>
+        <v>224374.2119641715</v>
       </c>
       <c r="DD100" s="440" t="n">
         <v>240079.7999555905</v>
@@ -22009,7 +22009,7 @@
         <v>289561.3047977526</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>309619.9738065998</v>
+        <v>309619.9738065999</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23138,13 +23138,13 @@
         <v>2366</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>0.6454387887317973</v>
+        <v>0.6454387887317972</v>
       </c>
       <c r="CX108" s="200" t="n">
         <v>0.5738078228343186</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5642210685925357</v>
+        <v>0.5642210685925358</v>
       </c>
       <c r="CZ108" s="200" t="n">
         <v>0.5462383402166368</v>
@@ -23728,7 +23728,7 @@
         <v>7686</v>
       </c>
       <c r="CW110" s="197" t="n">
-        <v>0.07866122670599515</v>
+        <v>0.07866122670599514</v>
       </c>
       <c r="CX110" s="190" t="n">
         <v>0.07924287032825833</v>
@@ -23972,7 +23972,7 @@
         <v>22.69215417114072</v>
       </c>
       <c r="BZ111" s="212" t="n">
-        <v>17.11384959082983</v>
+        <v>17.11384959082982</v>
       </c>
       <c r="CA111" s="212" t="n">
         <v>14.47945378566209</v>
@@ -24023,19 +24023,19 @@
         <v>1566</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.0124683621236049</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157616</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989036</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069173</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.01372109225177184</v>
+        <v>0.01372109225177136</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24282,7 +24282,7 @@
         <v>437.9845297780586</v>
       </c>
       <c r="CE112" s="222" t="n">
-        <v>506.7792077260667</v>
+        <v>506.7792077260666</v>
       </c>
       <c r="CF112" s="222" t="n">
         <v>530.7050712928472</v>
@@ -24318,19 +24318,19 @@
         <v>17676</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273312</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974732</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7444004017231202</v>
+        <v>0.7444004017231198</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908425</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675241</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -30326,19 +30326,19 @@
         <v>586.6102006092929</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>608.4286029140145</v>
+        <v>608.4286029140143</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>615.2501466925028</v>
+        <v>615.2501466925027</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>675.0153015009822</v>
+        <v>675.0153015009823</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>702.5569141655974</v>
+        <v>702.5569141655973</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>695.0424432280513</v>
+        <v>695.0424432280515</v>
       </c>
     </row>
     <row r="147">
@@ -30902,19 +30902,19 @@
         <v>28770.818246126</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>30.87585814343995</v>
+        <v>30.87585814343887</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>33.4290144749875</v>
+        <v>33.42901447498633</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>36.329466859512</v>
+        <v>36.32946685951074</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>39.07530999124027</v>
+        <v>39.0753099912389</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>42.03063898291106</v>
+        <v>42.03063898290959</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -31094,19 +31094,19 @@
         <v>2516.171986450182</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>1068.402173237966</v>
+        <v>1068.402173237965</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>1070.386644190056</v>
+        <v>1070.386644190055</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>1156.267712501015</v>
+        <v>1156.267712501014</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>1214.473977907794</v>
+        <v>1214.473977907792</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>1203.937355400997</v>
+        <v>1203.937355400995</v>
       </c>
     </row>
     <row r="151">
@@ -34574,13 +34574,13 @@
         <v>21.63800420233821</v>
       </c>
       <c r="BZ173" s="190" t="n">
-        <v>21.75078499390857</v>
+        <v>21.75078499390859</v>
       </c>
       <c r="CA173" s="190" t="n">
         <v>20.94215095471599</v>
       </c>
       <c r="CB173" s="198" t="n">
-        <v>21.29861264417694</v>
+        <v>21.29861264417693</v>
       </c>
       <c r="CC173" s="197" t="n">
         <v>24.1907998675334</v>
@@ -34589,13 +34589,13 @@
         <v>21.63800420233821</v>
       </c>
       <c r="CE173" s="190" t="n">
-        <v>21.75078499390857</v>
+        <v>21.75078499390859</v>
       </c>
       <c r="CF173" s="190" t="n">
         <v>20.94215095471599</v>
       </c>
       <c r="CG173" s="198" t="n">
-        <v>21.29861264417694</v>
+        <v>21.29861264417693</v>
       </c>
       <c r="CI173" s="197" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>4.329022708878102</v>
       </c>
       <c r="BY175" s="212" t="n">
-        <v>4.441490719827371</v>
+        <v>4.441490719827372</v>
       </c>
       <c r="BZ175" s="212" t="n">
         <v>4.576467623128091</v>
@@ -35138,13 +35138,13 @@
         <v>4.66927838548026</v>
       </c>
       <c r="CB175" s="213" t="n">
-        <v>4.763971350750315</v>
+        <v>4.763971350750316</v>
       </c>
       <c r="CC175" s="212" t="n">
         <v>4.329022708878102</v>
       </c>
       <c r="CD175" s="212" t="n">
-        <v>4.441490719827371</v>
+        <v>4.441490719827372</v>
       </c>
       <c r="CE175" s="212" t="n">
         <v>4.576467623128091</v>
@@ -35153,7 +35153,7 @@
         <v>4.66927838548026</v>
       </c>
       <c r="CG175" s="213" t="n">
-        <v>4.763971350750315</v>
+        <v>4.763971350750316</v>
       </c>
       <c r="CI175" s="211" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>157.8989653359704</v>
       </c>
       <c r="BY176" s="222" t="n">
-        <v>148.988375230998</v>
+        <v>148.9883752309981</v>
       </c>
       <c r="BZ176" s="222" t="n">
         <v>150.1919596652802</v>
@@ -35423,7 +35423,7 @@
         <v>157.8989653359704</v>
       </c>
       <c r="CD176" s="222" t="n">
-        <v>148.988375230998</v>
+        <v>148.9883752309981</v>
       </c>
       <c r="CE176" s="222" t="n">
         <v>150.1919596652802</v>
@@ -38461,34 +38461,34 @@
         <v>0</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462433</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="AV190" s="190" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462436</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38511,34 +38511,34 @@
         <v>0</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462433</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="BM190" s="200" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462433</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38561,34 +38561,34 @@
         <v>0</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>69.78370559292641</v>
+        <v>69.78370559292638</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>57.03491411263914</v>
+        <v>57.03491411263911</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>51.69911604575851</v>
+        <v>51.69911604575854</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>44.54995519344448</v>
+        <v>44.5499551934445</v>
       </c>
       <c r="CB190" s="198" t="n">
-        <v>44.98472521926205</v>
+        <v>44.98472521926212</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>69.78370559292641</v>
+        <v>69.78370559292638</v>
       </c>
       <c r="CD190" s="200" t="n">
-        <v>57.03491411263914</v>
+        <v>57.03491411263911</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>51.69911604575851</v>
+        <v>51.69911604575854</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>44.54995519344448</v>
+        <v>44.5499551934445</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>44.98472521926205</v>
+        <v>44.98472521926212</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>0</v>
@@ -38624,7 +38624,7 @@
         <v>0.5738078228343186</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5642210685925357</v>
+        <v>0.5642210685925358</v>
       </c>
       <c r="CZ190" s="92" t="n">
         <v>0.5462383402166368</v>
@@ -38633,19 +38633,19 @@
         <v>0.5331966353622142</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.008301495056945576</v>
+        <v>0.008301495056945579</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.009097557470214323</v>
+        <v>0.009097557470214328</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.00993285801282286</v>
+        <v>0.009932858012822857</v>
       </c>
       <c r="DF190" s="394" t="n">
         <v>0.0112498615179298</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.01085111771704301</v>
+        <v>0.010851117717043</v>
       </c>
     </row>
     <row r="191">
@@ -38767,13 +38767,13 @@
         <v>0</v>
       </c>
       <c r="AO191" s="195" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="AR191" s="179" t="n">
         <v>21.83867583929181</v>
@@ -38782,22 +38782,22 @@
         <v>21.0292752695913</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497721</v>
       </c>
       <c r="AU191" s="190" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>21.8386758392918</v>
+        <v>21.83867583929181</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>21.02927526959131</v>
+        <v>21.0292752695913</v>
       </c>
       <c r="AY191" s="196" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497719</v>
       </c>
       <c r="BA191" s="101" t="inlineStr">
         <is>
@@ -38817,13 +38817,13 @@
         <v>0</v>
       </c>
       <c r="BF191" s="198" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="BI191" s="190" t="n">
         <v>21.83867583929181</v>
@@ -38832,13 +38832,13 @@
         <v>21.0292752695913</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497721</v>
       </c>
       <c r="BL191" s="197" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="BM191" s="190" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="BN191" s="190" t="n">
         <v>21.83867583929181</v>
@@ -38847,7 +38847,7 @@
         <v>21.0292752695913</v>
       </c>
       <c r="BP191" s="198" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497721</v>
       </c>
       <c r="BR191" s="101" t="inlineStr">
         <is>
@@ -38870,34 +38870,34 @@
         <v>0</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>24.19079986737808</v>
+        <v>24.19079986737812</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>21.63800420271416</v>
+        <v>21.63800420271419</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>21.75078499419922</v>
+        <v>21.75078499419923</v>
       </c>
       <c r="CA191" s="190" t="n">
         <v>20.94215095430898</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>21.29861264415429</v>
+        <v>21.29861264415422</v>
       </c>
       <c r="CC191" s="197" t="n">
-        <v>24.19079986737808</v>
+        <v>24.19079986737812</v>
       </c>
       <c r="CD191" s="190" t="n">
-        <v>21.63800420271416</v>
+        <v>21.63800420271419</v>
       </c>
       <c r="CE191" s="190" t="n">
-        <v>21.75078499419922</v>
+        <v>21.75078499419923</v>
       </c>
       <c r="CF191" s="190" t="n">
         <v>20.94215095430898</v>
       </c>
       <c r="CG191" s="198" t="n">
-        <v>21.29861264415429</v>
+        <v>21.29861264415422</v>
       </c>
       <c r="CI191" s="197" t="n">
         <v>0</v>
@@ -38930,22 +38930,22 @@
         <v>0.1037014274659339</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>0.08753547266332017</v>
+        <v>0.08753547266332018</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>0.08789084509257697</v>
+        <v>0.08789084509257702</v>
       </c>
       <c r="CZ191" s="103" t="n">
         <v>0.08712431528231337</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>0.07552666082297217</v>
+        <v>0.07552666082297213</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.003014280652330891</v>
+        <v>0.003014280652330886</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.002774916966255243</v>
+        <v>0.002774916966255239</v>
       </c>
       <c r="DE191" s="397" t="n">
         <v>0.002770316402479114</v>
@@ -38954,7 +38954,7 @@
         <v>0.002888767623633594</v>
       </c>
       <c r="DG191" s="398" t="n">
-        <v>0.002279319615990401</v>
+        <v>0.002279319615990407</v>
       </c>
     </row>
     <row r="192">
@@ -39079,34 +39079,34 @@
         <v>0</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="AQ192" s="179" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="AS192" s="179" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="AX192" s="190" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39129,34 +39129,34 @@
         <v>0</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="BH192" s="190" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="BJ192" s="190" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="BL192" s="197" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="BM192" s="190" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="BN192" s="190" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="BO192" s="190" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39179,34 +39179,34 @@
         <v>0</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>59.59543716616347</v>
+        <v>59.5954371661634</v>
       </c>
       <c r="BY192" s="190" t="n">
-        <v>65.87396619592056</v>
+        <v>65.87396619592057</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>72.16559100319834</v>
+        <v>72.1655910031983</v>
       </c>
       <c r="CA192" s="190" t="n">
-        <v>79.33915971836331</v>
+        <v>79.33915971836328</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>80.50025297216024</v>
+        <v>80.5002529721602</v>
       </c>
       <c r="CC192" s="197" t="n">
-        <v>59.59543716616347</v>
+        <v>59.5954371661634</v>
       </c>
       <c r="CD192" s="190" t="n">
-        <v>65.87396619592056</v>
+        <v>65.87396619592057</v>
       </c>
       <c r="CE192" s="190" t="n">
-        <v>72.16559100319834</v>
+        <v>72.1655910031983</v>
       </c>
       <c r="CF192" s="190" t="n">
-        <v>79.33915971836331</v>
+        <v>79.33915971836328</v>
       </c>
       <c r="CG192" s="198" t="n">
-        <v>80.50025297216024</v>
+        <v>80.5002529721602</v>
       </c>
       <c r="CI192" s="197" t="n">
         <v>0</v>
@@ -39251,19 +39251,19 @@
         <v>0.07902089963056634</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.001124083347205914</v>
+        <v>0.001124083347205915</v>
       </c>
       <c r="DD192" s="397" t="n">
         <v>0.001007404309347209</v>
       </c>
       <c r="DE192" s="397" t="n">
-        <v>0.0009008959653007927</v>
+        <v>0.0009008959653007933</v>
       </c>
       <c r="DF192" s="397" t="n">
-        <v>0.000805627196036726</v>
+        <v>0.0008056271960367263</v>
       </c>
       <c r="DG192" s="398" t="n">
-        <v>0.0007865633091200317</v>
+        <v>0.0007865633091200321</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" thickBot="1">
@@ -39391,31 +39391,31 @@
         <v>4.341491071594504</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="AR193" s="207" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="AS193" s="207" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="AU193" s="209" t="n">
         <v>4.341491071594504</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="AW193" s="209" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="AX193" s="209" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39441,31 +39441,31 @@
         <v>4.341491071594504</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="BI193" s="212" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="BJ193" s="212" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="BL193" s="212" t="n">
         <v>4.341491071594504</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="BN193" s="212" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="BO193" s="212" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39491,31 +39491,31 @@
         <v>4.329022709470899</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>4.441490719462946</v>
+        <v>4.44149071946295</v>
       </c>
       <c r="BZ193" s="212" t="n">
-        <v>4.576467622427431</v>
+        <v>4.576467622427428</v>
       </c>
       <c r="CA193" s="212" t="n">
         <v>4.669278385810258</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>4.763971351474487</v>
+        <v>4.763971351474492</v>
       </c>
       <c r="CC193" s="212" t="n">
         <v>4.329022709470899</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>4.441490719462946</v>
+        <v>4.44149071946295</v>
       </c>
       <c r="CE193" s="212" t="n">
-        <v>4.576467622427431</v>
+        <v>4.576467622427428</v>
       </c>
       <c r="CF193" s="212" t="n">
         <v>4.669278385810258</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>4.763971351474487</v>
+        <v>4.763971351474492</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>0</v>
@@ -39545,19 +39545,19 @@
         <v>972</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.0124683621236049</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157616</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989036</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069173</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.01372109225177185</v>
+        <v>0.01372109225177136</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39697,7 +39697,7 @@
         <v>0</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="AQ194" s="207" t="n">
         <v>149.7417536867343</v>
@@ -39712,7 +39712,7 @@
         <v>152.2490274751186</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="AV194" s="207" t="n">
         <v>149.7417536867343</v>
@@ -39747,7 +39747,7 @@
         <v>0</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="BH194" s="222" t="n">
         <v>149.7417536867343</v>
@@ -39762,7 +39762,7 @@
         <v>152.2490274751186</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="BM194" s="222" t="n">
         <v>149.7417536867343</v>
@@ -39809,7 +39809,7 @@
         <v>149.500544251927</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>151.5475621870511</v>
+        <v>151.547562187051</v>
       </c>
       <c r="CC194" s="222" t="n">
         <v>157.8989653359388</v>
@@ -39824,7 +39824,7 @@
         <v>149.500544251927</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>151.5475621870511</v>
+        <v>151.547562187051</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>0</v>
@@ -39854,19 +39854,19 @@
         <v>22134</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273312</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974733</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.7444004017231201</v>
+        <v>0.7444004017231198</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908425</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675241</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40670,7 +40670,7 @@
       </c>
       <c r="CS198" s="465" t="n"/>
       <c r="CT198" s="396" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CU198" s="397" t="n">
         <v>1</v>
@@ -40679,7 +40679,7 @@
         <v>1</v>
       </c>
       <c r="CW198" s="397" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CX198" s="398" t="n">
         <v>1</v>
@@ -40837,19 +40837,19 @@
         <v>-0</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462433</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40887,19 +40887,19 @@
         <v>-0</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>70.4291443816582</v>
+        <v>70.42914438165818</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>57.60872193547345</v>
+        <v>57.60872193547343</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>52.26333711435105</v>
+        <v>52.26333711435107</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>45.09619353366112</v>
+        <v>45.09619353366114</v>
       </c>
       <c r="BP199" s="201" t="n">
-        <v>45.51792185462426</v>
+        <v>45.51792185462433</v>
       </c>
       <c r="BR199" s="83" t="inlineStr">
         <is>
@@ -40922,25 +40922,25 @@
         <v>45.51792185462427</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>1</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="CA199" s="463" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>1</v>
+        <v>0.9999999999999986</v>
       </c>
       <c r="CC199" s="199" t="n">
         <v>69.7837055929264</v>
       </c>
       <c r="CD199" s="200" t="n">
-        <v>57.03491411263915</v>
+        <v>57.03491411263914</v>
       </c>
       <c r="CE199" s="200" t="n">
         <v>51.69911604575851</v>
@@ -40973,13 +40973,13 @@
         <v>1.000000015019799</v>
       </c>
       <c r="CP199" s="397" t="n">
-        <v>1.000000007401979</v>
+        <v>1.000000007401978</v>
       </c>
       <c r="CQ199" s="397" t="n">
         <v>0.9999999871074222</v>
       </c>
       <c r="CR199" s="398" t="n">
-        <v>0.9999999856798223</v>
+        <v>0.999999985679823</v>
       </c>
       <c r="CS199" s="465" t="n"/>
       <c r="CT199" s="396" t="n">
@@ -40992,7 +40992,7 @@
         <v>1</v>
       </c>
       <c r="CW199" s="397" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CX199" s="398" t="n">
         <v>1</v>
@@ -41007,7 +41007,7 @@
         <v>1.000000001775828</v>
       </c>
       <c r="DB199" s="397" t="n">
-        <v>0.9999999969882596</v>
+        <v>0.9999999969882595</v>
       </c>
       <c r="DC199" s="398" t="n">
         <v>0.9999999965795362</v>
@@ -41126,13 +41126,13 @@
         <v>0</v>
       </c>
       <c r="AM200" s="227" t="n">
-        <v>-6.50719614127614e-16</v>
+        <v>-0</v>
       </c>
       <c r="AN200" s="227" t="n">
         <v>0</v>
       </c>
       <c r="AO200" s="232" t="n">
-        <v>0</v>
+        <v>-6.648620799384824e-16</v>
       </c>
       <c r="AP200" s="233" t="n">
         <v>0</v>
@@ -41141,28 +41141,28 @@
         <v>0</v>
       </c>
       <c r="AR200" s="190" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS200" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT200" s="196" t="n">
         <v>-1.4210854715202e-14</v>
       </c>
-      <c r="AS200" s="190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT200" s="196" t="n">
-        <v>0</v>
-      </c>
       <c r="AU200" s="190" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>21.8386758392918</v>
+        <v>21.83867583929181</v>
       </c>
       <c r="AX200" s="190" t="n">
         <v>21.0292752695913</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497719</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41176,13 +41176,13 @@
         <v>0</v>
       </c>
       <c r="BD200" s="227" t="n">
-        <v>-6.50719614127614e-16</v>
+        <v>-0</v>
       </c>
       <c r="BE200" s="227" t="n">
         <v>0</v>
       </c>
       <c r="BF200" s="235" t="n">
-        <v>0</v>
+        <v>-6.648620799384824e-16</v>
       </c>
       <c r="BG200" s="197" t="n">
         <v>0</v>
@@ -41191,28 +41191,28 @@
         <v>0</v>
       </c>
       <c r="BI200" s="190" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ200" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK200" s="198" t="n">
         <v>-1.421085471520201e-14</v>
       </c>
-      <c r="BJ200" s="190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK200" s="198" t="n">
-        <v>0</v>
-      </c>
       <c r="BL200" s="197" t="n">
-        <v>24.29450129484401</v>
+        <v>24.29450129484405</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>21.72553967537748</v>
+        <v>21.7255396753775</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>21.8386758392918</v>
+        <v>21.83867583929181</v>
       </c>
       <c r="BO200" s="190" t="n">
         <v>21.0292752695913</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>21.37413930497726</v>
+        <v>21.37413930497719</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41235,10 +41235,10 @@
         <v>21.37413930497724</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>1.000000000000001</v>
+        <v>0.9999999999999992</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>1</v>
+        <v>0.9999999999999992</v>
       </c>
       <c r="BZ200" s="463" t="n">
         <v>0.9999999999999999</v>
@@ -41247,7 +41247,7 @@
         <v>1</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.999999999999999</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>24.1907998673781</v>
@@ -41256,13 +41256,13 @@
         <v>21.63800420271417</v>
       </c>
       <c r="CE200" s="190" t="n">
-        <v>21.75078499419921</v>
+        <v>21.75078499419923</v>
       </c>
       <c r="CF200" s="190" t="n">
         <v>20.94215095430898</v>
       </c>
       <c r="CG200" s="198" t="n">
-        <v>21.29861264415427</v>
+        <v>21.29861264415425</v>
       </c>
       <c r="CI200" s="396" t="n">
         <v>1</v>
@@ -41296,7 +41296,7 @@
       </c>
       <c r="CS200" s="465" t="n"/>
       <c r="CT200" s="396" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CU200" s="397" t="n">
         <v>0.9999999999999998</v>
@@ -41311,10 +41311,10 @@
         <v>1</v>
       </c>
       <c r="CY200" s="396" t="n">
-        <v>0.9999999975730698</v>
+        <v>0.9999999975730697</v>
       </c>
       <c r="CZ200" s="397" t="n">
-        <v>0.9999999996034326</v>
+        <v>0.9999999996034324</v>
       </c>
       <c r="DA200" s="397" t="n">
         <v>0.9999999973604107</v>
@@ -41463,19 +41463,19 @@
         <v>0</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="AV201" s="190" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="AX201" s="190" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41513,19 +41513,19 @@
         <v>0</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>59.67409839286947</v>
+        <v>59.6740983928694</v>
       </c>
       <c r="BM201" s="190" t="n">
-        <v>65.95320906624882</v>
+        <v>65.95320906624883</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>72.24469844336646</v>
+        <v>72.24469844336642</v>
       </c>
       <c r="BO201" s="190" t="n">
-        <v>79.41855637473451</v>
+        <v>79.41855637473448</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>80.5792738717908</v>
+        <v>80.57927387179076</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41548,19 +41548,19 @@
         <v>80.57927387179082</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.9999999999999999</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="BY201" s="463" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="BZ201" s="463" t="n">
         <v>1</v>
-      </c>
-      <c r="BZ201" s="463" t="n">
-        <v>0.9999999999999998</v>
       </c>
       <c r="CA201" s="463" t="n">
         <v>1</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CC201" s="197" t="n">
         <v>59.59543716616346</v>
@@ -41572,7 +41572,7 @@
         <v>72.16559100319833</v>
       </c>
       <c r="CF201" s="190" t="n">
-        <v>79.33915971836332</v>
+        <v>79.33915971836331</v>
       </c>
       <c r="CG201" s="198" t="n">
         <v>80.50025297216025</v>
@@ -41620,16 +41620,16 @@
         <v>1</v>
       </c>
       <c r="CX201" s="424" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CY201" s="422" t="n">
-        <v>0.9999999974433325</v>
+        <v>0.9999999974433322</v>
       </c>
       <c r="CZ201" s="423" t="n">
-        <v>0.9999999996314928</v>
+        <v>0.9999999996314929</v>
       </c>
       <c r="DA201" s="423" t="n">
-        <v>1.000000015168151</v>
+        <v>1.000000015168152</v>
       </c>
       <c r="DB201" s="423" t="n">
         <v>1.000000013316759</v>
@@ -41778,16 +41778,16 @@
         <v>4.341491071594504</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="AW202" s="209" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="AX202" s="209" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41828,16 +41828,16 @@
         <v>4.341491071594504</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>4.454283009634523</v>
+        <v>4.454283009634526</v>
       </c>
       <c r="BN202" s="212" t="n">
-        <v>4.589648670297322</v>
+        <v>4.589648670297318</v>
       </c>
       <c r="BO202" s="212" t="n">
         <v>4.68272674533095</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>4.777692443726259</v>
+        <v>4.777692443726263</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41863,16 +41863,16 @@
         <v>0.9999999999999993</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.9999999999999992</v>
+        <v>1</v>
       </c>
       <c r="CA202" s="467" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>4.329022709470896</v>
@@ -41887,7 +41887,7 @@
         <v>4.669278385810257</v>
       </c>
       <c r="CG202" s="213" t="n">
-        <v>4.763971351474489</v>
+        <v>4.76397135147449</v>
       </c>
       <c r="CW202" s="465" t="n"/>
       <c r="CX202" s="465" t="n"/>
@@ -42013,13 +42013,13 @@
         <v>0</v>
       </c>
       <c r="AM203" s="266" t="n">
-        <v>-6.50719614127614e-16</v>
+        <v>0</v>
       </c>
       <c r="AN203" s="266" t="n">
         <v>0</v>
       </c>
       <c r="AO203" s="267" t="n">
-        <v>0</v>
+        <v>-6.648620799384824e-16</v>
       </c>
       <c r="AP203" s="206" t="n">
         <v>0</v>
@@ -42028,16 +42028,16 @@
         <v>0</v>
       </c>
       <c r="AR203" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS203" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT203" s="208" t="n">
         <v>-1.4210854715202e-14</v>
       </c>
-      <c r="AS203" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT203" s="208" t="n">
-        <v>0</v>
-      </c>
       <c r="AU203" s="207" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="AV203" s="207" t="n">
         <v>149.7417536867343</v>
@@ -42063,13 +42063,13 @@
         <v>0</v>
       </c>
       <c r="BD203" s="269" t="n">
-        <v>-6.50719614127614e-16</v>
+        <v>0</v>
       </c>
       <c r="BE203" s="269" t="n">
         <v>0</v>
       </c>
       <c r="BF203" s="270" t="n">
-        <v>0</v>
+        <v>-6.648620799384824e-16</v>
       </c>
       <c r="BG203" s="221" t="n">
         <v>0</v>
@@ -42078,16 +42078,16 @@
         <v>0</v>
       </c>
       <c r="BI203" s="222" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ203" s="222" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK203" s="214" t="n">
         <v>-1.421085471520201e-14</v>
       </c>
-      <c r="BJ203" s="222" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK203" s="214" t="n">
-        <v>0</v>
-      </c>
       <c r="BL203" s="222" t="n">
-        <v>158.7392351409662</v>
+        <v>158.7392351409661</v>
       </c>
       <c r="BM203" s="222" t="n">
         <v>149.7417536867343</v>
@@ -42149,7 +42149,7 @@
         <v>149.500544251927</v>
       </c>
       <c r="CG203" s="213" t="n">
-        <v>151.5475621870511</v>
+        <v>151.547562187051</v>
       </c>
       <c r="CW203" s="465" t="n"/>
       <c r="CX203" s="465" t="n"/>
@@ -42949,7 +42949,7 @@
         <v>0</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0</v>
+        <v>6.24407008764099e-16</v>
       </c>
       <c r="AU208" s="463" t="n">
         <v>0</v>
@@ -43183,14 +43183,14 @@
         <v>0</v>
       </c>
       <c r="AM209" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN209" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO209" s="196" t="n">
         <v>1.4210854715202e-14</v>
       </c>
-      <c r="AN209" s="190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO209" s="196" t="n">
-        <v>0</v>
-      </c>
       <c r="AP209" s="473" t="n">
         <v>0</v>
       </c>
@@ -43198,13 +43198,13 @@
         <v>0</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>-6.50719614127614e-16</v>
+        <v>0</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>6.757653096942976e-16</v>
+        <v>0</v>
       </c>
       <c r="AT209" s="474" t="n">
-        <v>0</v>
+        <v>-6.648620799384824e-16</v>
       </c>
       <c r="AU209" s="463" t="n">
         <v>0</v>
@@ -43213,13 +43213,13 @@
         <v>0</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>6.50719614127614e-16</v>
+        <v>0</v>
       </c>
       <c r="AX209" s="463" t="n">
         <v>0</v>
       </c>
       <c r="AY209" s="474" t="n">
-        <v>0</v>
+        <v>6.648620799384824e-16</v>
       </c>
       <c r="BA209" s="101" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>0</v>
       </c>
       <c r="BK209" s="464" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL209" s="462" t="n">
         <v>0</v>
@@ -43948,14 +43948,14 @@
         <v>0</v>
       </c>
       <c r="AM212" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN212" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO212" s="208" t="n">
         <v>1.4210854715202e-14</v>
       </c>
-      <c r="AN212" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO212" s="208" t="n">
-        <v>0</v>
-      </c>
       <c r="AP212" s="500" t="n">
         <v>0</v>
       </c>
@@ -43978,13 +43978,13 @@
         <v>0</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>9.415130130914114e-17</v>
+        <v>0</v>
       </c>
       <c r="AX212" s="501" t="n">
         <v>0</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0</v>
+        <v>9.333954344978936e-17</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -44740,10 +44740,10 @@
         <v>0</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>0</v>
@@ -44775,10 +44775,10 @@
         <v>0</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>0</v>
@@ -44926,19 +44926,19 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="AL220" s="368" t="n">
         <v>0</v>
       </c>
       <c r="AM220" s="368" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AO220" s="380" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AP220" s="381" t="n">
         <v>0</v>
@@ -44961,19 +44961,19 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="BC220" s="375" t="n">
         <v>0</v>
       </c>
       <c r="BD220" s="375" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BF220" s="392" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BG220" s="386" t="n">
         <v>0</v>
@@ -45133,7 +45133,7 @@
         <v>0</v>
       </c>
       <c r="AO221" s="380" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP221" s="381" t="n">
         <v>0</v>
@@ -45168,7 +45168,7 @@
         <v>0</v>
       </c>
       <c r="BF221" s="392" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG221" s="386" t="n">
         <v>0</v>
@@ -45511,16 +45511,16 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="AL223" s="408" t="n">
         <v>0</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN223" s="408" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="AO223" s="409" t="n">
         <v>0</v>
@@ -45546,16 +45546,16 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="BC223" s="440" t="n">
         <v>0</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE223" s="440" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="BF223" s="441" t="n">
         <v>0</v>
@@ -47638,10 +47638,10 @@
         <v>0</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>0</v>
@@ -47673,10 +47673,10 @@
         <v>0</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>0</v>
@@ -47824,19 +47824,19 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="AL238" s="368" t="n">
         <v>0</v>
       </c>
       <c r="AM238" s="368" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AO238" s="380" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="AP238" s="381" t="n">
         <v>0</v>
@@ -47859,19 +47859,19 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="BC238" s="375" t="n">
         <v>0</v>
       </c>
       <c r="BD238" s="375" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BF238" s="392" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="BG238" s="386" t="n">
         <v>0</v>
@@ -48031,7 +48031,7 @@
         <v>0</v>
       </c>
       <c r="AO239" s="380" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AP239" s="381" t="n">
         <v>0</v>
@@ -48066,7 +48066,7 @@
         <v>0</v>
       </c>
       <c r="BF239" s="392" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BG239" s="386" t="n">
         <v>0</v>
@@ -48409,16 +48409,16 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="AL241" s="408" t="n">
         <v>0</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="AN241" s="408" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="AO241" s="409" t="n">
         <v>0</v>
@@ -48444,16 +48444,16 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>-7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="BC241" s="440" t="n">
         <v>0</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="BE241" s="440" t="n">
-        <v>-4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="BF241" s="441" t="n">
         <v>0</v>
@@ -49036,31 +49036,31 @@
         </is>
       </c>
       <c r="AK246" s="506" t="n">
-        <v>66390.65769892574</v>
+        <v>66390.65769892579</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>61769.41695598941</v>
+        <v>61769.4169559894</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>62526.1163513383</v>
+        <v>62526.11635133825</v>
       </c>
       <c r="AN246" s="368" t="n">
-        <v>58001.49964746026</v>
+        <v>58001.49964746027</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>59334.37238636029</v>
+        <v>59334.37238636032</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>942.6588705782093</v>
+        <v>942.6588705782099</v>
       </c>
       <c r="AQ246" s="372" t="n">
         <v>1072.223352300919</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>1196.366703774627</v>
+        <v>1196.366703774626</v>
       </c>
       <c r="AS246" s="372" t="n">
-        <v>1286.172847465061</v>
+        <v>1286.172847465062</v>
       </c>
       <c r="AT246" s="382" t="n">
         <v>1303.538693543105</v>
@@ -49071,31 +49071,31 @@
         </is>
       </c>
       <c r="BB246" s="391" t="n">
-        <v>66390.65769892574</v>
+        <v>66390.65769892579</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>61769.41695598941</v>
+        <v>61769.4169559894</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>62526.1163513383</v>
+        <v>62526.11635133825</v>
       </c>
       <c r="BE246" s="375" t="n">
-        <v>58001.49964746026</v>
+        <v>58001.49964746027</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>59334.37238636029</v>
+        <v>59334.37238636032</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>942.6588705782093</v>
+        <v>942.6588705782099</v>
       </c>
       <c r="BH246" s="372" t="n">
         <v>1072.223352300919</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>1196.366703774627</v>
+        <v>1196.366703774626</v>
       </c>
       <c r="BJ246" s="372" t="n">
-        <v>1286.172847465061</v>
+        <v>1286.172847465062</v>
       </c>
       <c r="BK246" s="387" t="n">
         <v>1303.538693543105</v>
@@ -49106,31 +49106,31 @@
         </is>
       </c>
       <c r="BS246" s="391" t="n">
-        <v>65782.22909930952</v>
+        <v>65782.22909930955</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>61154.16680860789</v>
+        <v>61154.16680860788</v>
       </c>
       <c r="BU246" s="375" t="n">
-        <v>61851.10105131057</v>
+        <v>61851.10105131053</v>
       </c>
       <c r="BV246" s="375" t="n">
-        <v>57298.94272602395</v>
+        <v>57298.94272602397</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>58639.32994090818</v>
+        <v>58639.32994090822</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>942.6588705782093</v>
+        <v>942.6588705782099</v>
       </c>
       <c r="BY246" s="372" t="n">
         <v>1072.223352300919</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>1196.366703774627</v>
+        <v>1196.366703774626</v>
       </c>
       <c r="CA246" s="372" t="n">
-        <v>1286.172847465061</v>
+        <v>1286.172847465062</v>
       </c>
       <c r="CB246" s="387" t="n">
         <v>1303.538693543105</v>
@@ -49215,34 +49215,34 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>58598.88127559348</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>57407.08920022819</v>
+        <v>57407.08920022813</v>
       </c>
       <c r="AM247" s="368" t="n">
         <v>60876.37537505453</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085033</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>67766.10007773865</v>
+        <v>67766.10007773871</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>2412.022398156968</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>2642.378051776896</v>
+        <v>2642.378051776894</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>2787.548834180695</v>
       </c>
       <c r="AS247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>3170.471526864536</v>
+        <v>3170.471526864539</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49250,34 +49250,34 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>58598.88127559348</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>57407.08920022819</v>
+        <v>57407.08920022813</v>
       </c>
       <c r="BD247" s="375" t="n">
         <v>60876.37537505453</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085033</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>67766.10007773865</v>
+        <v>67766.10007773871</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>2412.022398156968</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>2642.378051776896</v>
+        <v>2642.378051776894</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>2787.548834180695</v>
       </c>
       <c r="BJ247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>3170.471526864536</v>
+        <v>3170.471526864539</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49285,34 +49285,34 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>58348.75110982319</v>
+        <v>58348.75110982321</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>57175.78738851473</v>
+        <v>57175.78738851468</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>60631.3753522848</v>
+        <v>60631.37535228484</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>62727.38814771608</v>
+        <v>62727.38814771605</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>67526.64495007999</v>
+        <v>67526.64495008001</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>2412.022398156968</v>
+        <v>2412.022398156969</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>2642.378051776896</v>
+        <v>2642.378051776894</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>2787.548834180695</v>
       </c>
       <c r="CA247" s="372" t="n">
-        <v>2995.269601644735</v>
+        <v>2995.269601644733</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>3170.471526864536</v>
+        <v>3170.471526864539</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49400,7 +49400,7 @@
         <v>158473.1245926057</v>
       </c>
       <c r="AM248" s="368" t="n">
-        <v>182579.175577938</v>
+        <v>182579.1755779381</v>
       </c>
       <c r="AN248" s="368" t="n">
         <v>211939.3794528705</v>
@@ -49412,10 +49412,10 @@
         <v>2275.168462138938</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2402.811430055211</v>
+        <v>2402.81143005521</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2527.232856013515</v>
+        <v>2527.232856013517</v>
       </c>
       <c r="AS248" s="372" t="n">
         <v>2668.638025251066</v>
@@ -49435,7 +49435,7 @@
         <v>158473.1245926057</v>
       </c>
       <c r="BD248" s="375" t="n">
-        <v>182579.175577938</v>
+        <v>182579.1755779381</v>
       </c>
       <c r="BE248" s="375" t="n">
         <v>211939.3794528705</v>
@@ -49447,10 +49447,10 @@
         <v>2275.168462138938</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2402.811430055211</v>
+        <v>2402.81143005521</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2527.232856013515</v>
+        <v>2527.232856013517</v>
       </c>
       <c r="BJ248" s="372" t="n">
         <v>2668.638025251066</v>
@@ -49470,7 +49470,7 @@
         <v>158282.7189180313</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>182379.252655991</v>
+        <v>182379.2526559912</v>
       </c>
       <c r="BV248" s="375" t="n">
         <v>211727.4985165998</v>
@@ -49482,10 +49482,10 @@
         <v>2275.168462138938</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2402.811430055211</v>
+        <v>2402.81143005521</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2527.232856013515</v>
+        <v>2527.232856013517</v>
       </c>
       <c r="CA248" s="372" t="n">
         <v>2668.638025251066</v>
@@ -49573,7 +49573,7 @@
         </is>
       </c>
       <c r="AK249" s="435" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="AL249" s="408" t="n">
         <v>11640.0026023282</v>
@@ -49585,10 +49585,10 @@
         <v>13606.04680805828</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>14635.09201340936</v>
+        <v>14635.09201340942</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="AQ249" s="411" t="n">
         <v>2613.215769226169</v>
@@ -49600,7 +49600,7 @@
         <v>2905.582056989805</v>
       </c>
       <c r="AT249" s="412" t="n">
-        <v>3063.213504848319</v>
+        <v>3063.213504848331</v>
       </c>
       <c r="BA249" s="111" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         </is>
       </c>
       <c r="BB249" s="419" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="BC249" s="420" t="n">
         <v>11640.0026023282</v>
@@ -49620,10 +49620,10 @@
         <v>13606.04680805828</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>14635.09201340936</v>
+        <v>14635.09201340942</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="BH249" s="417" t="n">
         <v>2613.215769226169</v>
@@ -49635,7 +49635,7 @@
         <v>2905.582056989805</v>
       </c>
       <c r="BK249" s="418" t="n">
-        <v>3063.213504848319</v>
+        <v>3063.213504848331</v>
       </c>
       <c r="BR249" s="111" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>10720.11604629892</v>
+        <v>10720.1160462988</v>
       </c>
       <c r="BT249" s="420" t="n">
         <v>11606.57358792457</v>
@@ -49655,10 +49655,10 @@
         <v>13566.97149594177</v>
       </c>
       <c r="BW249" s="421" t="n">
-        <v>14593.06137832885</v>
+        <v>14593.06137832891</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>2476.336292788151</v>
+        <v>2476.336292788124</v>
       </c>
       <c r="BY249" s="417" t="n">
         <v>2613.215769226169</v>
@@ -49670,7 +49670,7 @@
         <v>2905.582056989805</v>
       </c>
       <c r="CB249" s="418" t="n">
-        <v>3063.213504848319</v>
+        <v>3063.213504848331</v>
       </c>
       <c r="CI249" s="225" t="n"/>
       <c r="CJ249" s="225" t="n"/>
@@ -49752,22 +49752,22 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>271509.1575487817</v>
+        <v>271509.1575487816</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>289289.6333511515</v>
+        <v>289289.6333511514</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>318631.6100773186</v>
+        <v>318631.6100773187</v>
       </c>
       <c r="AN250" s="408" t="n">
         <v>346535.2748692394</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>373629.4515146997</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="AP250" s="436" t="n">
-        <v>1710.409888945313</v>
+        <v>1710.409888945312</v>
       </c>
       <c r="AQ250" s="437" t="n">
         <v>1931.923636715539</v>
@@ -49787,22 +49787,22 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>271509.1575487817</v>
+        <v>271509.1575487816</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>289289.6333511515</v>
+        <v>289289.6333511514</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>318631.6100773186</v>
+        <v>318631.6100773187</v>
       </c>
       <c r="BE250" s="440" t="n">
         <v>346535.2748692394</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>373629.4515146997</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="BG250" s="442" t="n">
-        <v>1710.409888945313</v>
+        <v>1710.409888945312</v>
       </c>
       <c r="BH250" s="443" t="n">
         <v>1931.923636715539</v>
@@ -49822,25 +49822,25 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>270440.7553835661</v>
+        <v>270440.755383566</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>288219.2467030785</v>
+        <v>288219.2467030784</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>317475.3423631049</v>
+        <v>317475.342363105</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>345320.8008862816</v>
+        <v>345320.8008862815</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>372425.5141640326</v>
+        <v>372425.5141640327</v>
       </c>
       <c r="BX250" s="442" t="n">
         <v>1712.745582646056</v>
       </c>
       <c r="BY250" s="443" t="n">
-        <v>1934.508288020531</v>
+        <v>1934.50828802053</v>
       </c>
       <c r="BZ250" s="443" t="n">
         <v>2113.797190413087</v>
@@ -49849,7 +49849,7 @@
         <v>2309.829724116651</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>2457.482712305753</v>
+        <v>2457.482712305754</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51942,34 +51942,34 @@
         </is>
       </c>
       <c r="AK264" s="506" t="n">
-        <v>66390.65769892574</v>
+        <v>66390.65769892579</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>61769.41695598941</v>
+        <v>61769.4169559894</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>62526.1163513383</v>
+        <v>62526.11635133825</v>
       </c>
       <c r="AN264" s="368" t="n">
-        <v>58001.49964746026</v>
+        <v>58001.49964746027</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>59334.37238636029</v>
+        <v>59334.37238636032</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>942.6588705827839</v>
+        <v>942.658870582785</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>1072.223352310719</v>
+        <v>1072.22335231072</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>1196.366703766591</v>
+        <v>1196.366703766589</v>
       </c>
       <c r="AS264" s="372" t="n">
         <v>1286.172847474726</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>1303.538693525227</v>
+        <v>1303.538693525226</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51977,34 +51977,34 @@
         </is>
       </c>
       <c r="BB264" s="391" t="n">
-        <v>66390.65769892574</v>
+        <v>66390.65769892579</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>61769.41695598941</v>
+        <v>61769.4169559894</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>62526.1163513383</v>
+        <v>62526.11635133825</v>
       </c>
       <c r="BE264" s="375" t="n">
-        <v>58001.49964746026</v>
+        <v>58001.49964746027</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>59334.37238636029</v>
+        <v>59334.37238636032</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>942.6588705827839</v>
+        <v>942.658870582785</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>1072.223352310719</v>
+        <v>1072.22335231072</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>1196.366703766591</v>
+        <v>1196.366703766589</v>
       </c>
       <c r="BJ264" s="372" t="n">
         <v>1286.172847474726</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>1303.538693525227</v>
+        <v>1303.538693525226</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,34 +52012,34 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>65782.22909930951</v>
+        <v>65782.22909930955</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>61154.16680860789</v>
+        <v>61154.16680860787</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>61851.10105131058</v>
+        <v>61851.10105131053</v>
       </c>
       <c r="BV264" s="375" t="n">
-        <v>57298.94272602396</v>
+        <v>57298.94272602397</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>58639.32994090818</v>
+        <v>58639.32994090821</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>942.6588705827839</v>
+        <v>942.658870582785</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>1072.223352310719</v>
+        <v>1072.22335231072</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>1196.366703766591</v>
+        <v>1196.366703766589</v>
       </c>
       <c r="CA264" s="372" t="n">
         <v>1286.172847474726</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>1303.538693525227</v>
+        <v>1303.538693525226</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>1</v>
@@ -52057,25 +52057,25 @@
         <v>1</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.999999999950997</v>
+        <v>0.9999999999509965</v>
       </c>
       <c r="CO264" s="103" t="n">
         <v>1.00000000001144</v>
       </c>
       <c r="CP264" s="103" t="n">
-        <v>0.999999999970711</v>
+        <v>0.9999999999707117</v>
       </c>
       <c r="CQ264" s="103" t="n">
         <v>1.000000000118858</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000031784</v>
+        <v>1.000000000031783</v>
       </c>
       <c r="CT264" s="396" t="n">
         <v>1</v>
       </c>
       <c r="CU264" s="397" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="CV264" s="397" t="n">
         <v>1</v>
@@ -52093,13 +52093,13 @@
         <v>1.000000000000091</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>0.9999999999971356</v>
+        <v>0.999999999997136</v>
       </c>
       <c r="DB264" s="103" t="n">
-        <v>0.9999999999959688</v>
+        <v>0.9999999999959687</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>0.9999999999967928</v>
+        <v>0.9999999999967922</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,19 +52117,19 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>56692.45153990572</v>
+        <v>56692.4515399057</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>53152.45709120955</v>
+        <v>53152.45709120954</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>54365.66030675422</v>
+        <v>54365.66030675421</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>49985.42743407265</v>
+        <v>49985.42743407263</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>47629.93996276433</v>
+        <v>47629.93996276431</v>
       </c>
     </row>
     <row r="265">
@@ -52209,34 +52209,34 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>58598.88127559348</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>57407.08920022819</v>
+        <v>57407.08920022813</v>
       </c>
       <c r="AM265" s="368" t="n">
         <v>60876.37537505453</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085033</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>67766.10007773865</v>
+        <v>67766.10007773871</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>2412.022398172456</v>
+        <v>2412.022398172453</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>2642.378051730987</v>
+        <v>2642.378051730981</v>
       </c>
       <c r="AR265" s="372" t="n">
         <v>2787.548834143446</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>2995.269601702948</v>
+        <v>2995.269601702946</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>3170.471526867909</v>
+        <v>3170.47152686792</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52244,34 +52244,34 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>58598.88127559348</v>
+        <v>58598.88127559351</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>57407.08920022819</v>
+        <v>57407.08920022813</v>
       </c>
       <c r="BD265" s="375" t="n">
         <v>60876.37537505453</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>62988.34896085037</v>
+        <v>62988.34896085033</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>67766.10007773865</v>
+        <v>67766.10007773871</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>2412.022398172456</v>
+        <v>2412.022398172453</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>2642.378051730987</v>
+        <v>2642.378051730981</v>
       </c>
       <c r="BI265" s="372" t="n">
         <v>2787.548834143446</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>2995.269601702948</v>
+        <v>2995.269601702946</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>3170.471526867909</v>
+        <v>3170.47152686792</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,34 +52279,34 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>58348.75110982319</v>
+        <v>58348.75110982321</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>57175.78738851474</v>
+        <v>57175.78738851468</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>60631.37535228479</v>
+        <v>60631.37535228483</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>62727.38814771608</v>
+        <v>62727.38814771604</v>
       </c>
       <c r="BW265" s="392" t="n">
         <v>67526.64495008001</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>2412.022398172456</v>
+        <v>2412.022398172453</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>2642.378051730987</v>
+        <v>2642.378051730981</v>
       </c>
       <c r="BZ265" s="372" t="n">
         <v>2787.548834143446</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>2995.269601702948</v>
+        <v>2995.269601702946</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>3170.471526867909</v>
+        <v>3170.47152686792</v>
       </c>
       <c r="CI265" s="396" t="n">
         <v>1</v>
@@ -52324,25 +52324,25 @@
         <v>1</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999549114</v>
+        <v>0.9999999999549111</v>
       </c>
       <c r="CO265" s="103" t="n">
-        <v>1.000000000056472</v>
+        <v>1.000000000056473</v>
       </c>
       <c r="CP265" s="103" t="n">
-        <v>1.000000000028841</v>
+        <v>1.00000000002884</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.9999999999490421</v>
+        <v>0.9999999999490427</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.9999999999532596</v>
+        <v>0.9999999999532594</v>
       </c>
       <c r="CT265" s="396" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU265" s="397" t="n">
         <v>0.9999999999999999</v>
-      </c>
-      <c r="CU265" s="397" t="n">
-        <v>1</v>
       </c>
       <c r="CV265" s="397" t="n">
         <v>1</v>
@@ -52354,19 +52354,19 @@
         <v>1</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.000000000002534</v>
+        <v>1.000000000002533</v>
       </c>
       <c r="CZ265" s="103" t="n">
-        <v>0.9999999999986157</v>
+        <v>0.999999999998616</v>
       </c>
       <c r="DA265" s="103" t="n">
-        <v>0.9999999999996826</v>
+        <v>0.9999999999996825</v>
       </c>
       <c r="DB265" s="103" t="n">
         <v>1.000000000000836</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>1.000000000001393</v>
+        <v>1.000000000001392</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,19 +52384,19 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>49357.38537389892</v>
+        <v>49357.38537389891</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>48368.75020661164</v>
       </c>
       <c r="DM265" s="375" t="n">
-        <v>51410.76756075159</v>
+        <v>51410.76756075161</v>
       </c>
       <c r="DN265" s="375" t="n">
         <v>53321.84510118968</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>57463.98155087595</v>
+        <v>57463.98155087593</v>
       </c>
     </row>
     <row r="266">
@@ -52482,7 +52482,7 @@
         <v>158473.1245926057</v>
       </c>
       <c r="AM266" s="368" t="n">
-        <v>182579.175577938</v>
+        <v>182579.1755779381</v>
       </c>
       <c r="AN266" s="368" t="n">
         <v>211939.3794528705</v>
@@ -52491,19 +52491,19 @@
         <v>231893.8870371914</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143917</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2402.811430046145</v>
+        <v>2402.811430046144</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2527.232856000696</v>
+        <v>2527.232856000699</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2668.638025259987</v>
+        <v>2668.638025259988</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266797</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52517,7 +52517,7 @@
         <v>158473.1245926057</v>
       </c>
       <c r="BD266" s="375" t="n">
-        <v>182579.175577938</v>
+        <v>182579.1755779381</v>
       </c>
       <c r="BE266" s="375" t="n">
         <v>211939.3794528705</v>
@@ -52526,19 +52526,19 @@
         <v>231893.8870371914</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143917</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2402.811430046145</v>
+        <v>2402.811430046144</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2527.232856000696</v>
+        <v>2527.232856000699</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2668.638025259987</v>
+        <v>2668.638025259988</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266797</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52546,13 +52546,13 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>135589.6591281345</v>
+        <v>135589.6591281344</v>
       </c>
       <c r="BT266" s="375" t="n">
         <v>158282.7189180313</v>
       </c>
       <c r="BU266" s="375" t="n">
-        <v>182379.2526559911</v>
+        <v>182379.2526559912</v>
       </c>
       <c r="BV266" s="375" t="n">
         <v>211727.4985165998</v>
@@ -52561,19 +52561,19 @@
         <v>231666.4778947156</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2275.168462143915</v>
+        <v>2275.168462143917</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2402.811430046145</v>
+        <v>2402.811430046144</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2527.232856000696</v>
+        <v>2527.232856000699</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2668.638025259987</v>
+        <v>2668.638025259988</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2877.835402266795</v>
+        <v>2877.835402266797</v>
       </c>
       <c r="CI266" s="396" t="n">
         <v>1</v>
@@ -52597,7 +52597,7 @@
         <v>1.00000000000128</v>
       </c>
       <c r="CP266" s="103" t="n">
-        <v>0.9999999999936122</v>
+        <v>0.9999999999936114</v>
       </c>
       <c r="CQ266" s="103" t="n">
         <v>0.9999999999958892</v>
@@ -52621,13 +52621,13 @@
         <v>1</v>
       </c>
       <c r="CY266" s="102" t="n">
-        <v>0.9999999999982733</v>
+        <v>0.9999999999982732</v>
       </c>
       <c r="CZ266" s="103" t="n">
         <v>1.000000000001832</v>
       </c>
       <c r="DA266" s="103" t="n">
-        <v>1.00000000000026</v>
+        <v>1.000000000000259</v>
       </c>
       <c r="DB266" s="103" t="n">
         <v>1.000000000000489</v>
@@ -52743,7 +52743,7 @@
         </is>
       </c>
       <c r="AK267" s="435" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="AL267" s="408" t="n">
         <v>11640.0026023282</v>
@@ -52755,22 +52755,22 @@
         <v>13606.04680805828</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>14635.09201340936</v>
+        <v>14635.09201340942</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>2476.336292449053</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>2613.215769440583</v>
+        <v>2613.215769440581</v>
       </c>
       <c r="AR267" s="411" t="n">
-        <v>2756.189783077294</v>
+        <v>2756.189783077295</v>
       </c>
       <c r="AS267" s="411" t="n">
         <v>2905.582056784455</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>3063.213504382679</v>
+        <v>3063.213504382689</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         </is>
       </c>
       <c r="BB267" s="419" t="n">
-        <v>10750.991903933</v>
+        <v>10750.99190393288</v>
       </c>
       <c r="BC267" s="420" t="n">
         <v>11640.0026023282</v>
@@ -52790,22 +52790,22 @@
         <v>13606.04680805828</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>14635.09201340936</v>
+        <v>14635.09201340942</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>2476.336292449053</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>2613.215769440583</v>
+        <v>2613.215769440581</v>
       </c>
       <c r="BI267" s="417" t="n">
-        <v>2756.189783077294</v>
+        <v>2756.189783077295</v>
       </c>
       <c r="BJ267" s="417" t="n">
         <v>2905.582056784455</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>3063.213504382679</v>
+        <v>3063.213504382689</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>10720.11604629892</v>
+        <v>10720.1160462988</v>
       </c>
       <c r="BT267" s="420" t="n">
         <v>11606.57358792457</v>
@@ -52825,22 +52825,22 @@
         <v>13566.97149594177</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>14593.06137832885</v>
+        <v>14593.06137832892</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>2476.336292449053</v>
+        <v>2476.336292449026</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>2613.215769440583</v>
+        <v>2613.215769440581</v>
       </c>
       <c r="BZ267" s="417" t="n">
-        <v>2756.189783077294</v>
+        <v>2756.189783077295</v>
       </c>
       <c r="CA267" s="417" t="n">
         <v>2905.582056784455</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>3063.213504382679</v>
+        <v>3063.213504382689</v>
       </c>
       <c r="CI267" s="422" t="n">
         <v>1</v>
@@ -52858,10 +52858,10 @@
         <v>1</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>0.9999999999587359</v>
+        <v>0.9999999999587467</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>0.9999999999655748</v>
+        <v>0.9999999999655745</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>1.000000000207868</v>
@@ -52870,7 +52870,7 @@
         <v>1.000000000152355</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>0.9999999997045332</v>
+        <v>0.9999999997045295</v>
       </c>
       <c r="CT267" s="422" t="n">
         <v>0.9999999999999999</v>
@@ -52900,7 +52900,7 @@
         <v>0.9999999999998599</v>
       </c>
       <c r="DC267" s="134" t="n">
-        <v>0.9999999999990653</v>
+        <v>0.9999999999990654</v>
       </c>
       <c r="DE267" s="419" t="n">
         <v>0</v>
@@ -52921,7 +52921,7 @@
         <v>8916.232863165696</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>9666.763954628112</v>
+        <v>9666.76395462811</v>
       </c>
       <c r="DM267" s="420" t="n">
         <v>10532.06230041419</v>
@@ -53010,19 +53010,19 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>271509.1575487817</v>
+        <v>271509.1575487816</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>289289.6333511515</v>
+        <v>289289.6333511514</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>318631.6100773186</v>
+        <v>318631.6100773187</v>
       </c>
       <c r="AN268" s="408" t="n">
         <v>346535.2748692394</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>373629.4515146997</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="AP268" s="436" t="n">
         <v>1710.409888945677</v>
@@ -53031,13 +53031,13 @@
         <v>1931.923636718967</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>2111.032821615892</v>
+        <v>2111.032821615893</v>
       </c>
       <c r="AS268" s="437" t="n">
-        <v>2306.748102003335</v>
+        <v>2306.748102003336</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2454.067902507688</v>
+        <v>2454.067902507689</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53045,19 +53045,19 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>271509.1575487817</v>
+        <v>271509.1575487816</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>289289.6333511515</v>
+        <v>289289.6333511514</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>318631.6100773186</v>
+        <v>318631.6100773187</v>
       </c>
       <c r="BE268" s="440" t="n">
         <v>346535.2748692394</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>373629.4515146997</v>
+        <v>373629.4515146998</v>
       </c>
       <c r="BG268" s="442" t="n">
         <v>1710.409888945677</v>
@@ -53066,13 +53066,13 @@
         <v>1931.923636718967</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>2111.032821615892</v>
+        <v>2111.032821615893</v>
       </c>
       <c r="BJ268" s="443" t="n">
-        <v>2306.748102003335</v>
+        <v>2306.748102003336</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2454.067902507688</v>
+        <v>2454.067902507689</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,34 +53080,34 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>270440.7553835661</v>
+        <v>270440.755383566</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>288219.2467030785</v>
+        <v>288219.2467030784</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>317475.3423631049</v>
+        <v>317475.3423631051</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>345320.8008862816</v>
+        <v>345320.8008862815</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>372425.5141640326</v>
+        <v>372425.5141640328</v>
       </c>
       <c r="BX268" s="442" t="n">
         <v>1712.745582646399</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>1934.508288023923</v>
+        <v>1934.508288023922</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>2113.797190408818</v>
+        <v>2113.797190408819</v>
       </c>
       <c r="CA268" s="443" t="n">
         <v>2309.829724127111</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2457.482712287762</v>
+        <v>2457.482712287764</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,16 +53125,16 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>224374.2119632446</v>
+        <v>224374.2119632445</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>240079.7999561946</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>265937.1538292894</v>
+        <v>265937.1538292895</v>
       </c>
       <c r="DN268" s="440" t="n">
-        <v>289561.3047971948</v>
+        <v>289561.3047971947</v>
       </c>
       <c r="DO268" s="441" t="n">
         <v>309619.9738031465</v>
@@ -54056,22 +54056,22 @@
         <v>114.6289552489976</v>
       </c>
       <c r="AO276" s="195" t="n">
-        <v>128.5014827135569</v>
+        <v>128.5014827135568</v>
       </c>
       <c r="AP276" s="194" t="n">
         <v>104.4365967359875</v>
       </c>
       <c r="AQ276" s="179" t="n">
-        <v>105.5672075584585</v>
+        <v>105.5672075584586</v>
       </c>
       <c r="AR276" s="179" t="n">
         <v>102.2313269926236</v>
       </c>
       <c r="AS276" s="179" t="n">
-        <v>99.20268881209786</v>
+        <v>99.20268881209785</v>
       </c>
       <c r="AT276" s="195" t="n">
-        <v>89.68714935167566</v>
+        <v>89.68714935167564</v>
       </c>
       <c r="AU276" s="190" t="n">
         <v>120.2436157232417</v>
@@ -54106,22 +54106,22 @@
         <v>114.6289552489976</v>
       </c>
       <c r="BF276" s="198" t="n">
-        <v>128.5014827135569</v>
+        <v>128.5014827135568</v>
       </c>
       <c r="BG276" s="197" t="n">
         <v>104.4365967359875</v>
       </c>
       <c r="BH276" s="190" t="n">
-        <v>105.5672075584585</v>
+        <v>105.5672075584586</v>
       </c>
       <c r="BI276" s="190" t="n">
         <v>102.2313269926236</v>
       </c>
       <c r="BJ276" s="190" t="n">
-        <v>99.20268881209786</v>
+        <v>99.20268881209785</v>
       </c>
       <c r="BK276" s="198" t="n">
-        <v>89.68714935167566</v>
+        <v>89.68714935167564</v>
       </c>
       <c r="BL276" s="199" t="n">
         <v>120.2436157232417</v>
@@ -54156,7 +54156,7 @@
         <v>113.5597970286921</v>
       </c>
       <c r="BW276" s="198" t="n">
-        <v>127.1923509211655</v>
+        <v>127.1923509211654</v>
       </c>
       <c r="BX276" s="197" t="n">
         <v>105.3225227561658</v>
@@ -54171,19 +54171,19 @@
         <v>100.81808537262</v>
       </c>
       <c r="CB276" s="198" t="n">
-        <v>91.52947777942926</v>
+        <v>91.52947777942924</v>
       </c>
       <c r="CC276" s="199" t="n">
         <v>120.8890545119735</v>
       </c>
       <c r="CD276" s="200" t="n">
-        <v>160.5993459227723</v>
+        <v>160.5993459227724</v>
       </c>
       <c r="CE276" s="200" t="n">
         <v>200.5711342551427</v>
       </c>
       <c r="CF276" s="200" t="n">
-        <v>214.377882401312</v>
+        <v>214.3778824013121</v>
       </c>
       <c r="CG276" s="201" t="n">
         <v>218.7218287005947</v>
@@ -54324,13 +54324,13 @@
         </is>
       </c>
       <c r="AK277" s="194" t="n">
-        <v>27.10789901090662</v>
+        <v>27.10789901090663</v>
       </c>
       <c r="AL277" s="179" t="n">
         <v>49.5825520157382</v>
       </c>
       <c r="AM277" s="179" t="n">
-        <v>67.83338551434515</v>
+        <v>67.83338551434517</v>
       </c>
       <c r="AN277" s="179" t="n">
         <v>74.47154139200721</v>
@@ -54348,13 +54348,13 @@
         <v>68.27813854510515</v>
       </c>
       <c r="AS277" s="179" t="n">
-        <v>67.90742542298955</v>
+        <v>67.90742542298956</v>
       </c>
       <c r="AT277" s="195" t="n">
-        <v>66.91452623491826</v>
+        <v>66.91452623491827</v>
       </c>
       <c r="AU277" s="190" t="n">
-        <v>96.30817571377783</v>
+        <v>96.30817571377784</v>
       </c>
       <c r="AV277" s="190" t="n">
         <v>118.904066587265</v>
@@ -54374,13 +54374,13 @@
         </is>
       </c>
       <c r="BB277" s="197" t="n">
-        <v>27.10789901090662</v>
+        <v>27.10789901090663</v>
       </c>
       <c r="BC277" s="190" t="n">
         <v>49.5825520157382</v>
       </c>
       <c r="BD277" s="190" t="n">
-        <v>67.83338551434515</v>
+        <v>67.83338551434517</v>
       </c>
       <c r="BE277" s="190" t="n">
         <v>74.47154139200721</v>
@@ -54398,13 +54398,13 @@
         <v>68.27813854510515</v>
       </c>
       <c r="BJ277" s="190" t="n">
-        <v>67.90742542298955</v>
+        <v>67.90742542298956</v>
       </c>
       <c r="BK277" s="198" t="n">
-        <v>66.91452623491826</v>
+        <v>66.91452623491827</v>
       </c>
       <c r="BL277" s="197" t="n">
-        <v>96.30817571377783</v>
+        <v>96.30817571377784</v>
       </c>
       <c r="BM277" s="190" t="n">
         <v>118.904066587265</v>
@@ -54430,7 +54430,7 @@
         <v>49.22583981597641</v>
       </c>
       <c r="BU277" s="190" t="n">
-        <v>67.28893941810735</v>
+        <v>67.28893941810736</v>
       </c>
       <c r="BV277" s="190" t="n">
         <v>73.75964655793223</v>
@@ -54448,13 +54448,13 @@
         <v>68.91047548643553</v>
       </c>
       <c r="CA277" s="190" t="n">
-        <v>68.70644457234684</v>
+        <v>68.70644457234685</v>
       </c>
       <c r="CB277" s="198" t="n">
-        <v>67.87055345512762</v>
+        <v>67.87055345512763</v>
       </c>
       <c r="CC277" s="197" t="n">
-        <v>96.41187714124376</v>
+        <v>96.41187714124378</v>
       </c>
       <c r="CD277" s="190" t="n">
         <v>118.9916020599283</v>
@@ -54625,13 +54625,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="AR278" s="179" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778421</v>
       </c>
       <c r="AS278" s="179" t="n">
         <v>85.27800681733346</v>
       </c>
       <c r="AT278" s="195" t="n">
-        <v>84.87934076273498</v>
+        <v>84.87934076273497</v>
       </c>
       <c r="AU278" s="190" t="n">
         <v>118.5676032367616</v>
@@ -54646,7 +54646,7 @@
         <v>142.3435694709199</v>
       </c>
       <c r="AY278" s="196" t="n">
-        <v>153.1929817606721</v>
+        <v>153.192981760672</v>
       </c>
       <c r="BA278" s="111" t="inlineStr">
         <is>
@@ -54675,13 +54675,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="BI278" s="190" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778421</v>
       </c>
       <c r="BJ278" s="190" t="n">
         <v>85.27800681733346</v>
       </c>
       <c r="BK278" s="198" t="n">
-        <v>84.87934076273498</v>
+        <v>84.87934076273497</v>
       </c>
       <c r="BL278" s="197" t="n">
         <v>118.5676032367616</v>
@@ -54696,7 +54696,7 @@
         <v>142.3435694709199</v>
       </c>
       <c r="BP278" s="198" t="n">
-        <v>153.1929817606721</v>
+        <v>153.192981760672</v>
       </c>
       <c r="BR278" s="111" t="inlineStr">
         <is>
@@ -54725,13 +54725,13 @@
         <v>100.5549145594557</v>
       </c>
       <c r="BZ278" s="190" t="n">
-        <v>95.66368651665945</v>
+        <v>95.66368651665944</v>
       </c>
       <c r="CA278" s="190" t="n">
         <v>86.06912132105927</v>
       </c>
       <c r="CB278" s="198" t="n">
-        <v>85.87751955292958</v>
+        <v>85.87751955292957</v>
       </c>
       <c r="CC278" s="197" t="n">
         <v>118.6462644634676</v>
@@ -54890,13 +54890,13 @@
         <v>7.015258528875047</v>
       </c>
       <c r="AM279" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN279" s="207" t="n">
         <v>17.11580126467504</v>
       </c>
       <c r="AO279" s="208" t="n">
-        <v>17.86531224755395</v>
+        <v>17.86531224755396</v>
       </c>
       <c r="AP279" s="206" t="n">
         <v>23.37206383069039</v>
@@ -54940,13 +54940,13 @@
         <v>7.015258528875047</v>
       </c>
       <c r="BD279" s="212" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE279" s="212" t="n">
         <v>17.11580126467504</v>
       </c>
       <c r="BF279" s="213" t="n">
-        <v>17.86531224755395</v>
+        <v>17.86531224755396</v>
       </c>
       <c r="BG279" s="211" t="n">
         <v>23.37206383069039</v>
@@ -54990,7 +54990,7 @@
         <v>6.926441119872522</v>
       </c>
       <c r="BU279" s="212" t="n">
-        <v>13.47010685860509</v>
+        <v>13.47010685860508</v>
       </c>
       <c r="BV279" s="212" t="n">
         <v>16.95867784830281</v>
@@ -55005,7 +55005,7 @@
         <v>22.69215417114072</v>
       </c>
       <c r="BZ279" s="212" t="n">
-        <v>17.11384959082983</v>
+        <v>17.11384959082982</v>
       </c>
       <c r="CA279" s="212" t="n">
         <v>14.47945378566209</v>
@@ -55164,19 +55164,19 @@
         </is>
       </c>
       <c r="AK280" s="206" t="n">
-        <v>64.90820670948202</v>
+        <v>64.90820670948203</v>
       </c>
       <c r="AL280" s="207" t="n">
         <v>139.6623002618839</v>
       </c>
       <c r="AM280" s="207" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="AN280" s="207" t="n">
-        <v>263.2818605592662</v>
+        <v>263.2818605592663</v>
       </c>
       <c r="AO280" s="208" t="n">
-        <v>294.5160029551957</v>
+        <v>294.5160029551956</v>
       </c>
       <c r="AP280" s="206" t="n">
         <v>299.0305946717849</v>
@@ -55194,10 +55194,10 @@
         <v>255.9935468178305</v>
       </c>
       <c r="AU280" s="207" t="n">
-        <v>363.9388013812669</v>
+        <v>363.938801381267</v>
       </c>
       <c r="AV280" s="207" t="n">
-        <v>437.2311513220611</v>
+        <v>437.2311513220612</v>
       </c>
       <c r="AW280" s="207" t="n">
         <v>506.0348073243434</v>
@@ -55206,7 +55206,7 @@
         <v>529.9788636214563</v>
       </c>
       <c r="AY280" s="208" t="n">
-        <v>550.5095497730263</v>
+        <v>550.5095497730262</v>
       </c>
       <c r="BA280" s="155" t="inlineStr">
         <is>
@@ -55214,19 +55214,19 @@
         </is>
       </c>
       <c r="BB280" s="221" t="n">
-        <v>64.90820670948202</v>
+        <v>64.90820670948203</v>
       </c>
       <c r="BC280" s="222" t="n">
         <v>139.6623002618839</v>
       </c>
       <c r="BD280" s="222" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="BE280" s="222" t="n">
-        <v>263.2818605592662</v>
+        <v>263.2818605592663</v>
       </c>
       <c r="BF280" s="214" t="n">
-        <v>294.5160029551957</v>
+        <v>294.5160029551956</v>
       </c>
       <c r="BG280" s="221" t="n">
         <v>299.0305946717849</v>
@@ -55244,10 +55244,10 @@
         <v>255.9935468178305</v>
       </c>
       <c r="BL280" s="222" t="n">
-        <v>363.9388013812669</v>
+        <v>363.938801381267</v>
       </c>
       <c r="BM280" s="222" t="n">
-        <v>437.2311513220611</v>
+        <v>437.2311513220612</v>
       </c>
       <c r="BN280" s="222" t="n">
         <v>506.0348073243434</v>
@@ -55256,7 +55256,7 @@
         <v>529.9788636214563</v>
       </c>
       <c r="BP280" s="214" t="n">
-        <v>550.5095497730263</v>
+        <v>550.5095497730262</v>
       </c>
       <c r="BR280" s="155" t="inlineStr">
         <is>
@@ -55273,19 +55273,19 @@
         <v>221.4956204181795</v>
       </c>
       <c r="BV280" s="222" t="n">
-        <v>260.6319662411589</v>
+        <v>260.631966241159</v>
       </c>
       <c r="BW280" s="214" t="n">
-        <v>291.2129456565576</v>
+        <v>291.2129456565575</v>
       </c>
       <c r="BX280" s="221" t="n">
         <v>300.5987420795748</v>
       </c>
       <c r="BY280" s="222" t="n">
-        <v>299.6339229701409</v>
+        <v>299.633922970141</v>
       </c>
       <c r="BZ280" s="222" t="n">
-        <v>285.2835873078872</v>
+        <v>285.2835873078871</v>
       </c>
       <c r="CA280" s="222" t="n">
         <v>270.0731050516882</v>
@@ -55297,10 +55297,10 @@
         <v>364.7790711862943</v>
       </c>
       <c r="CD280" s="222" t="n">
-        <v>437.9845297780586</v>
+        <v>437.9845297780587</v>
       </c>
       <c r="CE280" s="222" t="n">
-        <v>506.7792077260667</v>
+        <v>506.7792077260666</v>
       </c>
       <c r="CF280" s="222" t="n">
         <v>530.7050712928472</v>
@@ -58303,22 +58303,22 @@
         <v>114.6289552489976</v>
       </c>
       <c r="AO294" s="195" t="n">
-        <v>128.5014827135569</v>
+        <v>128.5014827135568</v>
       </c>
       <c r="AP294" s="194" t="n">
         <v>104.4365967359875</v>
       </c>
       <c r="AQ294" s="179" t="n">
-        <v>105.5672075584585</v>
+        <v>105.5672075584586</v>
       </c>
       <c r="AR294" s="179" t="n">
         <v>102.2313269926236</v>
       </c>
       <c r="AS294" s="179" t="n">
-        <v>99.20268881209786</v>
+        <v>99.20268881209785</v>
       </c>
       <c r="AT294" s="195" t="n">
-        <v>89.68714935167566</v>
+        <v>89.68714935167564</v>
       </c>
       <c r="AU294" s="190" t="n">
         <v>120.2436157232417</v>
@@ -58353,22 +58353,22 @@
         <v>114.6289552489976</v>
       </c>
       <c r="BF294" s="198" t="n">
-        <v>128.5014827135569</v>
+        <v>128.5014827135568</v>
       </c>
       <c r="BG294" s="197" t="n">
         <v>104.4365967359875</v>
       </c>
       <c r="BH294" s="190" t="n">
-        <v>105.5672075584585</v>
+        <v>105.5672075584586</v>
       </c>
       <c r="BI294" s="190" t="n">
         <v>102.2313269926236</v>
       </c>
       <c r="BJ294" s="190" t="n">
-        <v>99.20268881209786</v>
+        <v>99.20268881209785</v>
       </c>
       <c r="BK294" s="198" t="n">
-        <v>89.68714935167566</v>
+        <v>89.68714935167564</v>
       </c>
       <c r="BL294" s="199" t="n">
         <v>120.2436157232417</v>
@@ -58403,7 +58403,7 @@
         <v>113.5597970286921</v>
       </c>
       <c r="BW294" s="198" t="n">
-        <v>127.1923509211655</v>
+        <v>127.1923509211654</v>
       </c>
       <c r="BX294" s="197" t="n">
         <v>105.3225227561658</v>
@@ -58418,7 +58418,7 @@
         <v>100.81808537262</v>
       </c>
       <c r="CB294" s="198" t="n">
-        <v>91.52947777942927</v>
+        <v>91.52947777942926</v>
       </c>
       <c r="CC294" s="199" t="n">
         <v>120.8890545119735</v>
@@ -58430,10 +58430,10 @@
         <v>200.5711342551427</v>
       </c>
       <c r="CF294" s="200" t="n">
-        <v>214.377882401312</v>
+        <v>214.3778824013121</v>
       </c>
       <c r="CG294" s="201" t="n">
-        <v>218.7218287005948</v>
+        <v>218.7218287005947</v>
       </c>
       <c r="CI294" s="199" t="n">
         <v>0</v>
@@ -58469,7 +58469,7 @@
         <v>0.5738078228343186</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5642210685925357</v>
+        <v>0.5642210685925358</v>
       </c>
       <c r="CZ294" s="200" t="n">
         <v>0.5462383402166368</v>
@@ -58586,13 +58586,13 @@
         </is>
       </c>
       <c r="AK295" s="194" t="n">
-        <v>27.10789901090662</v>
+        <v>27.10789901090663</v>
       </c>
       <c r="AL295" s="179" t="n">
         <v>49.5825520157382</v>
       </c>
       <c r="AM295" s="179" t="n">
-        <v>67.83338551434515</v>
+        <v>67.83338551434517</v>
       </c>
       <c r="AN295" s="179" t="n">
         <v>74.47154139200721</v>
@@ -58610,13 +58610,13 @@
         <v>68.27813854510515</v>
       </c>
       <c r="AS295" s="179" t="n">
-        <v>67.90742542298955</v>
+        <v>67.90742542298956</v>
       </c>
       <c r="AT295" s="195" t="n">
-        <v>66.91452623491826</v>
+        <v>66.91452623491827</v>
       </c>
       <c r="AU295" s="190" t="n">
-        <v>96.30817571377783</v>
+        <v>96.30817571377784</v>
       </c>
       <c r="AV295" s="190" t="n">
         <v>118.904066587265</v>
@@ -58636,13 +58636,13 @@
         </is>
       </c>
       <c r="BB295" s="197" t="n">
-        <v>27.10789901090662</v>
+        <v>27.10789901090663</v>
       </c>
       <c r="BC295" s="190" t="n">
         <v>49.5825520157382</v>
       </c>
       <c r="BD295" s="190" t="n">
-        <v>67.83338551434515</v>
+        <v>67.83338551434517</v>
       </c>
       <c r="BE295" s="190" t="n">
         <v>74.47154139200721</v>
@@ -58660,13 +58660,13 @@
         <v>68.27813854510515</v>
       </c>
       <c r="BJ295" s="190" t="n">
-        <v>67.90742542298955</v>
+        <v>67.90742542298956</v>
       </c>
       <c r="BK295" s="198" t="n">
-        <v>66.91452623491826</v>
+        <v>66.91452623491827</v>
       </c>
       <c r="BL295" s="197" t="n">
-        <v>96.30817571377783</v>
+        <v>96.30817571377784</v>
       </c>
       <c r="BM295" s="190" t="n">
         <v>118.904066587265</v>
@@ -58692,7 +58692,7 @@
         <v>49.22583981597641</v>
       </c>
       <c r="BU295" s="190" t="n">
-        <v>67.28893941810735</v>
+        <v>67.28893941810736</v>
       </c>
       <c r="BV295" s="190" t="n">
         <v>73.75964655793223</v>
@@ -58710,13 +58710,13 @@
         <v>68.91047548643553</v>
       </c>
       <c r="CA295" s="190" t="n">
-        <v>68.70644457234684</v>
+        <v>68.70644457234685</v>
       </c>
       <c r="CB295" s="198" t="n">
-        <v>67.87055345512762</v>
+        <v>67.87055345512763</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>96.41187714124376</v>
+        <v>96.41187714124378</v>
       </c>
       <c r="CD295" s="190" t="n">
         <v>118.9916020599283</v>
@@ -58761,16 +58761,16 @@
         <v>0.1037014274659339</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>0.08753547266332017</v>
+        <v>0.08753547266332018</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>0.08789084509257697</v>
+        <v>0.08789084509257702</v>
       </c>
       <c r="CZ295" s="190" t="n">
         <v>0.08712431528231337</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>0.07552666082297217</v>
+        <v>0.07552666082297213</v>
       </c>
     </row>
     <row r="296">
@@ -58902,13 +58902,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="AR296" s="179" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778421</v>
       </c>
       <c r="AS296" s="179" t="n">
         <v>85.27800681733346</v>
       </c>
       <c r="AT296" s="195" t="n">
-        <v>84.87934076273498</v>
+        <v>84.87934076273497</v>
       </c>
       <c r="AU296" s="190" t="n">
         <v>118.5676032367616</v>
@@ -58923,7 +58923,7 @@
         <v>142.3435694709199</v>
       </c>
       <c r="AY296" s="196" t="n">
-        <v>153.1929817606721</v>
+        <v>153.192981760672</v>
       </c>
       <c r="BA296" s="111" t="inlineStr">
         <is>
@@ -58952,13 +58952,13 @@
         <v>100.0895844582254</v>
       </c>
       <c r="BI296" s="190" t="n">
-        <v>95.02719669778422</v>
+        <v>95.02719669778421</v>
       </c>
       <c r="BJ296" s="190" t="n">
         <v>85.27800681733346</v>
       </c>
       <c r="BK296" s="198" t="n">
-        <v>84.87934076273498</v>
+        <v>84.87934076273497</v>
       </c>
       <c r="BL296" s="197" t="n">
         <v>118.5676032367616</v>
@@ -58973,7 +58973,7 @@
         <v>142.3435694709199</v>
       </c>
       <c r="BP296" s="198" t="n">
-        <v>153.1929817606721</v>
+        <v>153.192981760672</v>
       </c>
       <c r="BR296" s="111" t="inlineStr">
         <is>
@@ -58996,19 +58996,19 @@
         <v>67.39448310737303</v>
       </c>
       <c r="BX296" s="197" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="BY296" s="190" t="n">
         <v>100.5549145594557</v>
       </c>
       <c r="BZ296" s="190" t="n">
-        <v>95.66368651665945</v>
+        <v>95.66368651665944</v>
       </c>
       <c r="CA296" s="190" t="n">
         <v>86.06912132105927</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>85.87751955292958</v>
+        <v>85.87751955292957</v>
       </c>
       <c r="CC296" s="197" t="n">
         <v>118.6462644634676</v>
@@ -59182,13 +59182,13 @@
         <v>7.015258528875047</v>
       </c>
       <c r="AM297" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN297" s="207" t="n">
         <v>17.11580126467504</v>
       </c>
       <c r="AO297" s="208" t="n">
-        <v>17.86531224755395</v>
+        <v>17.86531224755396</v>
       </c>
       <c r="AP297" s="206" t="n">
         <v>23.37206383069039</v>
@@ -59232,13 +59232,13 @@
         <v>7.015258528875047</v>
       </c>
       <c r="BD297" s="212" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE297" s="212" t="n">
         <v>17.11580126467504</v>
       </c>
       <c r="BF297" s="213" t="n">
-        <v>17.86531224755395</v>
+        <v>17.86531224755396</v>
       </c>
       <c r="BG297" s="211" t="n">
         <v>23.37206383069039</v>
@@ -59282,7 +59282,7 @@
         <v>6.926441119872522</v>
       </c>
       <c r="BU297" s="212" t="n">
-        <v>13.47010685860509</v>
+        <v>13.47010685860508</v>
       </c>
       <c r="BV297" s="212" t="n">
         <v>16.95867784830281</v>
@@ -59297,7 +59297,7 @@
         <v>22.69215417114072</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>17.11384959082983</v>
+        <v>17.11384959082982</v>
       </c>
       <c r="CA297" s="212" t="n">
         <v>14.47945378566209</v>
@@ -59306,7 +59306,7 @@
         <v>14.72051861704975</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>28.83187506960942</v>
+        <v>28.83187506960943</v>
       </c>
       <c r="CD297" s="212" t="n">
         <v>29.61859529101324</v>
@@ -59348,19 +59348,19 @@
         <v>1566</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.01246836212360534</v>
+        <v>0.0124683621236049</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.01279229017157661</v>
+        <v>0.01279229017157616</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.01318104786989082</v>
+        <v>0.01318104786989036</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.0134483595206922</v>
+        <v>0.01344835952069173</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.01372109225177185</v>
+        <v>0.01372109225177136</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59471,19 +59471,19 @@
         </is>
       </c>
       <c r="AK298" s="206" t="n">
-        <v>64.90820670948202</v>
+        <v>64.90820670948203</v>
       </c>
       <c r="AL298" s="207" t="n">
         <v>139.6623002618839</v>
       </c>
       <c r="AM298" s="207" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="AN298" s="207" t="n">
-        <v>263.2818605592662</v>
+        <v>263.2818605592663</v>
       </c>
       <c r="AO298" s="208" t="n">
-        <v>294.5160029551957</v>
+        <v>294.5160029551956</v>
       </c>
       <c r="AP298" s="206" t="n">
         <v>299.0305946717849</v>
@@ -59501,10 +59501,10 @@
         <v>255.9935468178305</v>
       </c>
       <c r="AU298" s="207" t="n">
-        <v>363.9388013812669</v>
+        <v>363.938801381267</v>
       </c>
       <c r="AV298" s="207" t="n">
-        <v>437.2311513220611</v>
+        <v>437.2311513220612</v>
       </c>
       <c r="AW298" s="207" t="n">
         <v>506.0348073243434</v>
@@ -59513,7 +59513,7 @@
         <v>529.9788636214563</v>
       </c>
       <c r="AY298" s="208" t="n">
-        <v>550.5095497730263</v>
+        <v>550.5095497730262</v>
       </c>
       <c r="BA298" s="155" t="inlineStr">
         <is>
@@ -59521,19 +59521,19 @@
         </is>
       </c>
       <c r="BB298" s="221" t="n">
-        <v>64.90820670948202</v>
+        <v>64.90820670948203</v>
       </c>
       <c r="BC298" s="222" t="n">
         <v>139.6623002618839</v>
       </c>
       <c r="BD298" s="222" t="n">
-        <v>223.5197596474768</v>
+        <v>223.5197596474769</v>
       </c>
       <c r="BE298" s="222" t="n">
-        <v>263.2818605592662</v>
+        <v>263.2818605592663</v>
       </c>
       <c r="BF298" s="214" t="n">
-        <v>294.5160029551957</v>
+        <v>294.5160029551956</v>
       </c>
       <c r="BG298" s="221" t="n">
         <v>299.0305946717849</v>
@@ -59551,10 +59551,10 @@
         <v>255.9935468178305</v>
       </c>
       <c r="BL298" s="222" t="n">
-        <v>363.9388013812669</v>
+        <v>363.938801381267</v>
       </c>
       <c r="BM298" s="222" t="n">
-        <v>437.2311513220611</v>
+        <v>437.2311513220612</v>
       </c>
       <c r="BN298" s="222" t="n">
         <v>506.0348073243434</v>
@@ -59563,7 +59563,7 @@
         <v>529.9788636214563</v>
       </c>
       <c r="BP298" s="214" t="n">
-        <v>550.5095497730263</v>
+        <v>550.5095497730262</v>
       </c>
       <c r="BR298" s="155" t="inlineStr">
         <is>
@@ -59580,19 +59580,19 @@
         <v>221.4956204181795</v>
       </c>
       <c r="BV298" s="222" t="n">
-        <v>260.6319662411589</v>
+        <v>260.631966241159</v>
       </c>
       <c r="BW298" s="214" t="n">
-        <v>291.2129456565576</v>
+        <v>291.2129456565575</v>
       </c>
       <c r="BX298" s="221" t="n">
         <v>300.5987420795748</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>299.6339229701409</v>
+        <v>299.633922970141</v>
       </c>
       <c r="BZ298" s="222" t="n">
-        <v>285.2835873078872</v>
+        <v>285.2835873078871</v>
       </c>
       <c r="CA298" s="222" t="n">
         <v>270.0731050516882</v>
@@ -59601,10 +59601,10 @@
         <v>259.9980694045362</v>
       </c>
       <c r="CC298" s="222" t="n">
-        <v>364.7790711862942</v>
+        <v>364.7790711862943</v>
       </c>
       <c r="CD298" s="222" t="n">
-        <v>437.9845297780586</v>
+        <v>437.9845297780587</v>
       </c>
       <c r="CE298" s="222" t="n">
         <v>506.7792077260666</v>
@@ -59643,19 +59643,19 @@
         <v>17676</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>0.8402698050273316</v>
+        <v>0.8402698050273312</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7533784559974738</v>
+        <v>0.7533784559974733</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.7444004017231201</v>
+        <v>0.7444004017231198</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.726207671390843</v>
+        <v>0.7262076713908425</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.7014652880675245</v>
+        <v>0.7014652880675241</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60449,7 +60449,7 @@
         <v>100.2718470324033</v>
       </c>
       <c r="AY303" s="196" t="n">
-        <v>90.99628114406705</v>
+        <v>90.99628114406704</v>
       </c>
       <c r="BA303" s="83" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>100.2718470324033</v>
       </c>
       <c r="BP303" s="201" t="n">
-        <v>90.99628114406705</v>
+        <v>90.99628114406704</v>
       </c>
       <c r="BR303" s="83" t="inlineStr">
         <is>
@@ -60531,16 +60531,16 @@
         <v>0.0776010247917919</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>0.06265916910334453</v>
+        <v>0.06265916910334454</v>
       </c>
       <c r="CB303" s="464" t="n">
-        <v>-0.00589407975925149</v>
+        <v>-0.005894079759251491</v>
       </c>
       <c r="CC303" s="199" t="n">
         <v>7.181997748466757</v>
       </c>
       <c r="CD303" s="200" t="n">
-        <v>7.622411855860019</v>
+        <v>7.622411855860021</v>
       </c>
       <c r="CE303" s="200" t="n">
         <v>8.039122839299147</v>
@@ -60674,13 +60674,13 @@
         <v>0.006</v>
       </c>
       <c r="AP304" s="233" t="n">
-        <v>0.1926163514275556</v>
+        <v>0.1926163514275557</v>
       </c>
       <c r="AQ304" s="190" t="n">
         <v>0.3567121997617949</v>
       </c>
       <c r="AR304" s="190" t="n">
-        <v>0.5444460962378012</v>
+        <v>0.5444460962378013</v>
       </c>
       <c r="AS304" s="190" t="n">
         <v>0.7118948340749839</v>
@@ -60698,10 +60698,10 @@
         <v>68.82258464134296</v>
       </c>
       <c r="AX304" s="190" t="n">
-        <v>68.61932025706453</v>
+        <v>68.61932025706454</v>
       </c>
       <c r="AY304" s="196" t="n">
-        <v>67.79502679430465</v>
+        <v>67.79502679430466</v>
       </c>
       <c r="BA304" s="101" t="inlineStr">
         <is>
@@ -60724,13 +60724,13 @@
         <v>0.006</v>
       </c>
       <c r="BG304" s="197" t="n">
-        <v>0.1926163514275556</v>
+        <v>0.1926163514275557</v>
       </c>
       <c r="BH304" s="190" t="n">
         <v>0.3567121997617949</v>
       </c>
       <c r="BI304" s="190" t="n">
-        <v>0.5444460962378012</v>
+        <v>0.5444460962378013</v>
       </c>
       <c r="BJ304" s="190" t="n">
         <v>0.7118948340749839</v>
@@ -60748,10 +60748,10 @@
         <v>68.82258464134296</v>
       </c>
       <c r="BO304" s="190" t="n">
-        <v>68.61932025706453</v>
+        <v>68.61932025706454</v>
       </c>
       <c r="BP304" s="198" t="n">
-        <v>67.79502679430465</v>
+        <v>67.79502679430466</v>
       </c>
       <c r="BR304" s="101" t="inlineStr">
         <is>
@@ -60783,10 +60783,10 @@
         <v>-0.001278696975840338</v>
       </c>
       <c r="CA304" s="463" t="n">
-        <v>-0.001271290290425322</v>
+        <v>-0.001271290290425321</v>
       </c>
       <c r="CB304" s="464" t="n">
-        <v>-0.001115286744203691</v>
+        <v>-0.00111528674420369</v>
       </c>
       <c r="CC304" s="197" t="n">
         <v>-0.1040118362268382</v>
@@ -60795,13 +60795,13 @@
         <v>-0.08775568771885138</v>
       </c>
       <c r="CE304" s="190" t="n">
-        <v>-0.08811561660822483</v>
+        <v>-0.08811561660822487</v>
       </c>
       <c r="CF304" s="190" t="n">
-        <v>-0.08734583587447009</v>
+        <v>-0.08734583587447008</v>
       </c>
       <c r="CG304" s="198" t="n">
-        <v>-0.07569512859027183</v>
+        <v>-0.07569512859027179</v>
       </c>
     </row>
     <row r="305">
@@ -60929,7 +60929,7 @@
         <v>0.2371352064735232</v>
       </c>
       <c r="AQ305" s="190" t="n">
-        <v>0.3860872309020494</v>
+        <v>0.3860872309020495</v>
       </c>
       <c r="AR305" s="190" t="n">
         <v>0.5573823787071119</v>
@@ -60938,7 +60938,7 @@
         <v>0.7117178473545996</v>
       </c>
       <c r="AT305" s="196" t="n">
-        <v>0.9191578905640324</v>
+        <v>0.9191578905640323</v>
       </c>
       <c r="AU305" s="190" t="n">
         <v>102.2587926087094</v>
@@ -60947,13 +60947,13 @@
         <v>100.4756716891274</v>
       </c>
       <c r="AW305" s="190" t="n">
-        <v>95.58457907649134</v>
+        <v>95.58457907649132</v>
       </c>
       <c r="AX305" s="190" t="n">
         <v>85.98972466468807</v>
       </c>
       <c r="AY305" s="196" t="n">
-        <v>85.79849865329902</v>
+        <v>85.79849865329901</v>
       </c>
       <c r="BA305" s="111" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>0.2371352064735232</v>
       </c>
       <c r="BH305" s="190" t="n">
-        <v>0.3860872309020494</v>
+        <v>0.3860872309020495</v>
       </c>
       <c r="BI305" s="190" t="n">
         <v>0.5573823787071119</v>
@@ -60988,7 +60988,7 @@
         <v>0.7117178473545996</v>
       </c>
       <c r="BK305" s="198" t="n">
-        <v>0.9191578905640324</v>
+        <v>0.9191578905640323</v>
       </c>
       <c r="BL305" s="197" t="n">
         <v>102.2587926087094</v>
@@ -60997,13 +60997,13 @@
         <v>100.4756716891274</v>
       </c>
       <c r="BN305" s="190" t="n">
-        <v>95.58457907649134</v>
+        <v>95.58457907649132</v>
       </c>
       <c r="BO305" s="190" t="n">
         <v>85.98972466468807</v>
       </c>
       <c r="BP305" s="198" t="n">
-        <v>85.79849865329902</v>
+        <v>85.79849865329901</v>
       </c>
       <c r="BR305" s="111" t="inlineStr">
         <is>
@@ -61026,19 +61026,19 @@
         <v>0</v>
       </c>
       <c r="BX305" s="462" t="n">
-        <v>-0.0007698289837964476</v>
+        <v>-0.0007698289837964475</v>
       </c>
       <c r="BY305" s="463" t="n">
-        <v>-0.0007892996918374467</v>
+        <v>-0.0007892996918374466</v>
       </c>
       <c r="BZ305" s="463" t="n">
-        <v>-0.0008283027015389342</v>
+        <v>-0.0008283027015389343</v>
       </c>
       <c r="CA305" s="463" t="n">
         <v>-0.0009241805753961782</v>
       </c>
       <c r="CB305" s="464" t="n">
-        <v>-0.0009218546554570505</v>
+        <v>-0.0009218546554570507</v>
       </c>
       <c r="CC305" s="197" t="n">
         <v>-0.07878233809043367</v>
@@ -61193,7 +61193,7 @@
         <v>0.1942670562963336</v>
       </c>
       <c r="AU306" s="209" t="n">
-        <v>23.42970264410536</v>
+        <v>23.42970264410537</v>
       </c>
       <c r="AV306" s="209" t="n">
         <v>22.67936188096915</v>
@@ -61243,7 +61243,7 @@
         <v>0.1942670562963336</v>
       </c>
       <c r="BL306" s="212" t="n">
-        <v>23.42970264410536</v>
+        <v>23.42970264410537</v>
       </c>
       <c r="BM306" s="212" t="n">
         <v>22.67936188096915</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.0005324438391599063</v>
+        <v>-0.0005324438391598877</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0005643681599164509</v>
+        <v>-0.0005643681599164311</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0007713859555817254</v>
+        <v>-0.0007713859555816984</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0009305176557131352</v>
+        <v>-0.0009305176557131026</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0009338474699130163</v>
+        <v>-0.0009338474699129835</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.0124816395287996</v>
+        <v>-0.01248163952879916</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.01280672929410711</v>
+        <v>-0.01280672929410666</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.01320138322030419</v>
+        <v>-0.01320138322030372</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.01347338739264097</v>
+        <v>-0.01347338739264049</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.01374671906633936</v>
+        <v>-0.01374671906633888</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61430,10 +61430,10 @@
         <v>0.024</v>
       </c>
       <c r="AP307" s="206" t="n">
-        <v>0.7278776027625338</v>
+        <v>0.7278776027625339</v>
       </c>
       <c r="AQ307" s="207" t="n">
-        <v>1.311693453966183</v>
+        <v>1.311693453966184</v>
       </c>
       <c r="AR307" s="207" t="n">
         <v>2.024139229297374</v>
@@ -61442,7 +61442,7 @@
         <v>2.649894318107282</v>
       </c>
       <c r="AT307" s="208" t="n">
-        <v>3.303057298638158</v>
+        <v>3.303057298638157</v>
       </c>
       <c r="AU307" s="207" t="n">
         <v>299.7584722745474</v>
@@ -61454,7 +61454,7 @@
         <v>284.539186906164</v>
       </c>
       <c r="AX307" s="207" t="n">
-        <v>269.3468973802973</v>
+        <v>269.3468973802974</v>
       </c>
       <c r="AY307" s="208" t="n">
         <v>259.2966041164687</v>
@@ -61480,10 +61480,10 @@
         <v>0.024</v>
       </c>
       <c r="BG307" s="221" t="n">
-        <v>0.7278776027625338</v>
+        <v>0.7278776027625339</v>
       </c>
       <c r="BH307" s="222" t="n">
-        <v>1.311693453966183</v>
+        <v>1.311693453966184</v>
       </c>
       <c r="BI307" s="222" t="n">
         <v>2.024139229297374</v>
@@ -61492,7 +61492,7 @@
         <v>2.649894318107282</v>
       </c>
       <c r="BK307" s="214" t="n">
-        <v>3.303057298638158</v>
+        <v>3.303057298638157</v>
       </c>
       <c r="BL307" s="222" t="n">
         <v>299.7584722745474</v>
@@ -61504,7 +61504,7 @@
         <v>284.539186906164</v>
       </c>
       <c r="BO307" s="222" t="n">
-        <v>269.3468973802973</v>
+        <v>269.3468973802974</v>
       </c>
       <c r="BP307" s="214" t="n">
         <v>259.2966041164687</v>
@@ -61542,13 +61542,13 @@
         <v>0.02272279139209537</v>
       </c>
       <c r="CB307" s="468" t="n">
-        <v>-0.002723445150311651</v>
+        <v>-0.002723445150311649</v>
       </c>
       <c r="CC307" s="212" t="n">
-        <v>6.986721934620685</v>
+        <v>6.986721934620686</v>
       </c>
       <c r="CD307" s="212" t="n">
-        <v>7.442481475772541</v>
+        <v>7.442481475772544</v>
       </c>
       <c r="CE307" s="212" t="n">
         <v>7.858567349489695</v>
@@ -61557,7 +61557,7 @@
         <v>6.13681482670497</v>
       </c>
       <c r="CG307" s="213" t="n">
-        <v>-0.7080904812101763</v>
+        <v>-0.7080904812101757</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" thickBot="1">
@@ -62310,19 +62310,19 @@
         <v>113.5597970286921</v>
       </c>
       <c r="AO312" s="196" t="n">
-        <v>127.1923509211655</v>
+        <v>127.1923509211654</v>
       </c>
       <c r="AP312" s="473" t="n">
         <v>0.1314582806927261</v>
       </c>
       <c r="AQ312" s="463" t="n">
-        <v>0.3403102479022415</v>
+        <v>0.3403102479022414</v>
       </c>
       <c r="AR312" s="463" t="n">
         <v>0.4888610330320405</v>
       </c>
       <c r="AS312" s="463" t="n">
-        <v>0.5360710560512085</v>
+        <v>0.5360710560512086</v>
       </c>
       <c r="AT312" s="474" t="n">
         <v>0.5889467361211486</v>
@@ -62331,13 +62331,13 @@
         <v>0.1294582806927261</v>
       </c>
       <c r="AV312" s="463" t="n">
-        <v>0.3373102479022415</v>
+        <v>0.3373102479022414</v>
       </c>
       <c r="AW312" s="463" t="n">
         <v>0.4848610330320406</v>
       </c>
       <c r="AX312" s="463" t="n">
-        <v>0.5310710560512085</v>
+        <v>0.5310710560512086</v>
       </c>
       <c r="AY312" s="474" t="n">
         <v>0.5829467361211486</v>
@@ -62360,19 +62360,19 @@
         <v>113.5597970286921</v>
       </c>
       <c r="BF312" s="198" t="n">
-        <v>127.1923509211655</v>
+        <v>127.1923509211654</v>
       </c>
       <c r="BG312" s="462" t="n">
         <v>0.1314582806927261</v>
       </c>
       <c r="BH312" s="463" t="n">
-        <v>0.3403102479022415</v>
+        <v>0.3403102479022414</v>
       </c>
       <c r="BI312" s="463" t="n">
         <v>0.4888610330320405</v>
       </c>
       <c r="BJ312" s="463" t="n">
-        <v>0.5360710560512085</v>
+        <v>0.5360710560512086</v>
       </c>
       <c r="BK312" s="464" t="n">
         <v>0.5889467361211486</v>
@@ -62381,13 +62381,13 @@
         <v>0.1294582806927261</v>
       </c>
       <c r="BM312" s="476" t="n">
-        <v>0.3373102479022415</v>
+        <v>0.3373102479022414</v>
       </c>
       <c r="BN312" s="476" t="n">
         <v>0.4848610330320406</v>
       </c>
       <c r="BO312" s="476" t="n">
-        <v>0.5310710560512085</v>
+        <v>0.5310710560512086</v>
       </c>
       <c r="BP312" s="477" t="n">
         <v>0.5829467361211486</v>
@@ -62559,7 +62559,7 @@
         <v>49.22583981597641</v>
       </c>
       <c r="AM313" s="190" t="n">
-        <v>67.28893941810735</v>
+        <v>67.28893941810736</v>
       </c>
       <c r="AN313" s="190" t="n">
         <v>73.75964655793223</v>
@@ -62609,7 +62609,7 @@
         <v>49.22583981597641</v>
       </c>
       <c r="BD313" s="190" t="n">
-        <v>67.28893941810735</v>
+        <v>67.28893941810736</v>
       </c>
       <c r="BE313" s="190" t="n">
         <v>73.75964655793223</v>
@@ -62674,13 +62674,13 @@
         <v>0.4136917140689019</v>
       </c>
       <c r="BZ313" s="463" t="n">
-        <v>0.4940471988463949</v>
+        <v>0.494047198846395</v>
       </c>
       <c r="CA313" s="463" t="n">
-        <v>0.5177347533911226</v>
+        <v>0.5177347533911225</v>
       </c>
       <c r="CB313" s="464" t="n">
-        <v>0.5377472030759876</v>
+        <v>0.5377472030759874</v>
       </c>
       <c r="CC313" s="482" t="n">
         <v>0</v>
@@ -62850,7 +62850,7 @@
         <v>0.3959001802167443</v>
       </c>
       <c r="AY314" s="474" t="n">
-        <v>0.4399319233348498</v>
+        <v>0.4399319233348499</v>
       </c>
       <c r="BA314" s="111" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>0.3959001802167443</v>
       </c>
       <c r="BP314" s="464" t="n">
-        <v>0.4399319233348498</v>
+        <v>0.4399319233348499</v>
       </c>
       <c r="BR314" s="111" t="inlineStr">
         <is>
@@ -63069,7 +63069,7 @@
         <v>6.926441119872522</v>
       </c>
       <c r="AM315" s="209" t="n">
-        <v>13.47010685860509</v>
+        <v>13.47010685860508</v>
       </c>
       <c r="AN315" s="209" t="n">
         <v>16.95867784830281</v>
@@ -63119,7 +63119,7 @@
         <v>6.926441119872522</v>
       </c>
       <c r="BD315" s="212" t="n">
-        <v>13.47010685860509</v>
+        <v>13.47010685860508</v>
       </c>
       <c r="BE315" s="212" t="n">
         <v>16.95867784830281</v>
@@ -63339,19 +63339,19 @@
         <v>0.3194244047789945</v>
       </c>
       <c r="AR316" s="501" t="n">
-        <v>0.4417082706806997</v>
+        <v>0.4417082706806998</v>
       </c>
       <c r="AS316" s="501" t="n">
-        <v>0.496778038958396</v>
+        <v>0.4967780389583961</v>
       </c>
       <c r="AT316" s="502" t="n">
         <v>0.5349879998932333</v>
       </c>
       <c r="AU316" s="501" t="n">
-        <v>0.1763492347151063</v>
+        <v>0.1763492347151062</v>
       </c>
       <c r="AV316" s="501" t="n">
-        <v>0.3164244047789946</v>
+        <v>0.3164244047789945</v>
       </c>
       <c r="AW316" s="501" t="n">
         <v>0.4377082706806997</v>
@@ -63360,7 +63360,7 @@
         <v>0.491778038958396</v>
       </c>
       <c r="AY316" s="502" t="n">
-        <v>0.5289879998932333</v>
+        <v>0.5289879998932334</v>
       </c>
       <c r="BA316" s="155" t="inlineStr">
         <is>
@@ -63389,19 +63389,19 @@
         <v>0.3194244047789945</v>
       </c>
       <c r="BI316" s="504" t="n">
-        <v>0.4417082706806997</v>
+        <v>0.4417082706806998</v>
       </c>
       <c r="BJ316" s="504" t="n">
-        <v>0.496778038958396</v>
+        <v>0.4967780389583961</v>
       </c>
       <c r="BK316" s="505" t="n">
         <v>0.5349879998932333</v>
       </c>
       <c r="BL316" s="504" t="n">
-        <v>0.1763492347151063</v>
+        <v>0.1763492347151062</v>
       </c>
       <c r="BM316" s="504" t="n">
-        <v>0.3164244047789946</v>
+        <v>0.3164244047789945</v>
       </c>
       <c r="BN316" s="504" t="n">
         <v>0.4377082706806997</v>
@@ -63410,7 +63410,7 @@
         <v>0.491778038958396</v>
       </c>
       <c r="BP316" s="505" t="n">
-        <v>0.5289879998932333</v>
+        <v>0.5289879998932334</v>
       </c>
       <c r="BR316" s="155" t="inlineStr">
         <is>
@@ -63433,19 +63433,19 @@
         <v>0</v>
       </c>
       <c r="BX316" s="503" t="n">
-        <v>0.1759430136657767</v>
+        <v>0.1759430136657766</v>
       </c>
       <c r="BY316" s="504" t="n">
-        <v>0.3158801222454696</v>
+        <v>0.3158801222454695</v>
       </c>
       <c r="BZ316" s="504" t="n">
         <v>0.4370653275457707</v>
       </c>
       <c r="CA316" s="504" t="n">
-        <v>0.4911050983670367</v>
+        <v>0.4911050983670369</v>
       </c>
       <c r="CB316" s="505" t="n">
-        <v>0.5283148153784278</v>
+        <v>0.5283148153784277</v>
       </c>
       <c r="CC316" s="492" t="n">
         <v>0</v>
@@ -64110,28 +64110,28 @@
         <v>9300.44889838463</v>
       </c>
       <c r="AL323" s="368" t="n">
-        <v>34513.22235879839</v>
+        <v>34513.2223587984</v>
       </c>
       <c r="AM323" s="368" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.24033128741</v>
       </c>
       <c r="AN323" s="368" t="n">
         <v>77145.27984093783</v>
       </c>
       <c r="AO323" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP323" s="381" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="AQ323" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="AR323" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="AS323" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="AT323" s="382" t="n">
         <v>697.1163277359263</v>
@@ -64145,28 +64145,28 @@
         <v>9300.44889838463</v>
       </c>
       <c r="BC323" s="375" t="n">
-        <v>34513.22235879839</v>
+        <v>34513.2223587984</v>
       </c>
       <c r="BD323" s="375" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.24033128741</v>
       </c>
       <c r="BE323" s="375" t="n">
         <v>77145.27984093783</v>
       </c>
       <c r="BF323" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG323" s="386" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="BH323" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="BI323" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="BJ323" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="BK323" s="387" t="n">
         <v>697.1163277359263</v>
@@ -64180,28 +64180,28 @@
         <v>9158.952313317863</v>
       </c>
       <c r="BT323" s="375" t="n">
-        <v>34208.97155320367</v>
+        <v>34208.97155320368</v>
       </c>
       <c r="BU323" s="375" t="n">
-        <v>61846.0238393364</v>
+        <v>61846.02383933641</v>
       </c>
       <c r="BV323" s="375" t="n">
         <v>76425.73642435046</v>
       </c>
       <c r="BW323" s="392" t="n">
-        <v>88667.86459026214</v>
+        <v>88667.86459026212</v>
       </c>
       <c r="BX323" s="386" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="BY323" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="BZ323" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="CA323" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="CB323" s="387" t="n">
         <v>697.1163277359263</v>
@@ -64305,7 +64305,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL324" s="368" t="n">
-        <v>90066.83119143534</v>
+        <v>90066.83119143535</v>
       </c>
       <c r="AM324" s="368" t="n">
         <v>128629.5373619414</v>
@@ -64317,13 +64317,13 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP324" s="381" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="AQ324" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="AR324" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="AS324" s="372" t="n">
         <v>1944.270389399181</v>
@@ -64340,7 +64340,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC324" s="375" t="n">
-        <v>90066.83119143534</v>
+        <v>90066.83119143535</v>
       </c>
       <c r="BD324" s="375" t="n">
         <v>128629.5373619414</v>
@@ -64352,13 +64352,13 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG324" s="386" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="BH324" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="BI324" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="BJ324" s="372" t="n">
         <v>1944.270389399181</v>
@@ -64375,7 +64375,7 @@
         <v>44020.42113175881</v>
       </c>
       <c r="BT324" s="375" t="n">
-        <v>89418.8625780071</v>
+        <v>89418.86257800712</v>
       </c>
       <c r="BU324" s="375" t="n">
         <v>127597.1275987169</v>
@@ -64387,13 +64387,13 @@
         <v>157648.4555401134</v>
       </c>
       <c r="BX324" s="386" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="BY324" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="BZ324" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="CA324" s="372" t="n">
         <v>1944.270389399181</v>
@@ -64774,7 +64774,7 @@
         <v>412591.2330931693</v>
       </c>
       <c r="BW326" s="421" t="n">
-        <v>446428.305553037</v>
+        <v>446428.3055530369</v>
       </c>
       <c r="BX326" s="416" t="n">
         <v>18128.807941329</v>
@@ -64899,7 +64899,7 @@
         <v>727099.2780700257</v>
       </c>
       <c r="AO327" s="409" t="n">
-        <v>812602.7137558617</v>
+        <v>812602.7137558619</v>
       </c>
       <c r="AP327" s="436" t="n">
         <v>2766.195750005259</v>
@@ -64914,7 +64914,7 @@
         <v>2761.676313459322</v>
       </c>
       <c r="AT327" s="438" t="n">
-        <v>2759.112257405863</v>
+        <v>2759.112257405864</v>
       </c>
       <c r="BA327" s="155" t="inlineStr">
         <is>
@@ -64934,7 +64934,7 @@
         <v>727099.2780700257</v>
       </c>
       <c r="BF327" s="441" t="n">
-        <v>812602.7137558617</v>
+        <v>812602.7137558619</v>
       </c>
       <c r="BG327" s="442" t="n">
         <v>2766.195750005259</v>
@@ -64949,7 +64949,7 @@
         <v>2761.676313459322</v>
       </c>
       <c r="BK327" s="444" t="n">
-        <v>2759.112257405863</v>
+        <v>2759.112257405864</v>
       </c>
       <c r="BR327" s="155" t="inlineStr">
         <is>
@@ -64969,7 +64969,7 @@
         <v>720066.080142892</v>
       </c>
       <c r="BW327" s="441" t="n">
-        <v>803513.4754289294</v>
+        <v>803513.4754289293</v>
       </c>
       <c r="BX327" s="442" t="n">
         <v>2768.108534927736</v>
@@ -64981,7 +64981,7 @@
         <v>2637.666976477417</v>
       </c>
       <c r="CA327" s="443" t="n">
-        <v>2762.769626948313</v>
+        <v>2762.769626948312</v>
       </c>
       <c r="CB327" s="444" t="n">
         <v>2759.195590077078</v>
@@ -67008,28 +67008,28 @@
         <v>9300.44889838463</v>
       </c>
       <c r="AL341" s="368" t="n">
-        <v>34513.22235879839</v>
+        <v>34513.2223587984</v>
       </c>
       <c r="AM341" s="368" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.24033128741</v>
       </c>
       <c r="AN341" s="368" t="n">
         <v>77145.27984093783</v>
       </c>
       <c r="AO341" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP341" s="381" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="AQ341" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="AR341" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="AS341" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="AT341" s="382" t="n">
         <v>697.1163277359263</v>
@@ -67043,28 +67043,28 @@
         <v>9300.44889838463</v>
       </c>
       <c r="BC341" s="375" t="n">
-        <v>34513.22235879839</v>
+        <v>34513.2223587984</v>
       </c>
       <c r="BD341" s="375" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.24033128741</v>
       </c>
       <c r="BE341" s="375" t="n">
         <v>77145.27984093783</v>
       </c>
       <c r="BF341" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG341" s="386" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="BH341" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="BI341" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="BJ341" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="BK341" s="387" t="n">
         <v>697.1163277359263</v>
@@ -67078,28 +67078,28 @@
         <v>9158.952313317863</v>
       </c>
       <c r="BT341" s="375" t="n">
-        <v>34208.97155320367</v>
+        <v>34208.97155320368</v>
       </c>
       <c r="BU341" s="375" t="n">
-        <v>61846.0238393364</v>
+        <v>61846.02383933641</v>
       </c>
       <c r="BV341" s="375" t="n">
         <v>76425.73642435046</v>
       </c>
       <c r="BW341" s="392" t="n">
-        <v>88667.86459026214</v>
+        <v>88667.86459026212</v>
       </c>
       <c r="BX341" s="386" t="n">
-        <v>588.3746268593676</v>
+        <v>588.3746268593677</v>
       </c>
       <c r="BY341" s="372" t="n">
-        <v>633.7546894227793</v>
+        <v>633.7546894227794</v>
       </c>
       <c r="BZ341" s="372" t="n">
-        <v>637.7485705645477</v>
+        <v>637.7485705645478</v>
       </c>
       <c r="CA341" s="372" t="n">
-        <v>672.9999385701675</v>
+        <v>672.9999385701673</v>
       </c>
       <c r="CB341" s="387" t="n">
         <v>697.1163277359263</v>
@@ -67203,7 +67203,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL342" s="368" t="n">
-        <v>90066.83119143534</v>
+        <v>90066.83119143535</v>
       </c>
       <c r="AM342" s="368" t="n">
         <v>128629.5373619414</v>
@@ -67215,13 +67215,13 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP342" s="381" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="AQ342" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="AR342" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="AS342" s="372" t="n">
         <v>1944.270389399181</v>
@@ -67238,7 +67238,7 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC342" s="375" t="n">
-        <v>90066.83119143534</v>
+        <v>90066.83119143535</v>
       </c>
       <c r="BD342" s="375" t="n">
         <v>128629.5373619414</v>
@@ -67250,13 +67250,13 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG342" s="386" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="BH342" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="BI342" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="BJ342" s="372" t="n">
         <v>1944.270389399181</v>
@@ -67273,7 +67273,7 @@
         <v>44020.42113175881</v>
       </c>
       <c r="BT342" s="375" t="n">
-        <v>89418.8625780071</v>
+        <v>89418.86257800712</v>
       </c>
       <c r="BU342" s="375" t="n">
         <v>127597.1275987169</v>
@@ -67285,13 +67285,13 @@
         <v>157648.4555401134</v>
       </c>
       <c r="BX342" s="386" t="n">
-        <v>1635.517697833117</v>
+        <v>1635.517697833116</v>
       </c>
       <c r="BY342" s="372" t="n">
         <v>1816.502530221657</v>
       </c>
       <c r="BZ342" s="372" t="n">
-        <v>1896.257077346366</v>
+        <v>1896.257077346365</v>
       </c>
       <c r="CA342" s="372" t="n">
         <v>1944.270389399181</v>
@@ -67672,7 +67672,7 @@
         <v>412591.2330931693</v>
       </c>
       <c r="BW344" s="421" t="n">
-        <v>446428.305553037</v>
+        <v>446428.3055530369</v>
       </c>
       <c r="BX344" s="416" t="n">
         <v>18128.807941329</v>
@@ -67797,7 +67797,7 @@
         <v>727099.2780700257</v>
       </c>
       <c r="AO345" s="409" t="n">
-        <v>812602.7137558617</v>
+        <v>812602.7137558619</v>
       </c>
       <c r="AP345" s="436" t="n">
         <v>2766.195750005259</v>
@@ -67812,7 +67812,7 @@
         <v>2761.676313459322</v>
       </c>
       <c r="AT345" s="438" t="n">
-        <v>2759.112257405863</v>
+        <v>2759.112257405864</v>
       </c>
       <c r="BA345" s="155" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>727099.2780700257</v>
       </c>
       <c r="BF345" s="441" t="n">
-        <v>812602.7137558617</v>
+        <v>812602.7137558619</v>
       </c>
       <c r="BG345" s="442" t="n">
         <v>2766.195750005259</v>
@@ -67847,7 +67847,7 @@
         <v>2761.676313459322</v>
       </c>
       <c r="BK345" s="444" t="n">
-        <v>2759.112257405863</v>
+        <v>2759.112257405864</v>
       </c>
       <c r="BR345" s="155" t="inlineStr">
         <is>
@@ -67867,7 +67867,7 @@
         <v>720066.080142892</v>
       </c>
       <c r="BW345" s="441" t="n">
-        <v>803513.4754289294</v>
+        <v>803513.4754289293</v>
       </c>
       <c r="BX345" s="442" t="n">
         <v>2768.108534927736</v>
@@ -67879,7 +67879,7 @@
         <v>2637.666976477417</v>
       </c>
       <c r="CA345" s="443" t="n">
-        <v>2762.769626948313</v>
+        <v>2762.769626948312</v>
       </c>
       <c r="CB345" s="444" t="n">
         <v>2759.195590077078</v>
@@ -68425,31 +68425,31 @@
         <v>51541.95398502168</v>
       </c>
       <c r="AL350" s="368" t="n">
-        <v>54853.96409601608</v>
+        <v>54853.96409601607</v>
       </c>
       <c r="AM350" s="368" t="n">
-        <v>55144.41702615939</v>
+        <v>55144.4170261594</v>
       </c>
       <c r="AN350" s="368" t="n">
-        <v>55574.29755313224</v>
+        <v>55574.29755313223</v>
       </c>
       <c r="AO350" s="380" t="n">
         <v>52234.63231220673</v>
       </c>
       <c r="AP350" s="381" t="n">
-        <v>493.5238756900339</v>
+        <v>493.5238756900338</v>
       </c>
       <c r="AQ350" s="372" t="n">
-        <v>519.6117749504773</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="AR350" s="372" t="n">
-        <v>539.4082092873379</v>
+        <v>539.408209287338</v>
       </c>
       <c r="AS350" s="372" t="n">
         <v>560.2095892622106</v>
       </c>
       <c r="AT350" s="382" t="n">
-        <v>582.409327197897</v>
+        <v>582.4093271978971</v>
       </c>
       <c r="BA350" s="83" t="inlineStr">
         <is>
@@ -68460,31 +68460,31 @@
         <v>51541.95398502168</v>
       </c>
       <c r="BC350" s="375" t="n">
-        <v>54853.96409601608</v>
+        <v>54853.96409601607</v>
       </c>
       <c r="BD350" s="375" t="n">
-        <v>55144.41702615939</v>
+        <v>55144.4170261594</v>
       </c>
       <c r="BE350" s="375" t="n">
-        <v>55574.29755313224</v>
+        <v>55574.29755313223</v>
       </c>
       <c r="BF350" s="392" t="n">
         <v>52234.63231220673</v>
       </c>
       <c r="BG350" s="386" t="n">
-        <v>493.5238756900339</v>
+        <v>493.5238756900338</v>
       </c>
       <c r="BH350" s="372" t="n">
-        <v>519.6117749504773</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="BI350" s="372" t="n">
-        <v>539.4082092873379</v>
+        <v>539.408209287338</v>
       </c>
       <c r="BJ350" s="372" t="n">
         <v>560.2095892622106</v>
       </c>
       <c r="BK350" s="387" t="n">
-        <v>582.409327197897</v>
+        <v>582.4093271978971</v>
       </c>
       <c r="BR350" s="83" t="inlineStr">
         <is>
@@ -68492,34 +68492,34 @@
         </is>
       </c>
       <c r="BS350" s="391" t="n">
-        <v>52269.06877515536</v>
+        <v>52269.06877515535</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>55718.66770506615</v>
+        <v>55718.66770506614</v>
       </c>
       <c r="BU350" s="375" t="n">
-        <v>56250.97380973528</v>
+        <v>56250.97380973529</v>
       </c>
       <c r="BV350" s="375" t="n">
-        <v>56875.80716202218</v>
+        <v>56875.80716202217</v>
       </c>
       <c r="BW350" s="392" t="n">
-        <v>53692.12532407887</v>
+        <v>53692.12532407889</v>
       </c>
       <c r="BX350" s="386" t="n">
         <v>496.2762703297993</v>
       </c>
       <c r="BY350" s="372" t="n">
-        <v>522.585791068144</v>
+        <v>522.5857910681437</v>
       </c>
       <c r="BZ350" s="372" t="n">
-        <v>542.98625614138</v>
+        <v>542.9862561413801</v>
       </c>
       <c r="CA350" s="372" t="n">
         <v>564.1429010659275</v>
       </c>
       <c r="CB350" s="387" t="n">
-        <v>586.6102006335917</v>
+        <v>586.6102006335919</v>
       </c>
       <c r="CI350" s="225" t="n"/>
       <c r="CJ350" s="225" t="n"/>
@@ -68610,7 +68610,7 @@
         <v>110003.6379453573</v>
       </c>
       <c r="AN351" s="368" t="n">
-        <v>114758.8239532721</v>
+        <v>114758.823953272</v>
       </c>
       <c r="AO351" s="380" t="n">
         <v>118336.8554245862</v>
@@ -68625,7 +68625,7 @@
         <v>1611.110675969702</v>
       </c>
       <c r="AS351" s="372" t="n">
-        <v>1689.930419809751</v>
+        <v>1689.93041980975</v>
       </c>
       <c r="AT351" s="382" t="n">
         <v>1768.477819138082</v>
@@ -68645,7 +68645,7 @@
         <v>110003.6379453573</v>
       </c>
       <c r="BE351" s="375" t="n">
-        <v>114758.8239532721</v>
+        <v>114758.823953272</v>
       </c>
       <c r="BF351" s="392" t="n">
         <v>118336.8554245862</v>
@@ -68660,7 +68660,7 @@
         <v>1611.110675969702</v>
       </c>
       <c r="BJ351" s="372" t="n">
-        <v>1689.930419809751</v>
+        <v>1689.93041980975</v>
       </c>
       <c r="BK351" s="387" t="n">
         <v>1768.477819138082</v>
@@ -68783,31 +68783,31 @@
         <v>54920.92979565485</v>
       </c>
       <c r="AL352" s="368" t="n">
-        <v>56496.75148806424</v>
+        <v>56496.75148806423</v>
       </c>
       <c r="AM352" s="368" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="AN352" s="368" t="n">
-        <v>52431.33015542696</v>
+        <v>52431.33015542695</v>
       </c>
       <c r="AO352" s="380" t="n">
-        <v>56018.87435173046</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="AP352" s="381" t="n">
         <v>538.326186753865</v>
       </c>
       <c r="AQ352" s="372" t="n">
-        <v>564.4618447950938</v>
+        <v>564.4618447950936</v>
       </c>
       <c r="AR352" s="372" t="n">
         <v>588.8613564801755</v>
       </c>
       <c r="AS352" s="372" t="n">
-        <v>614.8282788519614</v>
+        <v>614.8282788519613</v>
       </c>
       <c r="AT352" s="382" t="n">
-        <v>659.9824391699884</v>
+        <v>659.9824391699887</v>
       </c>
       <c r="BA352" s="111" t="inlineStr">
         <is>
@@ -68818,31 +68818,31 @@
         <v>54920.92979565485</v>
       </c>
       <c r="BC352" s="375" t="n">
-        <v>56496.75148806424</v>
+        <v>56496.75148806423</v>
       </c>
       <c r="BD352" s="375" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="BE352" s="375" t="n">
-        <v>52431.33015542696</v>
+        <v>52431.33015542695</v>
       </c>
       <c r="BF352" s="392" t="n">
-        <v>56018.87435173046</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="BG352" s="386" t="n">
         <v>538.326186753865</v>
       </c>
       <c r="BH352" s="372" t="n">
-        <v>564.4618447950938</v>
+        <v>564.4618447950936</v>
       </c>
       <c r="BI352" s="372" t="n">
         <v>588.8613564801755</v>
       </c>
       <c r="BJ352" s="372" t="n">
-        <v>614.8282788519614</v>
+        <v>614.8282788519613</v>
       </c>
       <c r="BK352" s="387" t="n">
-        <v>659.9824391699884</v>
+        <v>659.9824391699887</v>
       </c>
       <c r="BR352" s="111" t="inlineStr">
         <is>
@@ -68850,34 +68850,34 @@
         </is>
       </c>
       <c r="BS352" s="391" t="n">
-        <v>55227.55342929587</v>
+        <v>55227.55342929588</v>
       </c>
       <c r="BT352" s="375" t="n">
-        <v>56905.08867324545</v>
+        <v>56905.08867324543</v>
       </c>
       <c r="BU352" s="375" t="n">
-        <v>56485.98781551626</v>
+        <v>56485.98781551624</v>
       </c>
       <c r="BV352" s="375" t="n">
-        <v>53080.79535081491</v>
+        <v>53080.7953508149</v>
       </c>
       <c r="BW352" s="392" t="n">
-        <v>56852.91156080306</v>
+        <v>56852.91156080308</v>
       </c>
       <c r="BX352" s="386" t="n">
         <v>539.6612028096362</v>
       </c>
       <c r="BY352" s="372" t="n">
-        <v>565.9105666048659</v>
+        <v>565.9105666048657</v>
       </c>
       <c r="BZ352" s="372" t="n">
         <v>590.4642594520905</v>
       </c>
       <c r="CA352" s="372" t="n">
-        <v>616.722868040099</v>
+        <v>616.7228680400989</v>
       </c>
       <c r="CB352" s="387" t="n">
-        <v>662.02321465238</v>
+        <v>662.0232146523803</v>
       </c>
       <c r="CI352" s="225" t="n"/>
       <c r="CJ352" s="225" t="n"/>
@@ -68971,7 +68971,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="AO353" s="409" t="n">
-        <v>417885.4533985371</v>
+        <v>417885.4533985369</v>
       </c>
       <c r="AP353" s="410" t="n">
         <v>25268.66956059994</v>
@@ -68986,7 +68986,7 @@
         <v>27803.57572206694</v>
       </c>
       <c r="AT353" s="412" t="n">
-        <v>28794.80282956345</v>
+        <v>28794.80282956344</v>
       </c>
       <c r="BA353" s="111" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="BF353" s="421" t="n">
-        <v>417885.4533985371</v>
+        <v>417885.4533985369</v>
       </c>
       <c r="BG353" s="416" t="n">
         <v>25268.66956059994</v>
@@ -69021,7 +69021,7 @@
         <v>27803.57572206694</v>
       </c>
       <c r="BK353" s="418" t="n">
-        <v>28794.80282956345</v>
+        <v>28794.80282956344</v>
       </c>
       <c r="BR353" s="111" t="inlineStr">
         <is>
@@ -69035,13 +69035,13 @@
         <v>548288.8330684748</v>
       </c>
       <c r="BU353" s="420" t="n">
-        <v>448994.5861672615</v>
+        <v>448994.5861672614</v>
       </c>
       <c r="BV353" s="420" t="n">
         <v>402245.7525736701</v>
       </c>
       <c r="BW353" s="421" t="n">
-        <v>423521.3656159503</v>
+        <v>423521.3656159501</v>
       </c>
       <c r="BX353" s="416" t="n">
         <v>25256.546832515</v>
@@ -69050,13 +69050,13 @@
         <v>24162.04424372253</v>
       </c>
       <c r="BZ353" s="417" t="n">
-        <v>26235.74455205261</v>
+        <v>26235.74455205262</v>
       </c>
       <c r="CA353" s="417" t="n">
-        <v>27780.45073578561</v>
+        <v>27780.45073578562</v>
       </c>
       <c r="CB353" s="418" t="n">
-        <v>28770.81824586091</v>
+        <v>28770.8182458609</v>
       </c>
       <c r="CI353" s="225" t="n"/>
       <c r="CJ353" s="225" t="n"/>
@@ -69141,7 +69141,7 @@
         <v>798622.6246690482</v>
       </c>
       <c r="AL354" s="408" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="AM354" s="408" t="n">
         <v>666853.7543426913</v>
@@ -69165,7 +69165,7 @@
         <v>2326.994788066119</v>
       </c>
       <c r="AT354" s="438" t="n">
-        <v>2517.547115926639</v>
+        <v>2517.54711592664</v>
       </c>
       <c r="BA354" s="155" t="inlineStr">
         <is>
@@ -69176,7 +69176,7 @@
         <v>798622.6246690482</v>
       </c>
       <c r="BC354" s="440" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="BD354" s="440" t="n">
         <v>666853.7543426913</v>
@@ -69200,7 +69200,7 @@
         <v>2326.994788066119</v>
       </c>
       <c r="BK354" s="444" t="n">
-        <v>2517.547115926639</v>
+        <v>2517.54711592664</v>
       </c>
       <c r="BR354" s="155" t="inlineStr">
         <is>
@@ -69214,7 +69214,7 @@
         <v>768586.292102884</v>
       </c>
       <c r="BU354" s="440" t="n">
-        <v>672857.3486787789</v>
+        <v>672857.3486787787</v>
       </c>
       <c r="BV354" s="440" t="n">
         <v>628425.1925887223</v>
@@ -69235,7 +69235,7 @@
         <v>2326.87069106141</v>
       </c>
       <c r="CB354" s="444" t="n">
-        <v>2516.171986431975</v>
+        <v>2516.171986431976</v>
       </c>
       <c r="CI354" s="225" t="n"/>
       <c r="CJ354" s="225" t="n"/>
@@ -71116,31 +71116,31 @@
         <v>51541.95398502168</v>
       </c>
       <c r="AL368" s="368" t="n">
-        <v>54853.96409601608</v>
+        <v>54853.96409601607</v>
       </c>
       <c r="AM368" s="368" t="n">
-        <v>55144.41702615939</v>
+        <v>55144.4170261594</v>
       </c>
       <c r="AN368" s="368" t="n">
-        <v>55574.29755313224</v>
+        <v>55574.29755313223</v>
       </c>
       <c r="AO368" s="380" t="n">
         <v>52234.63231220673</v>
       </c>
       <c r="AP368" s="381" t="n">
-        <v>493.5238756900339</v>
+        <v>493.5238756900338</v>
       </c>
       <c r="AQ368" s="372" t="n">
-        <v>519.6117749504773</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="AR368" s="372" t="n">
-        <v>539.4082092873379</v>
+        <v>539.408209287338</v>
       </c>
       <c r="AS368" s="372" t="n">
         <v>560.2095892622106</v>
       </c>
       <c r="AT368" s="382" t="n">
-        <v>582.409327197897</v>
+        <v>582.4093271978971</v>
       </c>
       <c r="BA368" s="83" t="inlineStr">
         <is>
@@ -71151,31 +71151,31 @@
         <v>51541.95398502168</v>
       </c>
       <c r="BC368" s="375" t="n">
-        <v>54853.96409601608</v>
+        <v>54853.96409601607</v>
       </c>
       <c r="BD368" s="375" t="n">
-        <v>55144.41702615939</v>
+        <v>55144.4170261594</v>
       </c>
       <c r="BE368" s="375" t="n">
-        <v>55574.29755313224</v>
+        <v>55574.29755313223</v>
       </c>
       <c r="BF368" s="392" t="n">
         <v>52234.63231220673</v>
       </c>
       <c r="BG368" s="386" t="n">
-        <v>493.5238756900339</v>
+        <v>493.5238756900338</v>
       </c>
       <c r="BH368" s="372" t="n">
-        <v>519.6117749504773</v>
+        <v>519.6117749504771</v>
       </c>
       <c r="BI368" s="372" t="n">
-        <v>539.4082092873379</v>
+        <v>539.408209287338</v>
       </c>
       <c r="BJ368" s="372" t="n">
         <v>560.2095892622106</v>
       </c>
       <c r="BK368" s="387" t="n">
-        <v>582.409327197897</v>
+        <v>582.4093271978971</v>
       </c>
       <c r="BR368" s="83" t="inlineStr">
         <is>
@@ -71183,16 +71183,16 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>52269.06877515536</v>
+        <v>52269.06877515535</v>
       </c>
       <c r="BT368" s="375" t="n">
         <v>55718.66770506615</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>56250.97380973527</v>
+        <v>56250.97380973528</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>56875.80716202218</v>
+        <v>56875.80716202217</v>
       </c>
       <c r="BW368" s="392" t="n">
         <v>53692.12532407888</v>
@@ -71201,31 +71201,31 @@
         <v>496.2762703297993</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>522.585791068144</v>
+        <v>522.5857910681437</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>542.98625614138</v>
+        <v>542.9862561413801</v>
       </c>
       <c r="CA368" s="372" t="n">
         <v>564.1429010659275</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>586.6102006335917</v>
+        <v>586.6102006335918</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>608.4285996162361</v>
+        <v>608.4285996162366</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>615.2501473815284</v>
+        <v>615.2501473815286</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>675.0153000277156</v>
+        <v>675.0153000277148</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>702.5569214362999</v>
+        <v>702.5569214362998</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>695.0424454521076</v>
+        <v>695.0424454521068</v>
       </c>
     </row>
     <row r="369">
@@ -71314,7 +71314,7 @@
         <v>110003.6379453573</v>
       </c>
       <c r="AN369" s="368" t="n">
-        <v>114758.8239532721</v>
+        <v>114758.823953272</v>
       </c>
       <c r="AO369" s="380" t="n">
         <v>118336.8554245862</v>
@@ -71329,7 +71329,7 @@
         <v>1611.110675969702</v>
       </c>
       <c r="AS369" s="372" t="n">
-        <v>1689.930419809751</v>
+        <v>1689.93041980975</v>
       </c>
       <c r="AT369" s="382" t="n">
         <v>1768.477819138082</v>
@@ -71349,7 +71349,7 @@
         <v>110003.6379453573</v>
       </c>
       <c r="BE369" s="375" t="n">
-        <v>114758.8239532721</v>
+        <v>114758.823953272</v>
       </c>
       <c r="BF369" s="392" t="n">
         <v>118336.8554245862</v>
@@ -71364,7 +71364,7 @@
         <v>1611.110675969702</v>
       </c>
       <c r="BJ369" s="372" t="n">
-        <v>1689.930419809751</v>
+        <v>1689.93041980975</v>
       </c>
       <c r="BK369" s="387" t="n">
         <v>1768.477819138082</v>
@@ -71405,19 +71405,19 @@
         <v>1770.03796411774</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>250.1301657702889</v>
+        <v>250.1301657702885</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>231.301811713455</v>
+        <v>231.3018117134545</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>245.0000227696952</v>
+        <v>245.0000227696953</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>260.9608131342969</v>
+        <v>260.9608131342967</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>239.4551276586433</v>
+        <v>239.455127658644</v>
       </c>
     </row>
     <row r="370">
@@ -71500,31 +71500,31 @@
         <v>54920.92979565485</v>
       </c>
       <c r="AL370" s="368" t="n">
-        <v>56496.75148806424</v>
+        <v>56496.75148806423</v>
       </c>
       <c r="AM370" s="368" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="AN370" s="368" t="n">
-        <v>52431.33015542696</v>
+        <v>52431.33015542695</v>
       </c>
       <c r="AO370" s="380" t="n">
-        <v>56018.87435173046</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="AP370" s="381" t="n">
         <v>538.326186753865</v>
       </c>
       <c r="AQ370" s="372" t="n">
-        <v>564.4618447950938</v>
+        <v>564.4618447950936</v>
       </c>
       <c r="AR370" s="372" t="n">
         <v>588.8613564801755</v>
       </c>
       <c r="AS370" s="372" t="n">
-        <v>614.8282788519614</v>
+        <v>614.8282788519613</v>
       </c>
       <c r="AT370" s="382" t="n">
-        <v>659.9824391699884</v>
+        <v>659.9824391699887</v>
       </c>
       <c r="BA370" s="111" t="inlineStr">
         <is>
@@ -71535,31 +71535,31 @@
         <v>54920.92979565485</v>
       </c>
       <c r="BC370" s="375" t="n">
-        <v>56496.75148806424</v>
+        <v>56496.75148806423</v>
       </c>
       <c r="BD370" s="375" t="n">
-        <v>55957.84394996567</v>
+        <v>55957.84394996565</v>
       </c>
       <c r="BE370" s="375" t="n">
-        <v>52431.33015542696</v>
+        <v>52431.33015542695</v>
       </c>
       <c r="BF370" s="392" t="n">
-        <v>56018.87435173046</v>
+        <v>56018.87435173047</v>
       </c>
       <c r="BG370" s="386" t="n">
         <v>538.326186753865</v>
       </c>
       <c r="BH370" s="372" t="n">
-        <v>564.4618447950938</v>
+        <v>564.4618447950936</v>
       </c>
       <c r="BI370" s="372" t="n">
         <v>588.8613564801755</v>
       </c>
       <c r="BJ370" s="372" t="n">
-        <v>614.8282788519614</v>
+        <v>614.8282788519613</v>
       </c>
       <c r="BK370" s="387" t="n">
-        <v>659.9824391699884</v>
+        <v>659.9824391699887</v>
       </c>
       <c r="BR370" s="111" t="inlineStr">
         <is>
@@ -71567,49 +71567,49 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>55227.55342929586</v>
+        <v>55227.55342929587</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>56905.08867324544</v>
+        <v>56905.08867324542</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>56485.98781551626</v>
+        <v>56485.98781551624</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>53080.79535081491</v>
+        <v>53080.7953508149</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>56852.91156080306</v>
+        <v>56852.91156080308</v>
       </c>
       <c r="BX370" s="386" t="n">
         <v>539.6612028096362</v>
       </c>
       <c r="BY370" s="372" t="n">
-        <v>565.9105666048659</v>
+        <v>565.9105666048657</v>
       </c>
       <c r="BZ370" s="372" t="n">
         <v>590.4642594520905</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>616.722868040099</v>
+        <v>616.7228680400989</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>662.02321465238</v>
+        <v>662.0232146523803</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>178.9675421950328</v>
+        <v>178.967542195033</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>190.4056745744037</v>
+        <v>190.4056745744036</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>199.9229219469734</v>
+        <v>199.9229219469737</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>211.8809362706868</v>
+        <v>211.8809362706869</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>227.4091424758149</v>
+        <v>227.4091424758151</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71701,7 +71701,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="AO371" s="409" t="n">
-        <v>417885.4533985371</v>
+        <v>417885.4533985369</v>
       </c>
       <c r="AP371" s="410" t="n">
         <v>25268.66956059994</v>
@@ -71716,7 +71716,7 @@
         <v>27803.57572206694</v>
       </c>
       <c r="AT371" s="412" t="n">
-        <v>28794.80282956345</v>
+        <v>28794.80282956344</v>
       </c>
       <c r="BA371" s="111" t="inlineStr">
         <is>
@@ -71736,7 +71736,7 @@
         <v>397838.0844567387</v>
       </c>
       <c r="BF371" s="421" t="n">
-        <v>417885.4533985371</v>
+        <v>417885.4533985369</v>
       </c>
       <c r="BG371" s="416" t="n">
         <v>25268.66956059994</v>
@@ -71751,7 +71751,7 @@
         <v>27803.57572206694</v>
       </c>
       <c r="BK371" s="418" t="n">
-        <v>28794.80282956345</v>
+        <v>28794.80282956344</v>
       </c>
       <c r="BR371" s="111" t="inlineStr">
         <is>
@@ -71765,13 +71765,13 @@
         <v>548288.8330684749</v>
       </c>
       <c r="BU371" s="420" t="n">
-        <v>448994.5861672615</v>
+        <v>448994.5861672614</v>
       </c>
       <c r="BV371" s="420" t="n">
         <v>402245.7525736701</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>423521.3656159502</v>
+        <v>423521.3656159501</v>
       </c>
       <c r="BX371" s="416" t="n">
         <v>25256.546832515</v>
@@ -71780,28 +71780,28 @@
         <v>24162.04424372253</v>
       </c>
       <c r="BZ371" s="417" t="n">
-        <v>26235.74455205261</v>
+        <v>26235.74455205262</v>
       </c>
       <c r="CA371" s="417" t="n">
-        <v>27780.45073578561</v>
+        <v>27780.45073578562</v>
       </c>
       <c r="CB371" s="418" t="n">
-        <v>28770.81824586091</v>
+        <v>28770.8182458609</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>30.87585763408104</v>
+        <v>30.87585763407963</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>33.42901440362377</v>
+        <v>33.42901440362258</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>36.32946946924579</v>
+        <v>36.32946946924454</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>39.07531211650966</v>
+        <v>39.07531211650829</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>42.03063508050806</v>
+        <v>42.03063508050673</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71884,7 +71884,7 @@
         <v>798622.6246690482</v>
       </c>
       <c r="AL372" s="408" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="AM372" s="408" t="n">
         <v>666853.7543426913</v>
@@ -71908,7 +71908,7 @@
         <v>2326.994788066119</v>
       </c>
       <c r="AT372" s="438" t="n">
-        <v>2517.547115926639</v>
+        <v>2517.54711592664</v>
       </c>
       <c r="BA372" s="155" t="inlineStr">
         <is>
@@ -71919,7 +71919,7 @@
         <v>798622.6246690482</v>
       </c>
       <c r="BC372" s="440" t="n">
-        <v>764351.387857678</v>
+        <v>764351.3878576779</v>
       </c>
       <c r="BD372" s="440" t="n">
         <v>666853.7543426913</v>
@@ -71943,7 +71943,7 @@
         <v>2326.994788066119</v>
       </c>
       <c r="BK372" s="444" t="n">
-        <v>2517.547115926639</v>
+        <v>2517.54711592664</v>
       </c>
       <c r="BR372" s="155" t="inlineStr">
         <is>
@@ -71957,19 +71957,19 @@
         <v>768586.2921028842</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>672857.3486787789</v>
+        <v>672857.3486787787</v>
       </c>
       <c r="BV372" s="440" t="n">
         <v>628425.1925887223</v>
       </c>
       <c r="BW372" s="441" t="n">
-        <v>654199.8587620906</v>
+        <v>654199.8587620904</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>2666.932537370536</v>
+        <v>2666.932537370535</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>2565.084368566223</v>
+        <v>2565.084368566222</v>
       </c>
       <c r="BZ372" s="443" t="n">
         <v>2358.55611263262</v>
@@ -71981,19 +71981,19 @@
         <v>2516.171986431975</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>1068.402165215639</v>
+        <v>1068.402165215638</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>1070.386648073011</v>
+        <v>1070.386648073009</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>1156.26771421363</v>
+        <v>1156.267714213628</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>1214.473982957793</v>
+        <v>1214.473982957792</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>1203.937350667074</v>
+        <v>1203.937350667073</v>
       </c>
     </row>
     <row r="375">
